--- a/artfynd/A 31144-2024 artfynd.xlsx
+++ b/artfynd/A 31144-2024 artfynd.xlsx
@@ -1812,10 +1812,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>119590987</v>
+        <v>119591087</v>
       </c>
       <c r="B13" t="n">
-        <v>90562</v>
+        <v>78526</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1828,21 +1828,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1852,10 +1852,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>453772</v>
+        <v>453803</v>
       </c>
       <c r="R13" t="n">
-        <v>6807796</v>
+        <v>6808020</v>
       </c>
       <c r="S13" t="n">
         <v>15</v>
@@ -1882,12 +1882,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2024-09-06</t>
+          <t>2024-09-04</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2024-09-06</t>
+          <t>2024-09-04</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1914,7 +1914,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>119591087</v>
+        <v>119591043</v>
       </c>
       <c r="B14" t="n">
         <v>78526</v>
@@ -1954,10 +1954,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>453803</v>
+        <v>453774</v>
       </c>
       <c r="R14" t="n">
-        <v>6808020</v>
+        <v>6807849</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -1984,12 +1984,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2024-09-04</t>
+          <t>2024-09-06</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2024-09-04</t>
+          <t>2024-09-06</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2016,7 +2016,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>119591043</v>
+        <v>119591033</v>
       </c>
       <c r="B15" t="n">
         <v>78526</v>
@@ -2056,10 +2056,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>453774</v>
+        <v>453835</v>
       </c>
       <c r="R15" t="n">
-        <v>6807849</v>
+        <v>6807974</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2118,7 +2118,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>119591033</v>
+        <v>119591071</v>
       </c>
       <c r="B16" t="n">
         <v>78526</v>
@@ -2158,10 +2158,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>453835</v>
+        <v>453788</v>
       </c>
       <c r="R16" t="n">
-        <v>6807974</v>
+        <v>6808086</v>
       </c>
       <c r="S16" t="n">
         <v>15</v>
@@ -2220,10 +2220,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>119591071</v>
+        <v>119590987</v>
       </c>
       <c r="B17" t="n">
-        <v>78526</v>
+        <v>90562</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2236,21 +2236,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2260,10 +2260,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>453788</v>
+        <v>453772</v>
       </c>
       <c r="R17" t="n">
-        <v>6808086</v>
+        <v>6807796</v>
       </c>
       <c r="S17" t="n">
         <v>15</v>
@@ -2434,10 +2434,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>119591025</v>
+        <v>119591036</v>
       </c>
       <c r="B19" t="n">
-        <v>93935</v>
+        <v>78526</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2446,25 +2446,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>2387</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Källpraktmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Pseudobryum cinclidioides</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Huebener) T.J.Kop.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2474,10 +2474,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>453851</v>
+        <v>453849</v>
       </c>
       <c r="R19" t="n">
-        <v>6807838</v>
+        <v>6807844</v>
       </c>
       <c r="S19" t="n">
         <v>15</v>
@@ -2536,10 +2536,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>119591072</v>
+        <v>119590997</v>
       </c>
       <c r="B20" t="n">
-        <v>78526</v>
+        <v>57463</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2552,21 +2552,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2576,10 +2576,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>453773</v>
+        <v>453806</v>
       </c>
       <c r="R20" t="n">
-        <v>6808107</v>
+        <v>6808118</v>
       </c>
       <c r="S20" t="n">
         <v>15</v>
@@ -2638,10 +2638,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>119591090</v>
+        <v>119591025</v>
       </c>
       <c r="B21" t="n">
-        <v>78526</v>
+        <v>93935</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2650,25 +2650,25 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>2387</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Källpraktmossa</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudobryum cinclidioides</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Huebener) T.J.Kop.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2678,10 +2678,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>453794</v>
+        <v>453851</v>
       </c>
       <c r="R21" t="n">
-        <v>6808097</v>
+        <v>6807838</v>
       </c>
       <c r="S21" t="n">
         <v>15</v>
@@ -2708,12 +2708,12 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2024-09-04</t>
+          <t>2024-09-06</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2024-09-04</t>
+          <t>2024-09-06</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2740,7 +2740,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>119591086</v>
+        <v>119591072</v>
       </c>
       <c r="B22" t="n">
         <v>78526</v>
@@ -2780,10 +2780,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>453820</v>
+        <v>453773</v>
       </c>
       <c r="R22" t="n">
-        <v>6808020</v>
+        <v>6808107</v>
       </c>
       <c r="S22" t="n">
         <v>15</v>
@@ -2810,12 +2810,12 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2024-09-04</t>
+          <t>2024-09-06</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2024-09-04</t>
+          <t>2024-09-06</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2842,7 +2842,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>119591035</v>
+        <v>119591090</v>
       </c>
       <c r="B23" t="n">
         <v>78526</v>
@@ -2882,10 +2882,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>453808</v>
+        <v>453794</v>
       </c>
       <c r="R23" t="n">
-        <v>6807890</v>
+        <v>6808097</v>
       </c>
       <c r="S23" t="n">
         <v>15</v>
@@ -2912,12 +2912,12 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2024-09-06</t>
+          <t>2024-09-04</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2024-09-06</t>
+          <t>2024-09-04</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2944,7 +2944,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>119591036</v>
+        <v>119591086</v>
       </c>
       <c r="B24" t="n">
         <v>78526</v>
@@ -2984,10 +2984,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>453849</v>
+        <v>453820</v>
       </c>
       <c r="R24" t="n">
-        <v>6807844</v>
+        <v>6808020</v>
       </c>
       <c r="S24" t="n">
         <v>15</v>
@@ -3014,12 +3014,12 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2024-09-06</t>
+          <t>2024-09-04</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2024-09-06</t>
+          <t>2024-09-04</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3046,10 +3046,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>119590997</v>
+        <v>119591035</v>
       </c>
       <c r="B25" t="n">
-        <v>57463</v>
+        <v>78526</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3062,21 +3062,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3086,10 +3086,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>453806</v>
+        <v>453808</v>
       </c>
       <c r="R25" t="n">
-        <v>6808118</v>
+        <v>6807890</v>
       </c>
       <c r="S25" t="n">
         <v>15</v>
@@ -3454,10 +3454,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>119590976</v>
+        <v>119590994</v>
       </c>
       <c r="B29" t="n">
-        <v>79144</v>
+        <v>103418</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3466,25 +3466,25 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6453</v>
+        <v>222412</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3494,10 +3494,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>453836</v>
+        <v>453893</v>
       </c>
       <c r="R29" t="n">
-        <v>6807943</v>
+        <v>6808027</v>
       </c>
       <c r="S29" t="n">
         <v>15</v>
@@ -3556,10 +3556,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>119591012</v>
+        <v>119590976</v>
       </c>
       <c r="B30" t="n">
-        <v>96862</v>
+        <v>79144</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3568,25 +3568,25 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>221945</v>
+        <v>6453</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3596,10 +3596,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>453875</v>
+        <v>453836</v>
       </c>
       <c r="R30" t="n">
-        <v>6808094</v>
+        <v>6807943</v>
       </c>
       <c r="S30" t="n">
         <v>15</v>
@@ -3658,10 +3658,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>119590994</v>
+        <v>119591012</v>
       </c>
       <c r="B31" t="n">
-        <v>103418</v>
+        <v>96862</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3674,16 +3674,16 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>222412</v>
+        <v>221945</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -3698,10 +3698,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>453893</v>
+        <v>453875</v>
       </c>
       <c r="R31" t="n">
-        <v>6808027</v>
+        <v>6808094</v>
       </c>
       <c r="S31" t="n">
         <v>15</v>
@@ -4071,10 +4071,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>119590974</v>
+        <v>119591023</v>
       </c>
       <c r="B35" t="n">
-        <v>95455</v>
+        <v>78263</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4087,21 +4087,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>53</v>
+        <v>228912</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4111,10 +4111,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>453852</v>
+        <v>453770</v>
       </c>
       <c r="R35" t="n">
-        <v>6807959</v>
+        <v>6807984</v>
       </c>
       <c r="S35" t="n">
         <v>15</v>
@@ -4173,10 +4173,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>119591076</v>
+        <v>119590974</v>
       </c>
       <c r="B36" t="n">
-        <v>78526</v>
+        <v>95455</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4189,21 +4189,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>53</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4213,10 +4213,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>453811</v>
+        <v>453852</v>
       </c>
       <c r="R36" t="n">
-        <v>6808106</v>
+        <v>6807959</v>
       </c>
       <c r="S36" t="n">
         <v>15</v>
@@ -4275,7 +4275,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>119591057</v>
+        <v>119591076</v>
       </c>
       <c r="B37" t="n">
         <v>78526</v>
@@ -4315,10 +4315,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>453736</v>
+        <v>453811</v>
       </c>
       <c r="R37" t="n">
-        <v>6808004</v>
+        <v>6808106</v>
       </c>
       <c r="S37" t="n">
         <v>15</v>
@@ -4377,7 +4377,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>119591060</v>
+        <v>119591057</v>
       </c>
       <c r="B38" t="n">
         <v>78526</v>
@@ -4417,10 +4417,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>453748</v>
+        <v>453736</v>
       </c>
       <c r="R38" t="n">
-        <v>6808003</v>
+        <v>6808004</v>
       </c>
       <c r="S38" t="n">
         <v>15</v>
@@ -4479,10 +4479,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>119590979</v>
+        <v>119591060</v>
       </c>
       <c r="B39" t="n">
-        <v>79144</v>
+        <v>78526</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4495,21 +4495,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4519,10 +4519,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>453807</v>
+        <v>453748</v>
       </c>
       <c r="R39" t="n">
-        <v>6807719</v>
+        <v>6808003</v>
       </c>
       <c r="S39" t="n">
         <v>15</v>
@@ -4581,10 +4581,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>119591023</v>
+        <v>119590979</v>
       </c>
       <c r="B40" t="n">
-        <v>78263</v>
+        <v>79144</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4597,21 +4597,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4621,10 +4621,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>453770</v>
+        <v>453807</v>
       </c>
       <c r="R40" t="n">
-        <v>6807984</v>
+        <v>6807719</v>
       </c>
       <c r="S40" t="n">
         <v>15</v>
@@ -4683,10 +4683,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>119591089</v>
+        <v>119590986</v>
       </c>
       <c r="B41" t="n">
-        <v>78526</v>
+        <v>90562</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4699,21 +4699,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4723,10 +4723,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>453780</v>
+        <v>453795</v>
       </c>
       <c r="R41" t="n">
-        <v>6808055</v>
+        <v>6807770</v>
       </c>
       <c r="S41" t="n">
         <v>15</v>
@@ -4753,12 +4753,12 @@
       </c>
       <c r="Y41" t="inlineStr">
         <is>
-          <t>2024-09-04</t>
+          <t>2024-09-06</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>2024-09-04</t>
+          <t>2024-09-06</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4785,10 +4785,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>119591004</v>
+        <v>119591089</v>
       </c>
       <c r="B42" t="n">
-        <v>91884</v>
+        <v>78526</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4801,21 +4801,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>5449</v>
+        <v>6425</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4825,10 +4825,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>453785</v>
+        <v>453780</v>
       </c>
       <c r="R42" t="n">
-        <v>6808062</v>
+        <v>6808055</v>
       </c>
       <c r="S42" t="n">
         <v>15</v>
@@ -4855,12 +4855,12 @@
       </c>
       <c r="Y42" t="inlineStr">
         <is>
-          <t>2024-09-06</t>
+          <t>2024-09-04</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>2024-09-06</t>
+          <t>2024-09-04</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -4887,10 +4887,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>119591067</v>
+        <v>119591004</v>
       </c>
       <c r="B43" t="n">
-        <v>78526</v>
+        <v>91884</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -4903,21 +4903,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6425</v>
+        <v>5449</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4927,10 +4927,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>453775</v>
+        <v>453785</v>
       </c>
       <c r="R43" t="n">
-        <v>6808032</v>
+        <v>6808062</v>
       </c>
       <c r="S43" t="n">
         <v>15</v>
@@ -4989,7 +4989,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>119591065</v>
+        <v>119591067</v>
       </c>
       <c r="B44" t="n">
         <v>78526</v>
@@ -5029,10 +5029,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>453782</v>
+        <v>453775</v>
       </c>
       <c r="R44" t="n">
-        <v>6807982</v>
+        <v>6808032</v>
       </c>
       <c r="S44" t="n">
         <v>15</v>
@@ -5091,10 +5091,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>119590986</v>
+        <v>119591065</v>
       </c>
       <c r="B45" t="n">
-        <v>90562</v>
+        <v>78526</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5107,21 +5107,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5131,10 +5131,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>453795</v>
+        <v>453782</v>
       </c>
       <c r="R45" t="n">
-        <v>6807770</v>
+        <v>6807982</v>
       </c>
       <c r="S45" t="n">
         <v>15</v>
@@ -7355,10 +7355,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>119590999</v>
+        <v>119591006</v>
       </c>
       <c r="B67" t="n">
-        <v>91463</v>
+        <v>57310</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -7371,34 +7371,39 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>4745</v>
+        <v>100109</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Tallriska</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Lactarius musteus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P67" t="inlineStr">
         <is>
           <t>Rymån, Dlr</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>453793</v>
+        <v>453796</v>
       </c>
       <c r="R67" t="n">
-        <v>6808029</v>
+        <v>6808114</v>
       </c>
       <c r="S67" t="n">
         <v>15</v>
@@ -7425,12 +7430,17 @@
       </c>
       <c r="Y67" t="inlineStr">
         <is>
-          <t>2024-09-04</t>
+          <t>2024-09-06</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
         <is>
-          <t>2024-09-04</t>
+          <t>2024-09-06</t>
+        </is>
+      </c>
+      <c r="AC67" t="inlineStr">
+        <is>
+          <t>Färska ringhack (gran)</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7457,10 +7467,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>119591054</v>
+        <v>119590999</v>
       </c>
       <c r="B68" t="n">
-        <v>78526</v>
+        <v>91463</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -7473,21 +7483,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6425</v>
+        <v>4745</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallriska</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lactarius musteus</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7497,10 +7507,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>453738</v>
+        <v>453793</v>
       </c>
       <c r="R68" t="n">
-        <v>6807973</v>
+        <v>6808029</v>
       </c>
       <c r="S68" t="n">
         <v>15</v>
@@ -7527,12 +7537,12 @@
       </c>
       <c r="Y68" t="inlineStr">
         <is>
-          <t>2024-09-06</t>
+          <t>2024-09-04</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
         <is>
-          <t>2024-09-06</t>
+          <t>2024-09-04</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7559,10 +7569,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>119591006</v>
+        <v>119591054</v>
       </c>
       <c r="B69" t="n">
-        <v>57310</v>
+        <v>78526</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -7575,39 +7585,34 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
-      <c r="M69" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P69" t="inlineStr">
         <is>
           <t>Rymån, Dlr</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>453796</v>
+        <v>453738</v>
       </c>
       <c r="R69" t="n">
-        <v>6808114</v>
+        <v>6807973</v>
       </c>
       <c r="S69" t="n">
         <v>15</v>
@@ -7640,11 +7645,6 @@
       <c r="AA69" t="inlineStr">
         <is>
           <t>2024-09-06</t>
-        </is>
-      </c>
-      <c r="AC69" t="inlineStr">
-        <is>
-          <t>Färska ringhack (gran)</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8394,10 +8394,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>119591062</v>
+        <v>119590981</v>
       </c>
       <c r="B77" t="n">
-        <v>78526</v>
+        <v>79144</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -8410,21 +8410,21 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8434,10 +8434,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>453761</v>
+        <v>453770</v>
       </c>
       <c r="R77" t="n">
-        <v>6808000</v>
+        <v>6807987</v>
       </c>
       <c r="S77" t="n">
         <v>15</v>
@@ -8496,10 +8496,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>119591046</v>
+        <v>119590983</v>
       </c>
       <c r="B78" t="n">
-        <v>78526</v>
+        <v>79144</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -8512,21 +8512,21 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8536,10 +8536,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>453792</v>
+        <v>453762</v>
       </c>
       <c r="R78" t="n">
-        <v>6807881</v>
+        <v>6808048</v>
       </c>
       <c r="S78" t="n">
         <v>15</v>
@@ -8598,10 +8598,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>119591073</v>
+        <v>119591097</v>
       </c>
       <c r="B79" t="n">
-        <v>78526</v>
+        <v>57310</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -8614,34 +8614,39 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
+      <c r="M79" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P79" t="inlineStr">
         <is>
           <t>Rymån, Dlr</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>453797</v>
+        <v>453849</v>
       </c>
       <c r="R79" t="n">
-        <v>6808117</v>
+        <v>6807844</v>
       </c>
       <c r="S79" t="n">
         <v>15</v>
@@ -8700,7 +8705,7 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>119591037</v>
+        <v>119591062</v>
       </c>
       <c r="B80" t="n">
         <v>78526</v>
@@ -8740,10 +8745,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>453829</v>
+        <v>453761</v>
       </c>
       <c r="R80" t="n">
-        <v>6807768</v>
+        <v>6808000</v>
       </c>
       <c r="S80" t="n">
         <v>15</v>
@@ -8802,10 +8807,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>119590981</v>
+        <v>119591046</v>
       </c>
       <c r="B81" t="n">
-        <v>79144</v>
+        <v>78526</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -8818,21 +8823,21 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -8842,10 +8847,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>453770</v>
+        <v>453792</v>
       </c>
       <c r="R81" t="n">
-        <v>6807987</v>
+        <v>6807881</v>
       </c>
       <c r="S81" t="n">
         <v>15</v>
@@ -8904,10 +8909,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>119590983</v>
+        <v>119591073</v>
       </c>
       <c r="B82" t="n">
-        <v>79144</v>
+        <v>78526</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -8920,21 +8925,21 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -8944,10 +8949,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>453762</v>
+        <v>453797</v>
       </c>
       <c r="R82" t="n">
-        <v>6808048</v>
+        <v>6808117</v>
       </c>
       <c r="S82" t="n">
         <v>15</v>
@@ -9006,10 +9011,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>119591097</v>
+        <v>119591037</v>
       </c>
       <c r="B83" t="n">
-        <v>57310</v>
+        <v>78526</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -9022,39 +9027,34 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
-      <c r="M83" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P83" t="inlineStr">
         <is>
           <t>Rymån, Dlr</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>453849</v>
+        <v>453829</v>
       </c>
       <c r="R83" t="n">
-        <v>6807844</v>
+        <v>6807768</v>
       </c>
       <c r="S83" t="n">
         <v>15</v>
@@ -10133,10 +10133,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>119591028</v>
+        <v>119591007</v>
       </c>
       <c r="B94" t="n">
-        <v>90580</v>
+        <v>57310</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>
@@ -10149,34 +10149,39 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
+      <c r="M94" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P94" t="inlineStr">
         <is>
           <t>Rymån, Dlr</t>
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>453791</v>
+        <v>453808</v>
       </c>
       <c r="R94" t="n">
-        <v>6807765</v>
+        <v>6808114</v>
       </c>
       <c r="S94" t="n">
         <v>15</v>
@@ -10213,7 +10218,7 @@
       </c>
       <c r="AC94" t="inlineStr">
         <is>
-          <t>Gamla fruktkroppar</t>
+          <t>Färska ringhack (gran)</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -10240,10 +10245,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>119591077</v>
+        <v>119591028</v>
       </c>
       <c r="B95" t="n">
-        <v>78526</v>
+        <v>90580</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
@@ -10256,21 +10261,21 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -10280,10 +10285,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>453815</v>
+        <v>453791</v>
       </c>
       <c r="R95" t="n">
-        <v>6808130</v>
+        <v>6807765</v>
       </c>
       <c r="S95" t="n">
         <v>15</v>
@@ -10316,6 +10321,11 @@
       <c r="AA95" t="inlineStr">
         <is>
           <t>2024-09-06</t>
+        </is>
+      </c>
+      <c r="AC95" t="inlineStr">
+        <is>
+          <t>Gamla fruktkroppar</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -10342,7 +10352,7 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>119591053</v>
+        <v>119591077</v>
       </c>
       <c r="B96" t="n">
         <v>78526</v>
@@ -10382,10 +10392,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>453752</v>
+        <v>453815</v>
       </c>
       <c r="R96" t="n">
-        <v>6807968</v>
+        <v>6808130</v>
       </c>
       <c r="S96" t="n">
         <v>15</v>
@@ -10444,7 +10454,7 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>119591059</v>
+        <v>119591053</v>
       </c>
       <c r="B97" t="n">
         <v>78526</v>
@@ -10484,10 +10494,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>453737</v>
+        <v>453752</v>
       </c>
       <c r="R97" t="n">
-        <v>6808007</v>
+        <v>6807968</v>
       </c>
       <c r="S97" t="n">
         <v>15</v>
@@ -10546,10 +10556,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>119591031</v>
+        <v>119591059</v>
       </c>
       <c r="B98" t="n">
-        <v>90580</v>
+        <v>78526</v>
       </c>
       <c r="C98" t="inlineStr">
         <is>
@@ -10562,21 +10572,21 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -10586,10 +10596,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>453886</v>
+        <v>453737</v>
       </c>
       <c r="R98" t="n">
-        <v>6808055</v>
+        <v>6808007</v>
       </c>
       <c r="S98" t="n">
         <v>15</v>
@@ -10648,10 +10658,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>119591069</v>
+        <v>119591031</v>
       </c>
       <c r="B99" t="n">
-        <v>78526</v>
+        <v>90580</v>
       </c>
       <c r="C99" t="inlineStr">
         <is>
@@ -10664,21 +10674,21 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
@@ -10688,10 +10698,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>453756</v>
+        <v>453886</v>
       </c>
       <c r="R99" t="n">
-        <v>6808048</v>
+        <v>6808055</v>
       </c>
       <c r="S99" t="n">
         <v>15</v>
@@ -10750,7 +10760,7 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>119591032</v>
+        <v>119591069</v>
       </c>
       <c r="B100" t="n">
         <v>78526</v>
@@ -10790,10 +10800,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>453897</v>
+        <v>453756</v>
       </c>
       <c r="R100" t="n">
-        <v>6808009</v>
+        <v>6808048</v>
       </c>
       <c r="S100" t="n">
         <v>15</v>
@@ -10852,10 +10862,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>119591007</v>
+        <v>119591032</v>
       </c>
       <c r="B101" t="n">
-        <v>57310</v>
+        <v>78526</v>
       </c>
       <c r="C101" t="inlineStr">
         <is>
@@ -10868,39 +10878,34 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
-      <c r="M101" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P101" t="inlineStr">
         <is>
           <t>Rymån, Dlr</t>
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>453808</v>
+        <v>453897</v>
       </c>
       <c r="R101" t="n">
-        <v>6808114</v>
+        <v>6808009</v>
       </c>
       <c r="S101" t="n">
         <v>15</v>
@@ -10933,11 +10938,6 @@
       <c r="AA101" t="inlineStr">
         <is>
           <t>2024-09-06</t>
-        </is>
-      </c>
-      <c r="AC101" t="inlineStr">
-        <is>
-          <t>Färska ringhack (gran)</t>
         </is>
       </c>
       <c r="AD101" t="b">

--- a/artfynd/A 31144-2024 artfynd.xlsx
+++ b/artfynd/A 31144-2024 artfynd.xlsx
@@ -2434,10 +2434,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>119591036</v>
+        <v>119591025</v>
       </c>
       <c r="B19" t="n">
-        <v>78526</v>
+        <v>93935</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2446,25 +2446,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>2387</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Källpraktmossa</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudobryum cinclidioides</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Huebener) T.J.Kop.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2474,10 +2474,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>453849</v>
+        <v>453851</v>
       </c>
       <c r="R19" t="n">
-        <v>6807844</v>
+        <v>6807838</v>
       </c>
       <c r="S19" t="n">
         <v>15</v>
@@ -2638,10 +2638,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>119591025</v>
+        <v>119591072</v>
       </c>
       <c r="B21" t="n">
-        <v>93935</v>
+        <v>78526</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2650,25 +2650,25 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>2387</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Källpraktmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Pseudobryum cinclidioides</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Huebener) T.J.Kop.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2678,10 +2678,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>453851</v>
+        <v>453773</v>
       </c>
       <c r="R21" t="n">
-        <v>6807838</v>
+        <v>6808107</v>
       </c>
       <c r="S21" t="n">
         <v>15</v>
@@ -2740,7 +2740,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>119591072</v>
+        <v>119591090</v>
       </c>
       <c r="B22" t="n">
         <v>78526</v>
@@ -2780,10 +2780,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>453773</v>
+        <v>453794</v>
       </c>
       <c r="R22" t="n">
-        <v>6808107</v>
+        <v>6808097</v>
       </c>
       <c r="S22" t="n">
         <v>15</v>
@@ -2810,12 +2810,12 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2024-09-06</t>
+          <t>2024-09-04</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2024-09-06</t>
+          <t>2024-09-04</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2842,7 +2842,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>119591090</v>
+        <v>119591086</v>
       </c>
       <c r="B23" t="n">
         <v>78526</v>
@@ -2882,10 +2882,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>453794</v>
+        <v>453820</v>
       </c>
       <c r="R23" t="n">
-        <v>6808097</v>
+        <v>6808020</v>
       </c>
       <c r="S23" t="n">
         <v>15</v>
@@ -2944,7 +2944,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>119591086</v>
+        <v>119591035</v>
       </c>
       <c r="B24" t="n">
         <v>78526</v>
@@ -2984,10 +2984,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>453820</v>
+        <v>453808</v>
       </c>
       <c r="R24" t="n">
-        <v>6808020</v>
+        <v>6807890</v>
       </c>
       <c r="S24" t="n">
         <v>15</v>
@@ -3014,12 +3014,12 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2024-09-04</t>
+          <t>2024-09-06</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2024-09-04</t>
+          <t>2024-09-06</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3046,7 +3046,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>119591035</v>
+        <v>119591036</v>
       </c>
       <c r="B25" t="n">
         <v>78526</v>
@@ -3086,10 +3086,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>453808</v>
+        <v>453849</v>
       </c>
       <c r="R25" t="n">
-        <v>6807890</v>
+        <v>6807844</v>
       </c>
       <c r="S25" t="n">
         <v>15</v>
@@ -7355,10 +7355,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>119591006</v>
+        <v>119590999</v>
       </c>
       <c r="B67" t="n">
-        <v>57310</v>
+        <v>91463</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -7371,39 +7371,34 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>100109</v>
+        <v>4745</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tallriska</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lactarius musteus</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
-      <c r="M67" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P67" t="inlineStr">
         <is>
           <t>Rymån, Dlr</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>453796</v>
+        <v>453793</v>
       </c>
       <c r="R67" t="n">
-        <v>6808114</v>
+        <v>6808029</v>
       </c>
       <c r="S67" t="n">
         <v>15</v>
@@ -7430,17 +7425,12 @@
       </c>
       <c r="Y67" t="inlineStr">
         <is>
-          <t>2024-09-06</t>
+          <t>2024-09-04</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
         <is>
-          <t>2024-09-06</t>
-        </is>
-      </c>
-      <c r="AC67" t="inlineStr">
-        <is>
-          <t>Färska ringhack (gran)</t>
+          <t>2024-09-04</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7467,10 +7457,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>119590999</v>
+        <v>119591054</v>
       </c>
       <c r="B68" t="n">
-        <v>91463</v>
+        <v>78526</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -7483,21 +7473,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>4745</v>
+        <v>6425</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Tallriska</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Lactarius musteus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7507,10 +7497,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>453793</v>
+        <v>453738</v>
       </c>
       <c r="R68" t="n">
-        <v>6808029</v>
+        <v>6807973</v>
       </c>
       <c r="S68" t="n">
         <v>15</v>
@@ -7537,12 +7527,12 @@
       </c>
       <c r="Y68" t="inlineStr">
         <is>
-          <t>2024-09-04</t>
+          <t>2024-09-06</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
         <is>
-          <t>2024-09-04</t>
+          <t>2024-09-06</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7569,10 +7559,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>119591054</v>
+        <v>119591006</v>
       </c>
       <c r="B69" t="n">
-        <v>78526</v>
+        <v>57310</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -7585,34 +7575,39 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P69" t="inlineStr">
         <is>
           <t>Rymån, Dlr</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>453738</v>
+        <v>453796</v>
       </c>
       <c r="R69" t="n">
-        <v>6807973</v>
+        <v>6808114</v>
       </c>
       <c r="S69" t="n">
         <v>15</v>
@@ -7645,6 +7640,11 @@
       <c r="AA69" t="inlineStr">
         <is>
           <t>2024-09-06</t>
+        </is>
+      </c>
+      <c r="AC69" t="inlineStr">
+        <is>
+          <t>Färska ringhack (gran)</t>
         </is>
       </c>
       <c r="AD69" t="b">

--- a/artfynd/A 31144-2024 artfynd.xlsx
+++ b/artfynd/A 31144-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119590975</v>
+        <v>119591048</v>
       </c>
       <c r="B2" t="n">
-        <v>79144</v>
+        <v>78526</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>453828</v>
+        <v>453788</v>
       </c>
       <c r="R2" t="n">
-        <v>6807944</v>
+        <v>6807903</v>
       </c>
       <c r="S2" t="n">
         <v>15</v>
@@ -777,7 +777,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119591082</v>
+        <v>119591058</v>
       </c>
       <c r="B3" t="n">
         <v>78526</v>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>453850</v>
+        <v>453734</v>
       </c>
       <c r="R3" t="n">
-        <v>6808037</v>
+        <v>6808007</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -879,7 +879,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119591048</v>
+        <v>119591040</v>
       </c>
       <c r="B4" t="n">
         <v>78526</v>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>453788</v>
+        <v>453808</v>
       </c>
       <c r="R4" t="n">
-        <v>6807903</v>
+        <v>6807761</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119591026</v>
+        <v>119591052</v>
       </c>
       <c r="B5" t="n">
-        <v>78262</v>
+        <v>78526</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -997,21 +997,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>453770</v>
+        <v>453755</v>
       </c>
       <c r="R5" t="n">
-        <v>6807987</v>
+        <v>6807948</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1083,7 +1083,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119591080</v>
+        <v>119591069</v>
       </c>
       <c r="B6" t="n">
         <v>78526</v>
@@ -1123,10 +1123,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>453829</v>
+        <v>453756</v>
       </c>
       <c r="R6" t="n">
-        <v>6808069</v>
+        <v>6808048</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1185,7 +1185,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119591047</v>
+        <v>119591064</v>
       </c>
       <c r="B7" t="n">
         <v>78526</v>
@@ -1225,10 +1225,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>453785</v>
+        <v>453761</v>
       </c>
       <c r="R7" t="n">
-        <v>6807890</v>
+        <v>6807996</v>
       </c>
       <c r="S7" t="n">
         <v>15</v>
@@ -1287,10 +1287,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119591061</v>
+        <v>119591019</v>
       </c>
       <c r="B8" t="n">
-        <v>78526</v>
+        <v>96865</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1299,38 +1299,47 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>221946</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mattlummer</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium clavatum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Rymån, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>453756</v>
+        <v>453836</v>
       </c>
       <c r="R8" t="n">
-        <v>6808003</v>
+        <v>6807799</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1389,10 +1398,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>119591029</v>
+        <v>119590975</v>
       </c>
       <c r="B9" t="n">
-        <v>90580</v>
+        <v>79144</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1405,21 +1414,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5432</v>
+        <v>6453</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1429,10 +1438,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>453861</v>
+        <v>453828</v>
       </c>
       <c r="R9" t="n">
-        <v>6807970</v>
+        <v>6807944</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1491,7 +1500,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>119591055</v>
+        <v>119591050</v>
       </c>
       <c r="B10" t="n">
         <v>78526</v>
@@ -1531,10 +1540,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>453747</v>
+        <v>453782</v>
       </c>
       <c r="R10" t="n">
-        <v>6807979</v>
+        <v>6807956</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>
@@ -1593,10 +1602,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>119590991</v>
+        <v>119591042</v>
       </c>
       <c r="B11" t="n">
-        <v>57310</v>
+        <v>78526</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1609,39 +1618,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Rymån, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>453887</v>
+        <v>453788</v>
       </c>
       <c r="R11" t="n">
-        <v>6808050</v>
+        <v>6807792</v>
       </c>
       <c r="S11" t="n">
         <v>15</v>
@@ -1700,10 +1704,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>119591008</v>
+        <v>119591049</v>
       </c>
       <c r="B12" t="n">
-        <v>57310</v>
+        <v>78526</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1716,39 +1720,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Rymån, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>453821</v>
+        <v>453796</v>
       </c>
       <c r="R12" t="n">
-        <v>6808117</v>
+        <v>6807942</v>
       </c>
       <c r="S12" t="n">
         <v>15</v>
@@ -1781,11 +1780,6 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2024-09-06</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Färska ringhack (gran)</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1812,10 +1806,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>119591087</v>
+        <v>119591011</v>
       </c>
       <c r="B13" t="n">
-        <v>78526</v>
+        <v>96862</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1824,25 +1818,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1852,10 +1846,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>453803</v>
+        <v>453903</v>
       </c>
       <c r="R13" t="n">
-        <v>6808020</v>
+        <v>6807986</v>
       </c>
       <c r="S13" t="n">
         <v>15</v>
@@ -1882,12 +1876,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2024-09-04</t>
+          <t>2024-09-06</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2024-09-04</t>
+          <t>2024-09-06</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1914,10 +1908,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>119591043</v>
+        <v>119590980</v>
       </c>
       <c r="B14" t="n">
-        <v>78526</v>
+        <v>79144</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1930,21 +1924,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1954,10 +1948,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>453774</v>
+        <v>453791</v>
       </c>
       <c r="R14" t="n">
-        <v>6807849</v>
+        <v>6807707</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -2016,10 +2010,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>119591033</v>
+        <v>119591028</v>
       </c>
       <c r="B15" t="n">
-        <v>78526</v>
+        <v>90580</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2032,21 +2026,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2056,10 +2050,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>453835</v>
+        <v>453791</v>
       </c>
       <c r="R15" t="n">
-        <v>6807974</v>
+        <v>6807765</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2092,6 +2086,11 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2024-09-06</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Gamla fruktkroppar</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2118,7 +2117,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>119591071</v>
+        <v>119591067</v>
       </c>
       <c r="B16" t="n">
         <v>78526</v>
@@ -2158,10 +2157,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>453788</v>
+        <v>453775</v>
       </c>
       <c r="R16" t="n">
-        <v>6808086</v>
+        <v>6808032</v>
       </c>
       <c r="S16" t="n">
         <v>15</v>
@@ -2220,10 +2219,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>119590987</v>
+        <v>119591035</v>
       </c>
       <c r="B17" t="n">
-        <v>90562</v>
+        <v>78526</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2236,21 +2235,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2260,10 +2259,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>453772</v>
+        <v>453808</v>
       </c>
       <c r="R17" t="n">
-        <v>6807796</v>
+        <v>6807890</v>
       </c>
       <c r="S17" t="n">
         <v>15</v>
@@ -2322,10 +2321,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>119591010</v>
+        <v>119590997</v>
       </c>
       <c r="B18" t="n">
-        <v>57310</v>
+        <v>57463</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2338,36 +2337,31 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Rymån, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>453805</v>
+        <v>453806</v>
       </c>
       <c r="R18" t="n">
         <v>6808118</v>
@@ -2397,17 +2391,12 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2024-09-04</t>
+          <t>2024-09-06</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2024-09-04</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Färska ringhack (gran)</t>
+          <t>2024-09-06</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2434,10 +2423,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>119591025</v>
+        <v>119591008</v>
       </c>
       <c r="B19" t="n">
-        <v>93935</v>
+        <v>57310</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2446,38 +2435,43 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>2387</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Källpraktmossa</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Pseudobryum cinclidioides</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Huebener) T.J.Kop.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Rymån, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>453851</v>
+        <v>453821</v>
       </c>
       <c r="R19" t="n">
-        <v>6807838</v>
+        <v>6808117</v>
       </c>
       <c r="S19" t="n">
         <v>15</v>
@@ -2510,6 +2504,11 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2024-09-06</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Färska ringhack (gran)</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2536,10 +2535,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>119590997</v>
+        <v>119591009</v>
       </c>
       <c r="B20" t="n">
-        <v>57463</v>
+        <v>57310</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2552,34 +2551,39 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Rymån, Dlr</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>453806</v>
+        <v>453815</v>
       </c>
       <c r="R20" t="n">
-        <v>6808118</v>
+        <v>6808098</v>
       </c>
       <c r="S20" t="n">
         <v>15</v>
@@ -2612,6 +2616,11 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2024-09-06</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Färska ringhack (gran)</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2638,7 +2647,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>119591072</v>
+        <v>119591089</v>
       </c>
       <c r="B21" t="n">
         <v>78526</v>
@@ -2678,10 +2687,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>453773</v>
+        <v>453780</v>
       </c>
       <c r="R21" t="n">
-        <v>6808107</v>
+        <v>6808055</v>
       </c>
       <c r="S21" t="n">
         <v>15</v>
@@ -2708,12 +2717,12 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2024-09-06</t>
+          <t>2024-09-04</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2024-09-06</t>
+          <t>2024-09-04</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2740,7 +2749,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>119591090</v>
+        <v>119591077</v>
       </c>
       <c r="B22" t="n">
         <v>78526</v>
@@ -2780,10 +2789,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>453794</v>
+        <v>453815</v>
       </c>
       <c r="R22" t="n">
-        <v>6808097</v>
+        <v>6808130</v>
       </c>
       <c r="S22" t="n">
         <v>15</v>
@@ -2810,12 +2819,12 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2024-09-04</t>
+          <t>2024-09-06</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2024-09-04</t>
+          <t>2024-09-06</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2842,7 +2851,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>119591086</v>
+        <v>119591071</v>
       </c>
       <c r="B23" t="n">
         <v>78526</v>
@@ -2882,10 +2891,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>453820</v>
+        <v>453788</v>
       </c>
       <c r="R23" t="n">
-        <v>6808020</v>
+        <v>6808086</v>
       </c>
       <c r="S23" t="n">
         <v>15</v>
@@ -2912,12 +2921,12 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2024-09-04</t>
+          <t>2024-09-06</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2024-09-04</t>
+          <t>2024-09-06</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2944,10 +2953,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>119591035</v>
+        <v>119591023</v>
       </c>
       <c r="B24" t="n">
-        <v>78526</v>
+        <v>78263</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -2960,21 +2969,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2984,10 +2993,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>453808</v>
+        <v>453770</v>
       </c>
       <c r="R24" t="n">
-        <v>6807890</v>
+        <v>6807984</v>
       </c>
       <c r="S24" t="n">
         <v>15</v>
@@ -3046,7 +3055,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>119591036</v>
+        <v>119591072</v>
       </c>
       <c r="B25" t="n">
         <v>78526</v>
@@ -3086,10 +3095,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>453849</v>
+        <v>453773</v>
       </c>
       <c r="R25" t="n">
-        <v>6807844</v>
+        <v>6808107</v>
       </c>
       <c r="S25" t="n">
         <v>15</v>
@@ -3148,10 +3157,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>119591030</v>
+        <v>119591083</v>
       </c>
       <c r="B26" t="n">
-        <v>90580</v>
+        <v>78526</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3164,21 +3173,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3188,10 +3197,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>453779</v>
+        <v>453848</v>
       </c>
       <c r="R26" t="n">
-        <v>6807856</v>
+        <v>6808029</v>
       </c>
       <c r="S26" t="n">
         <v>15</v>
@@ -3250,7 +3259,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>119591049</v>
+        <v>119591057</v>
       </c>
       <c r="B27" t="n">
         <v>78526</v>
@@ -3290,10 +3299,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>453796</v>
+        <v>453736</v>
       </c>
       <c r="R27" t="n">
-        <v>6807942</v>
+        <v>6808004</v>
       </c>
       <c r="S27" t="n">
         <v>15</v>
@@ -3352,10 +3361,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>119591051</v>
+        <v>119591022</v>
       </c>
       <c r="B28" t="n">
-        <v>78526</v>
+        <v>78263</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3368,21 +3377,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3392,10 +3401,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>453755</v>
+        <v>453759</v>
       </c>
       <c r="R28" t="n">
-        <v>6807941</v>
+        <v>6807967</v>
       </c>
       <c r="S28" t="n">
         <v>15</v>
@@ -3454,10 +3463,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>119590994</v>
+        <v>119591012</v>
       </c>
       <c r="B29" t="n">
-        <v>103418</v>
+        <v>96862</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3470,16 +3479,16 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>222412</v>
+        <v>221945</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -3494,10 +3503,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>453893</v>
+        <v>453875</v>
       </c>
       <c r="R29" t="n">
-        <v>6808027</v>
+        <v>6808094</v>
       </c>
       <c r="S29" t="n">
         <v>15</v>
@@ -3556,10 +3565,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>119590976</v>
+        <v>119591004</v>
       </c>
       <c r="B30" t="n">
-        <v>79144</v>
+        <v>91884</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3572,21 +3581,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6453</v>
+        <v>5449</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3596,10 +3605,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>453836</v>
+        <v>453785</v>
       </c>
       <c r="R30" t="n">
-        <v>6807943</v>
+        <v>6808062</v>
       </c>
       <c r="S30" t="n">
         <v>15</v>
@@ -3658,10 +3667,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>119591012</v>
+        <v>119591053</v>
       </c>
       <c r="B31" t="n">
-        <v>96862</v>
+        <v>78526</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3670,25 +3679,25 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3698,10 +3707,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>453875</v>
+        <v>453752</v>
       </c>
       <c r="R31" t="n">
-        <v>6808094</v>
+        <v>6807968</v>
       </c>
       <c r="S31" t="n">
         <v>15</v>
@@ -3760,10 +3769,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>119590978</v>
+        <v>119591076</v>
       </c>
       <c r="B32" t="n">
-        <v>79144</v>
+        <v>78526</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3776,21 +3785,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3800,10 +3809,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>453823</v>
+        <v>453811</v>
       </c>
       <c r="R32" t="n">
-        <v>6807778</v>
+        <v>6808106</v>
       </c>
       <c r="S32" t="n">
         <v>15</v>
@@ -3862,10 +3871,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>119590982</v>
+        <v>119591080</v>
       </c>
       <c r="B33" t="n">
-        <v>79144</v>
+        <v>78526</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3878,21 +3887,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3902,10 +3911,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>453794</v>
+        <v>453829</v>
       </c>
       <c r="R33" t="n">
-        <v>6807980</v>
+        <v>6808069</v>
       </c>
       <c r="S33" t="n">
         <v>15</v>
@@ -3964,10 +3973,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>119590990</v>
+        <v>119591070</v>
       </c>
       <c r="B34" t="n">
-        <v>57310</v>
+        <v>78526</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -3980,39 +3989,34 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P34" t="inlineStr">
         <is>
           <t>Rymån, Dlr</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>453803</v>
+        <v>453759</v>
       </c>
       <c r="R34" t="n">
-        <v>6807752</v>
+        <v>6808051</v>
       </c>
       <c r="S34" t="n">
         <v>15</v>
@@ -4071,10 +4075,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>119591023</v>
+        <v>119591033</v>
       </c>
       <c r="B35" t="n">
-        <v>78263</v>
+        <v>78526</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4087,21 +4091,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4111,10 +4115,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>453770</v>
+        <v>453835</v>
       </c>
       <c r="R35" t="n">
-        <v>6807984</v>
+        <v>6807974</v>
       </c>
       <c r="S35" t="n">
         <v>15</v>
@@ -4173,10 +4177,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>119590974</v>
+        <v>119590978</v>
       </c>
       <c r="B36" t="n">
-        <v>95455</v>
+        <v>79144</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4189,21 +4193,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>53</v>
+        <v>6453</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4213,10 +4217,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>453852</v>
+        <v>453823</v>
       </c>
       <c r="R36" t="n">
-        <v>6807959</v>
+        <v>6807778</v>
       </c>
       <c r="S36" t="n">
         <v>15</v>
@@ -4275,10 +4279,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>119591076</v>
+        <v>119591010</v>
       </c>
       <c r="B37" t="n">
-        <v>78526</v>
+        <v>57310</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4291,34 +4295,39 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P37" t="inlineStr">
         <is>
           <t>Rymån, Dlr</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>453811</v>
+        <v>453805</v>
       </c>
       <c r="R37" t="n">
-        <v>6808106</v>
+        <v>6808118</v>
       </c>
       <c r="S37" t="n">
         <v>15</v>
@@ -4345,12 +4354,17 @@
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>2024-09-06</t>
+          <t>2024-09-04</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2024-09-06</t>
+          <t>2024-09-04</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>Färska ringhack (gran)</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4377,10 +4391,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>119591057</v>
+        <v>119590994</v>
       </c>
       <c r="B38" t="n">
-        <v>78526</v>
+        <v>103418</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4389,25 +4403,25 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>222412</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4417,10 +4431,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>453736</v>
+        <v>453893</v>
       </c>
       <c r="R38" t="n">
-        <v>6808004</v>
+        <v>6808027</v>
       </c>
       <c r="S38" t="n">
         <v>15</v>
@@ -4479,7 +4493,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>119591060</v>
+        <v>119591056</v>
       </c>
       <c r="B39" t="n">
         <v>78526</v>
@@ -4519,10 +4533,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>453748</v>
+        <v>453742</v>
       </c>
       <c r="R39" t="n">
-        <v>6808003</v>
+        <v>6807994</v>
       </c>
       <c r="S39" t="n">
         <v>15</v>
@@ -4581,10 +4595,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>119590979</v>
+        <v>119590996</v>
       </c>
       <c r="B40" t="n">
-        <v>79144</v>
+        <v>57463</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4597,21 +4611,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6453</v>
+        <v>103021</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4621,10 +4635,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>453807</v>
+        <v>453750</v>
       </c>
       <c r="R40" t="n">
-        <v>6807719</v>
+        <v>6807861</v>
       </c>
       <c r="S40" t="n">
         <v>15</v>
@@ -4683,10 +4697,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>119590986</v>
+        <v>119591066</v>
       </c>
       <c r="B41" t="n">
-        <v>90562</v>
+        <v>78526</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4699,21 +4713,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4723,10 +4737,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>453795</v>
+        <v>453787</v>
       </c>
       <c r="R41" t="n">
-        <v>6807770</v>
+        <v>6808020</v>
       </c>
       <c r="S41" t="n">
         <v>15</v>
@@ -4785,10 +4799,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>119591089</v>
+        <v>119591029</v>
       </c>
       <c r="B42" t="n">
-        <v>78526</v>
+        <v>90580</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4801,21 +4815,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4825,10 +4839,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>453780</v>
+        <v>453861</v>
       </c>
       <c r="R42" t="n">
-        <v>6808055</v>
+        <v>6807970</v>
       </c>
       <c r="S42" t="n">
         <v>15</v>
@@ -4855,12 +4869,12 @@
       </c>
       <c r="Y42" t="inlineStr">
         <is>
-          <t>2024-09-04</t>
+          <t>2024-09-06</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>2024-09-04</t>
+          <t>2024-09-06</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -4887,10 +4901,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>119591004</v>
+        <v>119591082</v>
       </c>
       <c r="B43" t="n">
-        <v>91884</v>
+        <v>78526</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -4903,21 +4917,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>5449</v>
+        <v>6425</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4927,10 +4941,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>453785</v>
+        <v>453850</v>
       </c>
       <c r="R43" t="n">
-        <v>6808062</v>
+        <v>6808037</v>
       </c>
       <c r="S43" t="n">
         <v>15</v>
@@ -4989,7 +5003,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>119591067</v>
+        <v>119591032</v>
       </c>
       <c r="B44" t="n">
         <v>78526</v>
@@ -5029,10 +5043,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>453775</v>
+        <v>453897</v>
       </c>
       <c r="R44" t="n">
-        <v>6808032</v>
+        <v>6808009</v>
       </c>
       <c r="S44" t="n">
         <v>15</v>
@@ -5091,7 +5105,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>119591065</v>
+        <v>119591087</v>
       </c>
       <c r="B45" t="n">
         <v>78526</v>
@@ -5131,10 +5145,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>453782</v>
+        <v>453803</v>
       </c>
       <c r="R45" t="n">
-        <v>6807982</v>
+        <v>6808020</v>
       </c>
       <c r="S45" t="n">
         <v>15</v>
@@ -5161,12 +5175,12 @@
       </c>
       <c r="Y45" t="inlineStr">
         <is>
-          <t>2024-09-06</t>
+          <t>2024-09-04</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>2024-09-06</t>
+          <t>2024-09-04</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5193,10 +5207,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>119590972</v>
+        <v>119591101</v>
       </c>
       <c r="B46" t="n">
-        <v>74638</v>
+        <v>5169</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5205,25 +5219,25 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6440</v>
+        <v>100526</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5233,10 +5247,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>453874</v>
+        <v>453849</v>
       </c>
       <c r="R46" t="n">
-        <v>6808094</v>
+        <v>6807844</v>
       </c>
       <c r="S46" t="n">
         <v>15</v>
@@ -5295,10 +5309,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>119591084</v>
+        <v>119591006</v>
       </c>
       <c r="B47" t="n">
-        <v>78526</v>
+        <v>57310</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5311,34 +5325,39 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P47" t="inlineStr">
         <is>
           <t>Rymån, Dlr</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>453835</v>
+        <v>453796</v>
       </c>
       <c r="R47" t="n">
-        <v>6808031</v>
+        <v>6808114</v>
       </c>
       <c r="S47" t="n">
         <v>15</v>
@@ -5365,12 +5384,17 @@
       </c>
       <c r="Y47" t="inlineStr">
         <is>
-          <t>2024-09-04</t>
+          <t>2024-09-06</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>2024-09-04</t>
+          <t>2024-09-06</t>
+        </is>
+      </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>Färska ringhack (gran)</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5397,7 +5421,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>119591058</v>
+        <v>119591059</v>
       </c>
       <c r="B48" t="n">
         <v>78526</v>
@@ -5437,7 +5461,7 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>453734</v>
+        <v>453737</v>
       </c>
       <c r="R48" t="n">
         <v>6808007</v>
@@ -5499,10 +5523,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>119591075</v>
+        <v>119590972</v>
       </c>
       <c r="B49" t="n">
-        <v>78526</v>
+        <v>74638</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5515,21 +5539,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5539,10 +5563,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>453809</v>
+        <v>453874</v>
       </c>
       <c r="R49" t="n">
-        <v>6808107</v>
+        <v>6808094</v>
       </c>
       <c r="S49" t="n">
         <v>15</v>
@@ -5601,7 +5625,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>119591045</v>
+        <v>119591073</v>
       </c>
       <c r="B50" t="n">
         <v>78526</v>
@@ -5641,10 +5665,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>453764</v>
+        <v>453797</v>
       </c>
       <c r="R50" t="n">
-        <v>6807871</v>
+        <v>6808117</v>
       </c>
       <c r="S50" t="n">
         <v>15</v>
@@ -5703,10 +5727,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>119591022</v>
+        <v>119591061</v>
       </c>
       <c r="B51" t="n">
-        <v>78263</v>
+        <v>78526</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -5719,21 +5743,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5743,10 +5767,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>453759</v>
+        <v>453756</v>
       </c>
       <c r="R51" t="n">
-        <v>6807967</v>
+        <v>6808003</v>
       </c>
       <c r="S51" t="n">
         <v>15</v>
@@ -5805,10 +5829,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>119591009</v>
+        <v>119591041</v>
       </c>
       <c r="B52" t="n">
-        <v>57310</v>
+        <v>78526</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -5821,39 +5845,34 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
-      <c r="M52" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P52" t="inlineStr">
         <is>
           <t>Rymån, Dlr</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>453815</v>
+        <v>453773</v>
       </c>
       <c r="R52" t="n">
-        <v>6808098</v>
+        <v>6807791</v>
       </c>
       <c r="S52" t="n">
         <v>15</v>
@@ -5886,11 +5905,6 @@
       <c r="AA52" t="inlineStr">
         <is>
           <t>2024-09-06</t>
-        </is>
-      </c>
-      <c r="AC52" t="inlineStr">
-        <is>
-          <t>Färska ringhack (gran)</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -5917,10 +5931,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>119590969</v>
+        <v>119591030</v>
       </c>
       <c r="B53" t="n">
-        <v>57310</v>
+        <v>90580</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -5933,39 +5947,34 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
-      <c r="M53" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P53" t="inlineStr">
         <is>
           <t>Rymån, Dlr</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>453847</v>
+        <v>453779</v>
       </c>
       <c r="R53" t="n">
-        <v>6807830</v>
+        <v>6807856</v>
       </c>
       <c r="S53" t="n">
         <v>15</v>
@@ -5998,11 +6007,6 @@
       <c r="AA53" t="inlineStr">
         <is>
           <t>2024-09-06</t>
-        </is>
-      </c>
-      <c r="AC53" t="inlineStr">
-        <is>
-          <t>Försett med naturvårdssnitsel</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6029,7 +6033,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>119591088</v>
+        <v>119591055</v>
       </c>
       <c r="B54" t="n">
         <v>78526</v>
@@ -6069,10 +6073,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>453778</v>
+        <v>453747</v>
       </c>
       <c r="R54" t="n">
-        <v>6808053</v>
+        <v>6807979</v>
       </c>
       <c r="S54" t="n">
         <v>15</v>
@@ -6099,12 +6103,12 @@
       </c>
       <c r="Y54" t="inlineStr">
         <is>
-          <t>2024-09-04</t>
+          <t>2024-09-06</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
         <is>
-          <t>2024-09-04</t>
+          <t>2024-09-06</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6131,10 +6135,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>119591091</v>
+        <v>119590976</v>
       </c>
       <c r="B55" t="n">
-        <v>78526</v>
+        <v>79144</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6147,21 +6151,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6171,10 +6175,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>453798</v>
+        <v>453836</v>
       </c>
       <c r="R55" t="n">
-        <v>6808108</v>
+        <v>6807943</v>
       </c>
       <c r="S55" t="n">
         <v>15</v>
@@ -6201,12 +6205,12 @@
       </c>
       <c r="Y55" t="inlineStr">
         <is>
-          <t>2024-09-04</t>
+          <t>2024-09-06</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
         <is>
-          <t>2024-09-04</t>
+          <t>2024-09-06</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6233,10 +6237,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>119591015</v>
+        <v>119591084</v>
       </c>
       <c r="B56" t="n">
-        <v>79635</v>
+        <v>78526</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6245,25 +6249,25 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6461</v>
+        <v>6425</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6273,10 +6277,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>453820</v>
+        <v>453835</v>
       </c>
       <c r="R56" t="n">
-        <v>6808064</v>
+        <v>6808031</v>
       </c>
       <c r="S56" t="n">
         <v>15</v>
@@ -6303,12 +6307,12 @@
       </c>
       <c r="Y56" t="inlineStr">
         <is>
-          <t>2024-09-06</t>
+          <t>2024-09-04</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
         <is>
-          <t>2024-09-06</t>
+          <t>2024-09-04</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6335,10 +6339,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>119591038</v>
+        <v>119591025</v>
       </c>
       <c r="B57" t="n">
-        <v>78526</v>
+        <v>93935</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6347,25 +6351,25 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6425</v>
+        <v>2387</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Källpraktmossa</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudobryum cinclidioides</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Huebener) T.J.Kop.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6375,10 +6379,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>453826</v>
+        <v>453851</v>
       </c>
       <c r="R57" t="n">
-        <v>6807750</v>
+        <v>6807838</v>
       </c>
       <c r="S57" t="n">
         <v>15</v>
@@ -6437,7 +6441,7 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>119591050</v>
+        <v>119591091</v>
       </c>
       <c r="B58" t="n">
         <v>78526</v>
@@ -6477,10 +6481,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>453782</v>
+        <v>453798</v>
       </c>
       <c r="R58" t="n">
-        <v>6807956</v>
+        <v>6808108</v>
       </c>
       <c r="S58" t="n">
         <v>15</v>
@@ -6507,12 +6511,12 @@
       </c>
       <c r="Y58" t="inlineStr">
         <is>
-          <t>2024-09-06</t>
+          <t>2024-09-04</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
         <is>
-          <t>2024-09-06</t>
+          <t>2024-09-04</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6539,7 +6543,7 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>119591085</v>
+        <v>119591054</v>
       </c>
       <c r="B59" t="n">
         <v>78526</v>
@@ -6579,10 +6583,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>453830</v>
+        <v>453738</v>
       </c>
       <c r="R59" t="n">
-        <v>6808029</v>
+        <v>6807973</v>
       </c>
       <c r="S59" t="n">
         <v>15</v>
@@ -6609,12 +6613,12 @@
       </c>
       <c r="Y59" t="inlineStr">
         <is>
-          <t>2024-09-04</t>
+          <t>2024-09-06</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
         <is>
-          <t>2024-09-04</t>
+          <t>2024-09-06</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6641,7 +6645,7 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>119591041</v>
+        <v>119591085</v>
       </c>
       <c r="B60" t="n">
         <v>78526</v>
@@ -6681,10 +6685,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>453773</v>
+        <v>453830</v>
       </c>
       <c r="R60" t="n">
-        <v>6807791</v>
+        <v>6808029</v>
       </c>
       <c r="S60" t="n">
         <v>15</v>
@@ -6711,12 +6715,12 @@
       </c>
       <c r="Y60" t="inlineStr">
         <is>
-          <t>2024-09-06</t>
+          <t>2024-09-04</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
         <is>
-          <t>2024-09-06</t>
+          <t>2024-09-04</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -6743,7 +6747,7 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>119591039</v>
+        <v>119591044</v>
       </c>
       <c r="B61" t="n">
         <v>78526</v>
@@ -6783,10 +6787,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>453790</v>
+        <v>453764</v>
       </c>
       <c r="R61" t="n">
-        <v>6807766</v>
+        <v>6807870</v>
       </c>
       <c r="S61" t="n">
         <v>15</v>
@@ -6845,10 +6849,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>119591040</v>
+        <v>119590982</v>
       </c>
       <c r="B62" t="n">
-        <v>78526</v>
+        <v>79144</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -6861,21 +6865,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6885,10 +6889,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>453808</v>
+        <v>453794</v>
       </c>
       <c r="R62" t="n">
-        <v>6807761</v>
+        <v>6807980</v>
       </c>
       <c r="S62" t="n">
         <v>15</v>
@@ -6947,10 +6951,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>119590977</v>
+        <v>119590998</v>
       </c>
       <c r="B63" t="n">
-        <v>79144</v>
+        <v>57463</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -6963,21 +6967,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6453</v>
+        <v>103021</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -6987,10 +6991,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>453807</v>
+        <v>453861</v>
       </c>
       <c r="R63" t="n">
-        <v>6807916</v>
+        <v>6808024</v>
       </c>
       <c r="S63" t="n">
         <v>15</v>
@@ -7049,10 +7053,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>119591066</v>
+        <v>119591026</v>
       </c>
       <c r="B64" t="n">
-        <v>78526</v>
+        <v>78262</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7065,21 +7069,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7089,10 +7093,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>453787</v>
+        <v>453770</v>
       </c>
       <c r="R64" t="n">
-        <v>6808020</v>
+        <v>6807987</v>
       </c>
       <c r="S64" t="n">
         <v>15</v>
@@ -7151,7 +7155,7 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>119591070</v>
+        <v>119591065</v>
       </c>
       <c r="B65" t="n">
         <v>78526</v>
@@ -7191,10 +7195,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>453759</v>
+        <v>453782</v>
       </c>
       <c r="R65" t="n">
-        <v>6808051</v>
+        <v>6807982</v>
       </c>
       <c r="S65" t="n">
         <v>15</v>
@@ -7253,7 +7257,7 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>119591068</v>
+        <v>119591036</v>
       </c>
       <c r="B66" t="n">
         <v>78526</v>
@@ -7293,10 +7297,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>453770</v>
+        <v>453849</v>
       </c>
       <c r="R66" t="n">
-        <v>6808029</v>
+        <v>6807844</v>
       </c>
       <c r="S66" t="n">
         <v>15</v>
@@ -7355,10 +7359,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>119590999</v>
+        <v>119590991</v>
       </c>
       <c r="B67" t="n">
-        <v>91463</v>
+        <v>57310</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -7371,34 +7375,39 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>4745</v>
+        <v>100109</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Tallriska</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Lactarius musteus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P67" t="inlineStr">
         <is>
           <t>Rymån, Dlr</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>453793</v>
+        <v>453887</v>
       </c>
       <c r="R67" t="n">
-        <v>6808029</v>
+        <v>6808050</v>
       </c>
       <c r="S67" t="n">
         <v>15</v>
@@ -7425,12 +7434,12 @@
       </c>
       <c r="Y67" t="inlineStr">
         <is>
-          <t>2024-09-04</t>
+          <t>2024-09-06</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
         <is>
-          <t>2024-09-04</t>
+          <t>2024-09-06</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7457,10 +7466,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>119591054</v>
+        <v>119591097</v>
       </c>
       <c r="B68" t="n">
-        <v>78526</v>
+        <v>57310</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -7473,34 +7482,39 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P68" t="inlineStr">
         <is>
           <t>Rymån, Dlr</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>453738</v>
+        <v>453849</v>
       </c>
       <c r="R68" t="n">
-        <v>6807973</v>
+        <v>6807844</v>
       </c>
       <c r="S68" t="n">
         <v>15</v>
@@ -7559,7 +7573,7 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>119591006</v>
+        <v>119591007</v>
       </c>
       <c r="B69" t="n">
         <v>57310</v>
@@ -7604,7 +7618,7 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>453796</v>
+        <v>453808</v>
       </c>
       <c r="R69" t="n">
         <v>6808114</v>
@@ -7671,10 +7685,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>119590998</v>
+        <v>119591062</v>
       </c>
       <c r="B70" t="n">
-        <v>57463</v>
+        <v>78526</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -7687,21 +7701,21 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7711,10 +7725,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>453861</v>
+        <v>453761</v>
       </c>
       <c r="R70" t="n">
-        <v>6808024</v>
+        <v>6808000</v>
       </c>
       <c r="S70" t="n">
         <v>15</v>
@@ -7773,10 +7787,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>119590996</v>
+        <v>119590981</v>
       </c>
       <c r="B71" t="n">
-        <v>57463</v>
+        <v>79144</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -7789,21 +7803,21 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>103021</v>
+        <v>6453</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -7813,10 +7827,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>453750</v>
+        <v>453770</v>
       </c>
       <c r="R71" t="n">
-        <v>6807861</v>
+        <v>6807987</v>
       </c>
       <c r="S71" t="n">
         <v>15</v>
@@ -7875,10 +7889,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>119591019</v>
+        <v>119591037</v>
       </c>
       <c r="B72" t="n">
-        <v>96865</v>
+        <v>78526</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -7887,47 +7901,38 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>221946</v>
+        <v>6425</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Mattlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Lycopodium clavatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I72" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J72" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
           <t>Rymån, Dlr</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>453836</v>
+        <v>453829</v>
       </c>
       <c r="R72" t="n">
-        <v>6807799</v>
+        <v>6807768</v>
       </c>
       <c r="S72" t="n">
         <v>15</v>
@@ -7986,7 +7991,7 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>119591064</v>
+        <v>119591034</v>
       </c>
       <c r="B73" t="n">
         <v>78526</v>
@@ -8026,10 +8031,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>453761</v>
+        <v>453825</v>
       </c>
       <c r="R73" t="n">
-        <v>6807996</v>
+        <v>6807960</v>
       </c>
       <c r="S73" t="n">
         <v>15</v>
@@ -8088,7 +8093,7 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>119591074</v>
+        <v>119591045</v>
       </c>
       <c r="B74" t="n">
         <v>78526</v>
@@ -8128,10 +8133,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>453796</v>
+        <v>453764</v>
       </c>
       <c r="R74" t="n">
-        <v>6808121</v>
+        <v>6807871</v>
       </c>
       <c r="S74" t="n">
         <v>15</v>
@@ -8190,10 +8195,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>119591056</v>
+        <v>119590979</v>
       </c>
       <c r="B75" t="n">
-        <v>78526</v>
+        <v>79144</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -8206,21 +8211,21 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8230,10 +8235,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>453742</v>
+        <v>453807</v>
       </c>
       <c r="R75" t="n">
-        <v>6807994</v>
+        <v>6807719</v>
       </c>
       <c r="S75" t="n">
         <v>15</v>
@@ -8292,10 +8297,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>119591101</v>
+        <v>119591046</v>
       </c>
       <c r="B76" t="n">
-        <v>5169</v>
+        <v>78526</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -8304,25 +8309,25 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>100526</v>
+        <v>6425</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8332,10 +8337,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>453849</v>
+        <v>453792</v>
       </c>
       <c r="R76" t="n">
-        <v>6807844</v>
+        <v>6807881</v>
       </c>
       <c r="S76" t="n">
         <v>15</v>
@@ -8394,10 +8399,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>119590981</v>
+        <v>119591039</v>
       </c>
       <c r="B77" t="n">
-        <v>79144</v>
+        <v>78526</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -8410,21 +8415,21 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8434,10 +8439,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>453770</v>
+        <v>453790</v>
       </c>
       <c r="R77" t="n">
-        <v>6807987</v>
+        <v>6807766</v>
       </c>
       <c r="S77" t="n">
         <v>15</v>
@@ -8496,10 +8501,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>119590983</v>
+        <v>119591068</v>
       </c>
       <c r="B78" t="n">
-        <v>79144</v>
+        <v>78526</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -8512,21 +8517,21 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8536,10 +8541,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>453762</v>
+        <v>453770</v>
       </c>
       <c r="R78" t="n">
-        <v>6808048</v>
+        <v>6808029</v>
       </c>
       <c r="S78" t="n">
         <v>15</v>
@@ -8598,10 +8603,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>119591097</v>
+        <v>119591051</v>
       </c>
       <c r="B79" t="n">
-        <v>57310</v>
+        <v>78526</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -8614,39 +8619,34 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
-      <c r="M79" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P79" t="inlineStr">
         <is>
           <t>Rymån, Dlr</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>453849</v>
+        <v>453755</v>
       </c>
       <c r="R79" t="n">
-        <v>6807844</v>
+        <v>6807941</v>
       </c>
       <c r="S79" t="n">
         <v>15</v>
@@ -8705,10 +8705,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>119591062</v>
+        <v>119590983</v>
       </c>
       <c r="B80" t="n">
-        <v>78526</v>
+        <v>79144</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -8721,21 +8721,21 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -8745,10 +8745,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>453761</v>
+        <v>453762</v>
       </c>
       <c r="R80" t="n">
-        <v>6808000</v>
+        <v>6808048</v>
       </c>
       <c r="S80" t="n">
         <v>15</v>
@@ -8807,10 +8807,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>119591046</v>
+        <v>119590969</v>
       </c>
       <c r="B81" t="n">
-        <v>78526</v>
+        <v>57310</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -8823,34 +8823,39 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
+      <c r="M81" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P81" t="inlineStr">
         <is>
           <t>Rymån, Dlr</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>453792</v>
+        <v>453847</v>
       </c>
       <c r="R81" t="n">
-        <v>6807881</v>
+        <v>6807830</v>
       </c>
       <c r="S81" t="n">
         <v>15</v>
@@ -8883,6 +8888,11 @@
       <c r="AA81" t="inlineStr">
         <is>
           <t>2024-09-06</t>
+        </is>
+      </c>
+      <c r="AC81" t="inlineStr">
+        <is>
+          <t>Försett med naturvårdssnitsel</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -8909,10 +8919,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>119591073</v>
+        <v>119590974</v>
       </c>
       <c r="B82" t="n">
-        <v>78526</v>
+        <v>95455</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -8925,21 +8935,21 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>6425</v>
+        <v>53</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -8949,10 +8959,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>453797</v>
+        <v>453852</v>
       </c>
       <c r="R82" t="n">
-        <v>6808117</v>
+        <v>6807959</v>
       </c>
       <c r="S82" t="n">
         <v>15</v>
@@ -9011,7 +9021,7 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>119591037</v>
+        <v>119591088</v>
       </c>
       <c r="B83" t="n">
         <v>78526</v>
@@ -9051,10 +9061,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>453829</v>
+        <v>453778</v>
       </c>
       <c r="R83" t="n">
-        <v>6807768</v>
+        <v>6808053</v>
       </c>
       <c r="S83" t="n">
         <v>15</v>
@@ -9081,12 +9091,12 @@
       </c>
       <c r="Y83" t="inlineStr">
         <is>
-          <t>2024-09-06</t>
+          <t>2024-09-04</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
         <is>
-          <t>2024-09-06</t>
+          <t>2024-09-04</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -9113,10 +9123,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>119591011</v>
+        <v>119591090</v>
       </c>
       <c r="B84" t="n">
-        <v>96862</v>
+        <v>78526</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -9125,25 +9135,25 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -9153,10 +9163,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>453903</v>
+        <v>453794</v>
       </c>
       <c r="R84" t="n">
-        <v>6807986</v>
+        <v>6808097</v>
       </c>
       <c r="S84" t="n">
         <v>15</v>
@@ -9183,12 +9193,12 @@
       </c>
       <c r="Y84" t="inlineStr">
         <is>
-          <t>2024-09-06</t>
+          <t>2024-09-04</t>
         </is>
       </c>
       <c r="AA84" t="inlineStr">
         <is>
-          <t>2024-09-06</t>
+          <t>2024-09-04</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -9215,7 +9225,7 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>119590985</v>
+        <v>119590987</v>
       </c>
       <c r="B85" t="n">
         <v>90562</v>
@@ -9255,10 +9265,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>453839</v>
+        <v>453772</v>
       </c>
       <c r="R85" t="n">
-        <v>6807828</v>
+        <v>6807796</v>
       </c>
       <c r="S85" t="n">
         <v>15</v>
@@ -9317,10 +9327,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>119591042</v>
+        <v>119590986</v>
       </c>
       <c r="B86" t="n">
-        <v>78526</v>
+        <v>90562</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -9333,21 +9343,21 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -9357,10 +9367,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>453788</v>
+        <v>453795</v>
       </c>
       <c r="R86" t="n">
-        <v>6807792</v>
+        <v>6807770</v>
       </c>
       <c r="S86" t="n">
         <v>15</v>
@@ -9419,10 +9429,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>119590980</v>
+        <v>119591075</v>
       </c>
       <c r="B87" t="n">
-        <v>79144</v>
+        <v>78526</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -9435,21 +9445,21 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -9459,10 +9469,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>453791</v>
+        <v>453809</v>
       </c>
       <c r="R87" t="n">
-        <v>6807707</v>
+        <v>6808107</v>
       </c>
       <c r="S87" t="n">
         <v>15</v>
@@ -9521,10 +9531,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>119591083</v>
+        <v>119590995</v>
       </c>
       <c r="B88" t="n">
-        <v>78526</v>
+        <v>103418</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
@@ -9533,25 +9543,25 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>6425</v>
+        <v>222412</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -9561,10 +9571,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>453848</v>
+        <v>453897</v>
       </c>
       <c r="R88" t="n">
-        <v>6808029</v>
+        <v>6808024</v>
       </c>
       <c r="S88" t="n">
         <v>15</v>
@@ -9623,10 +9633,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>119591034</v>
+        <v>119590999</v>
       </c>
       <c r="B89" t="n">
-        <v>78526</v>
+        <v>91463</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
@@ -9639,21 +9649,21 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>6425</v>
+        <v>4745</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallriska</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lactarius musteus</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -9663,10 +9673,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>453825</v>
+        <v>453793</v>
       </c>
       <c r="R89" t="n">
-        <v>6807960</v>
+        <v>6808029</v>
       </c>
       <c r="S89" t="n">
         <v>15</v>
@@ -9693,12 +9703,12 @@
       </c>
       <c r="Y89" t="inlineStr">
         <is>
-          <t>2024-09-06</t>
+          <t>2024-09-04</t>
         </is>
       </c>
       <c r="AA89" t="inlineStr">
         <is>
-          <t>2024-09-06</t>
+          <t>2024-09-04</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -9725,7 +9735,7 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>119591044</v>
+        <v>119591038</v>
       </c>
       <c r="B90" t="n">
         <v>78526</v>
@@ -9765,10 +9775,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>453764</v>
+        <v>453826</v>
       </c>
       <c r="R90" t="n">
-        <v>6807870</v>
+        <v>6807750</v>
       </c>
       <c r="S90" t="n">
         <v>15</v>
@@ -9827,7 +9837,7 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>119591096</v>
+        <v>119591060</v>
       </c>
       <c r="B91" t="n">
         <v>78526</v>
@@ -9867,10 +9877,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>453898</v>
+        <v>453748</v>
       </c>
       <c r="R91" t="n">
-        <v>6808089</v>
+        <v>6808003</v>
       </c>
       <c r="S91" t="n">
         <v>15</v>
@@ -9929,10 +9939,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>119591052</v>
+        <v>119591031</v>
       </c>
       <c r="B92" t="n">
-        <v>78526</v>
+        <v>90580</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
@@ -9945,21 +9955,21 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -9969,10 +9979,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>453755</v>
+        <v>453886</v>
       </c>
       <c r="R92" t="n">
-        <v>6807948</v>
+        <v>6808055</v>
       </c>
       <c r="S92" t="n">
         <v>15</v>
@@ -10031,10 +10041,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>119590995</v>
+        <v>119591015</v>
       </c>
       <c r="B93" t="n">
-        <v>103418</v>
+        <v>79635</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
@@ -10047,21 +10057,21 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>222412</v>
+        <v>6461</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -10071,10 +10081,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>453897</v>
+        <v>453820</v>
       </c>
       <c r="R93" t="n">
-        <v>6808024</v>
+        <v>6808064</v>
       </c>
       <c r="S93" t="n">
         <v>15</v>
@@ -10133,10 +10143,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>119591007</v>
+        <v>119591074</v>
       </c>
       <c r="B94" t="n">
-        <v>57310</v>
+        <v>78526</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>
@@ -10149,39 +10159,34 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
-      <c r="M94" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P94" t="inlineStr">
         <is>
           <t>Rymån, Dlr</t>
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>453808</v>
+        <v>453796</v>
       </c>
       <c r="R94" t="n">
-        <v>6808114</v>
+        <v>6808121</v>
       </c>
       <c r="S94" t="n">
         <v>15</v>
@@ -10214,11 +10219,6 @@
       <c r="AA94" t="inlineStr">
         <is>
           <t>2024-09-06</t>
-        </is>
-      </c>
-      <c r="AC94" t="inlineStr">
-        <is>
-          <t>Färska ringhack (gran)</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -10245,10 +10245,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>119591028</v>
+        <v>119590985</v>
       </c>
       <c r="B95" t="n">
-        <v>90580</v>
+        <v>90562</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
@@ -10261,21 +10261,21 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -10285,10 +10285,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>453791</v>
+        <v>453839</v>
       </c>
       <c r="R95" t="n">
-        <v>6807765</v>
+        <v>6807828</v>
       </c>
       <c r="S95" t="n">
         <v>15</v>
@@ -10321,11 +10321,6 @@
       <c r="AA95" t="inlineStr">
         <is>
           <t>2024-09-06</t>
-        </is>
-      </c>
-      <c r="AC95" t="inlineStr">
-        <is>
-          <t>Gamla fruktkroppar</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -10352,10 +10347,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>119591077</v>
+        <v>119590990</v>
       </c>
       <c r="B96" t="n">
-        <v>78526</v>
+        <v>57310</v>
       </c>
       <c r="C96" t="inlineStr">
         <is>
@@ -10368,34 +10363,39 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
+      <c r="M96" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P96" t="inlineStr">
         <is>
           <t>Rymån, Dlr</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>453815</v>
+        <v>453803</v>
       </c>
       <c r="R96" t="n">
-        <v>6808130</v>
+        <v>6807752</v>
       </c>
       <c r="S96" t="n">
         <v>15</v>
@@ -10454,7 +10454,7 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>119591053</v>
+        <v>119591043</v>
       </c>
       <c r="B97" t="n">
         <v>78526</v>
@@ -10494,10 +10494,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>453752</v>
+        <v>453774</v>
       </c>
       <c r="R97" t="n">
-        <v>6807968</v>
+        <v>6807849</v>
       </c>
       <c r="S97" t="n">
         <v>15</v>
@@ -10556,7 +10556,7 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>119591059</v>
+        <v>119591047</v>
       </c>
       <c r="B98" t="n">
         <v>78526</v>
@@ -10596,10 +10596,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>453737</v>
+        <v>453785</v>
       </c>
       <c r="R98" t="n">
-        <v>6808007</v>
+        <v>6807890</v>
       </c>
       <c r="S98" t="n">
         <v>15</v>
@@ -10658,10 +10658,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>119591031</v>
+        <v>119591086</v>
       </c>
       <c r="B99" t="n">
-        <v>90580</v>
+        <v>78526</v>
       </c>
       <c r="C99" t="inlineStr">
         <is>
@@ -10674,21 +10674,21 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
@@ -10698,10 +10698,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>453886</v>
+        <v>453820</v>
       </c>
       <c r="R99" t="n">
-        <v>6808055</v>
+        <v>6808020</v>
       </c>
       <c r="S99" t="n">
         <v>15</v>
@@ -10728,12 +10728,12 @@
       </c>
       <c r="Y99" t="inlineStr">
         <is>
-          <t>2024-09-06</t>
+          <t>2024-09-04</t>
         </is>
       </c>
       <c r="AA99" t="inlineStr">
         <is>
-          <t>2024-09-06</t>
+          <t>2024-09-04</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -10760,7 +10760,7 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>119591069</v>
+        <v>119591096</v>
       </c>
       <c r="B100" t="n">
         <v>78526</v>
@@ -10800,10 +10800,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>453756</v>
+        <v>453898</v>
       </c>
       <c r="R100" t="n">
-        <v>6808048</v>
+        <v>6808089</v>
       </c>
       <c r="S100" t="n">
         <v>15</v>
@@ -10862,10 +10862,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>119591032</v>
+        <v>119590977</v>
       </c>
       <c r="B101" t="n">
-        <v>78526</v>
+        <v>79144</v>
       </c>
       <c r="C101" t="inlineStr">
         <is>
@@ -10878,21 +10878,21 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
@@ -10902,10 +10902,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>453897</v>
+        <v>453807</v>
       </c>
       <c r="R101" t="n">
-        <v>6808009</v>
+        <v>6807916</v>
       </c>
       <c r="S101" t="n">
         <v>15</v>

--- a/artfynd/A 31144-2024 artfynd.xlsx
+++ b/artfynd/A 31144-2024 artfynd.xlsx
@@ -2321,10 +2321,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>119590997</v>
+        <v>119591089</v>
       </c>
       <c r="B18" t="n">
-        <v>57463</v>
+        <v>78526</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2337,21 +2337,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2361,10 +2361,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>453806</v>
+        <v>453780</v>
       </c>
       <c r="R18" t="n">
-        <v>6808118</v>
+        <v>6808055</v>
       </c>
       <c r="S18" t="n">
         <v>15</v>
@@ -2391,12 +2391,12 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2024-09-06</t>
+          <t>2024-09-04</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2024-09-06</t>
+          <t>2024-09-04</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2423,10 +2423,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>119591008</v>
+        <v>119591077</v>
       </c>
       <c r="B19" t="n">
-        <v>57310</v>
+        <v>78526</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2439,39 +2439,34 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Rymån, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>453821</v>
+        <v>453815</v>
       </c>
       <c r="R19" t="n">
-        <v>6808117</v>
+        <v>6808130</v>
       </c>
       <c r="S19" t="n">
         <v>15</v>
@@ -2504,11 +2499,6 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2024-09-06</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Färska ringhack (gran)</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2535,10 +2525,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>119591009</v>
+        <v>119591071</v>
       </c>
       <c r="B20" t="n">
-        <v>57310</v>
+        <v>78526</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2551,39 +2541,34 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Rymån, Dlr</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>453815</v>
+        <v>453788</v>
       </c>
       <c r="R20" t="n">
-        <v>6808098</v>
+        <v>6808086</v>
       </c>
       <c r="S20" t="n">
         <v>15</v>
@@ -2616,11 +2601,6 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2024-09-06</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Färska ringhack (gran)</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2647,10 +2627,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>119591089</v>
+        <v>119591008</v>
       </c>
       <c r="B21" t="n">
-        <v>78526</v>
+        <v>57310</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2663,34 +2643,39 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Rymån, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>453780</v>
+        <v>453821</v>
       </c>
       <c r="R21" t="n">
-        <v>6808055</v>
+        <v>6808117</v>
       </c>
       <c r="S21" t="n">
         <v>15</v>
@@ -2717,12 +2702,17 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2024-09-04</t>
+          <t>2024-09-06</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2024-09-04</t>
+          <t>2024-09-06</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Färska ringhack (gran)</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2749,10 +2739,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>119591077</v>
+        <v>119591009</v>
       </c>
       <c r="B22" t="n">
-        <v>78526</v>
+        <v>57310</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2765,24 +2755,29 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Rymån, Dlr</t>
@@ -2792,7 +2787,7 @@
         <v>453815</v>
       </c>
       <c r="R22" t="n">
-        <v>6808130</v>
+        <v>6808098</v>
       </c>
       <c r="S22" t="n">
         <v>15</v>
@@ -2825,6 +2820,11 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2024-09-06</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Färska ringhack (gran)</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2851,10 +2851,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>119591071</v>
+        <v>119591023</v>
       </c>
       <c r="B23" t="n">
-        <v>78526</v>
+        <v>78263</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2867,21 +2867,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2891,10 +2891,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>453788</v>
+        <v>453770</v>
       </c>
       <c r="R23" t="n">
-        <v>6808086</v>
+        <v>6807984</v>
       </c>
       <c r="S23" t="n">
         <v>15</v>
@@ -2953,10 +2953,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>119591023</v>
+        <v>119590997</v>
       </c>
       <c r="B24" t="n">
-        <v>78263</v>
+        <v>57463</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -2969,21 +2969,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>228912</v>
+        <v>103021</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2993,10 +2993,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>453770</v>
+        <v>453806</v>
       </c>
       <c r="R24" t="n">
-        <v>6807984</v>
+        <v>6808118</v>
       </c>
       <c r="S24" t="n">
         <v>15</v>
@@ -4901,10 +4901,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>119591082</v>
+        <v>119591006</v>
       </c>
       <c r="B43" t="n">
-        <v>78526</v>
+        <v>57310</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -4917,34 +4917,39 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P43" t="inlineStr">
         <is>
           <t>Rymån, Dlr</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>453850</v>
+        <v>453796</v>
       </c>
       <c r="R43" t="n">
-        <v>6808037</v>
+        <v>6808114</v>
       </c>
       <c r="S43" t="n">
         <v>15</v>
@@ -4977,6 +4982,11 @@
       <c r="AA43" t="inlineStr">
         <is>
           <t>2024-09-06</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>Färska ringhack (gran)</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5003,7 +5013,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>119591032</v>
+        <v>119591087</v>
       </c>
       <c r="B44" t="n">
         <v>78526</v>
@@ -5043,10 +5053,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>453897</v>
+        <v>453803</v>
       </c>
       <c r="R44" t="n">
-        <v>6808009</v>
+        <v>6808020</v>
       </c>
       <c r="S44" t="n">
         <v>15</v>
@@ -5073,12 +5083,12 @@
       </c>
       <c r="Y44" t="inlineStr">
         <is>
-          <t>2024-09-06</t>
+          <t>2024-09-04</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>2024-09-06</t>
+          <t>2024-09-04</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5105,7 +5115,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>119591087</v>
+        <v>119591082</v>
       </c>
       <c r="B45" t="n">
         <v>78526</v>
@@ -5145,10 +5155,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>453803</v>
+        <v>453850</v>
       </c>
       <c r="R45" t="n">
-        <v>6808020</v>
+        <v>6808037</v>
       </c>
       <c r="S45" t="n">
         <v>15</v>
@@ -5175,12 +5185,12 @@
       </c>
       <c r="Y45" t="inlineStr">
         <is>
-          <t>2024-09-04</t>
+          <t>2024-09-06</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>2024-09-04</t>
+          <t>2024-09-06</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5207,10 +5217,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>119591101</v>
+        <v>119591032</v>
       </c>
       <c r="B46" t="n">
-        <v>5169</v>
+        <v>78526</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5219,25 +5229,25 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>100526</v>
+        <v>6425</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5247,10 +5257,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>453849</v>
+        <v>453897</v>
       </c>
       <c r="R46" t="n">
-        <v>6807844</v>
+        <v>6808009</v>
       </c>
       <c r="S46" t="n">
         <v>15</v>
@@ -5309,10 +5319,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>119591006</v>
+        <v>119591101</v>
       </c>
       <c r="B47" t="n">
-        <v>57310</v>
+        <v>5169</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5321,43 +5331,38 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>100109</v>
+        <v>100526</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
-      <c r="M47" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P47" t="inlineStr">
         <is>
           <t>Rymån, Dlr</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>453796</v>
+        <v>453849</v>
       </c>
       <c r="R47" t="n">
-        <v>6808114</v>
+        <v>6807844</v>
       </c>
       <c r="S47" t="n">
         <v>15</v>
@@ -5390,11 +5395,6 @@
       <c r="AA47" t="inlineStr">
         <is>
           <t>2024-09-06</t>
-        </is>
-      </c>
-      <c r="AC47" t="inlineStr">
-        <is>
-          <t>Färska ringhack (gran)</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5523,10 +5523,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>119590972</v>
+        <v>119591061</v>
       </c>
       <c r="B49" t="n">
-        <v>74638</v>
+        <v>78526</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5539,21 +5539,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5563,10 +5563,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>453874</v>
+        <v>453756</v>
       </c>
       <c r="R49" t="n">
-        <v>6808094</v>
+        <v>6808003</v>
       </c>
       <c r="S49" t="n">
         <v>15</v>
@@ -5625,7 +5625,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>119591073</v>
+        <v>119591041</v>
       </c>
       <c r="B50" t="n">
         <v>78526</v>
@@ -5665,10 +5665,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>453797</v>
+        <v>453773</v>
       </c>
       <c r="R50" t="n">
-        <v>6808117</v>
+        <v>6807791</v>
       </c>
       <c r="S50" t="n">
         <v>15</v>
@@ -5727,10 +5727,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>119591061</v>
+        <v>119590972</v>
       </c>
       <c r="B51" t="n">
-        <v>78526</v>
+        <v>74638</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -5743,21 +5743,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5767,10 +5767,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>453756</v>
+        <v>453874</v>
       </c>
       <c r="R51" t="n">
-        <v>6808003</v>
+        <v>6808094</v>
       </c>
       <c r="S51" t="n">
         <v>15</v>
@@ -5829,7 +5829,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>119591041</v>
+        <v>119591073</v>
       </c>
       <c r="B52" t="n">
         <v>78526</v>
@@ -5869,10 +5869,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>453773</v>
+        <v>453797</v>
       </c>
       <c r="R52" t="n">
-        <v>6807791</v>
+        <v>6808117</v>
       </c>
       <c r="S52" t="n">
         <v>15</v>
@@ -6339,10 +6339,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>119591025</v>
+        <v>119590998</v>
       </c>
       <c r="B57" t="n">
-        <v>93935</v>
+        <v>57463</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6351,25 +6351,25 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>2387</v>
+        <v>103021</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Källpraktmossa</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Pseudobryum cinclidioides</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Huebener) T.J.Kop.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6379,10 +6379,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>453851</v>
+        <v>453861</v>
       </c>
       <c r="R57" t="n">
-        <v>6807838</v>
+        <v>6808024</v>
       </c>
       <c r="S57" t="n">
         <v>15</v>
@@ -6441,10 +6441,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>119591091</v>
+        <v>119591025</v>
       </c>
       <c r="B58" t="n">
-        <v>78526</v>
+        <v>93935</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6453,25 +6453,25 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6425</v>
+        <v>2387</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Källpraktmossa</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudobryum cinclidioides</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Huebener) T.J.Kop.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6481,10 +6481,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>453798</v>
+        <v>453851</v>
       </c>
       <c r="R58" t="n">
-        <v>6808108</v>
+        <v>6807838</v>
       </c>
       <c r="S58" t="n">
         <v>15</v>
@@ -6511,12 +6511,12 @@
       </c>
       <c r="Y58" t="inlineStr">
         <is>
-          <t>2024-09-04</t>
+          <t>2024-09-06</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
         <is>
-          <t>2024-09-04</t>
+          <t>2024-09-06</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6543,7 +6543,7 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>119591054</v>
+        <v>119591091</v>
       </c>
       <c r="B59" t="n">
         <v>78526</v>
@@ -6583,10 +6583,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>453738</v>
+        <v>453798</v>
       </c>
       <c r="R59" t="n">
-        <v>6807973</v>
+        <v>6808108</v>
       </c>
       <c r="S59" t="n">
         <v>15</v>
@@ -6613,12 +6613,12 @@
       </c>
       <c r="Y59" t="inlineStr">
         <is>
-          <t>2024-09-06</t>
+          <t>2024-09-04</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
         <is>
-          <t>2024-09-06</t>
+          <t>2024-09-04</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6645,7 +6645,7 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>119591085</v>
+        <v>119591054</v>
       </c>
       <c r="B60" t="n">
         <v>78526</v>
@@ -6685,10 +6685,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>453830</v>
+        <v>453738</v>
       </c>
       <c r="R60" t="n">
-        <v>6808029</v>
+        <v>6807973</v>
       </c>
       <c r="S60" t="n">
         <v>15</v>
@@ -6715,12 +6715,12 @@
       </c>
       <c r="Y60" t="inlineStr">
         <is>
-          <t>2024-09-04</t>
+          <t>2024-09-06</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
         <is>
-          <t>2024-09-04</t>
+          <t>2024-09-06</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -6747,7 +6747,7 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>119591044</v>
+        <v>119591085</v>
       </c>
       <c r="B61" t="n">
         <v>78526</v>
@@ -6787,10 +6787,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>453764</v>
+        <v>453830</v>
       </c>
       <c r="R61" t="n">
-        <v>6807870</v>
+        <v>6808029</v>
       </c>
       <c r="S61" t="n">
         <v>15</v>
@@ -6817,12 +6817,12 @@
       </c>
       <c r="Y61" t="inlineStr">
         <is>
-          <t>2024-09-06</t>
+          <t>2024-09-04</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
         <is>
-          <t>2024-09-06</t>
+          <t>2024-09-04</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -6849,10 +6849,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>119590982</v>
+        <v>119591044</v>
       </c>
       <c r="B62" t="n">
-        <v>79144</v>
+        <v>78526</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -6865,21 +6865,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6889,10 +6889,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>453794</v>
+        <v>453764</v>
       </c>
       <c r="R62" t="n">
-        <v>6807980</v>
+        <v>6807870</v>
       </c>
       <c r="S62" t="n">
         <v>15</v>
@@ -6951,10 +6951,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>119590998</v>
+        <v>119590982</v>
       </c>
       <c r="B63" t="n">
-        <v>57463</v>
+        <v>79144</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -6967,21 +6967,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>103021</v>
+        <v>6453</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -6991,10 +6991,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>453861</v>
+        <v>453794</v>
       </c>
       <c r="R63" t="n">
-        <v>6808024</v>
+        <v>6807980</v>
       </c>
       <c r="S63" t="n">
         <v>15</v>
@@ -8195,10 +8195,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>119590979</v>
+        <v>119591046</v>
       </c>
       <c r="B75" t="n">
-        <v>79144</v>
+        <v>78526</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -8211,21 +8211,21 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8235,10 +8235,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>453807</v>
+        <v>453792</v>
       </c>
       <c r="R75" t="n">
-        <v>6807719</v>
+        <v>6807881</v>
       </c>
       <c r="S75" t="n">
         <v>15</v>
@@ -8297,7 +8297,7 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>119591046</v>
+        <v>119591039</v>
       </c>
       <c r="B76" t="n">
         <v>78526</v>
@@ -8337,10 +8337,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>453792</v>
+        <v>453790</v>
       </c>
       <c r="R76" t="n">
-        <v>6807881</v>
+        <v>6807766</v>
       </c>
       <c r="S76" t="n">
         <v>15</v>
@@ -8399,7 +8399,7 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>119591039</v>
+        <v>119591068</v>
       </c>
       <c r="B77" t="n">
         <v>78526</v>
@@ -8439,10 +8439,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>453790</v>
+        <v>453770</v>
       </c>
       <c r="R77" t="n">
-        <v>6807766</v>
+        <v>6808029</v>
       </c>
       <c r="S77" t="n">
         <v>15</v>
@@ -8501,7 +8501,7 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>119591068</v>
+        <v>119591051</v>
       </c>
       <c r="B78" t="n">
         <v>78526</v>
@@ -8541,10 +8541,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>453770</v>
+        <v>453755</v>
       </c>
       <c r="R78" t="n">
-        <v>6808029</v>
+        <v>6807941</v>
       </c>
       <c r="S78" t="n">
         <v>15</v>
@@ -8603,10 +8603,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>119591051</v>
+        <v>119590983</v>
       </c>
       <c r="B79" t="n">
-        <v>78526</v>
+        <v>79144</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -8619,21 +8619,21 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8643,10 +8643,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>453755</v>
+        <v>453762</v>
       </c>
       <c r="R79" t="n">
-        <v>6807941</v>
+        <v>6808048</v>
       </c>
       <c r="S79" t="n">
         <v>15</v>
@@ -8705,7 +8705,7 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>119590983</v>
+        <v>119590979</v>
       </c>
       <c r="B80" t="n">
         <v>79144</v>
@@ -8745,10 +8745,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>453762</v>
+        <v>453807</v>
       </c>
       <c r="R80" t="n">
-        <v>6808048</v>
+        <v>6807719</v>
       </c>
       <c r="S80" t="n">
         <v>15</v>
@@ -9735,10 +9735,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>119591038</v>
+        <v>119591015</v>
       </c>
       <c r="B90" t="n">
-        <v>78526</v>
+        <v>79635</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
@@ -9747,25 +9747,25 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>6425</v>
+        <v>6461</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -9775,10 +9775,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>453826</v>
+        <v>453820</v>
       </c>
       <c r="R90" t="n">
-        <v>6807750</v>
+        <v>6808064</v>
       </c>
       <c r="S90" t="n">
         <v>15</v>
@@ -9837,10 +9837,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>119591060</v>
+        <v>119591031</v>
       </c>
       <c r="B91" t="n">
-        <v>78526</v>
+        <v>90580</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
@@ -9853,21 +9853,21 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -9877,10 +9877,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>453748</v>
+        <v>453886</v>
       </c>
       <c r="R91" t="n">
-        <v>6808003</v>
+        <v>6808055</v>
       </c>
       <c r="S91" t="n">
         <v>15</v>
@@ -9939,10 +9939,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>119591031</v>
+        <v>119591038</v>
       </c>
       <c r="B92" t="n">
-        <v>90580</v>
+        <v>78526</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
@@ -9955,21 +9955,21 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -9979,10 +9979,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>453886</v>
+        <v>453826</v>
       </c>
       <c r="R92" t="n">
-        <v>6808055</v>
+        <v>6807750</v>
       </c>
       <c r="S92" t="n">
         <v>15</v>
@@ -10041,10 +10041,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>119591015</v>
+        <v>119591060</v>
       </c>
       <c r="B93" t="n">
-        <v>79635</v>
+        <v>78526</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
@@ -10053,25 +10053,25 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>6461</v>
+        <v>6425</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -10081,10 +10081,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>453820</v>
+        <v>453748</v>
       </c>
       <c r="R93" t="n">
-        <v>6808064</v>
+        <v>6808003</v>
       </c>
       <c r="S93" t="n">
         <v>15</v>
@@ -10245,10 +10245,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>119590985</v>
+        <v>119590990</v>
       </c>
       <c r="B95" t="n">
-        <v>90562</v>
+        <v>57310</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
@@ -10261,34 +10261,39 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
+      <c r="M95" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P95" t="inlineStr">
         <is>
           <t>Rymån, Dlr</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>453839</v>
+        <v>453803</v>
       </c>
       <c r="R95" t="n">
-        <v>6807828</v>
+        <v>6807752</v>
       </c>
       <c r="S95" t="n">
         <v>15</v>
@@ -10347,10 +10352,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>119590990</v>
+        <v>119590985</v>
       </c>
       <c r="B96" t="n">
-        <v>57310</v>
+        <v>90562</v>
       </c>
       <c r="C96" t="inlineStr">
         <is>
@@ -10363,39 +10368,34 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
-      <c r="M96" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P96" t="inlineStr">
         <is>
           <t>Rymån, Dlr</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>453803</v>
+        <v>453839</v>
       </c>
       <c r="R96" t="n">
-        <v>6807752</v>
+        <v>6807828</v>
       </c>
       <c r="S96" t="n">
         <v>15</v>

--- a/artfynd/A 31144-2024 artfynd.xlsx
+++ b/artfynd/A 31144-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119591048</v>
+        <v>119590985</v>
       </c>
       <c r="B2" t="n">
-        <v>78526</v>
+        <v>90562</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>453788</v>
+        <v>453839</v>
       </c>
       <c r="R2" t="n">
-        <v>6807903</v>
+        <v>6807828</v>
       </c>
       <c r="S2" t="n">
         <v>15</v>
@@ -777,7 +777,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119591058</v>
+        <v>119591072</v>
       </c>
       <c r="B3" t="n">
         <v>78526</v>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>453734</v>
+        <v>453773</v>
       </c>
       <c r="R3" t="n">
-        <v>6808007</v>
+        <v>6808107</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -879,7 +879,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119591040</v>
+        <v>119591049</v>
       </c>
       <c r="B4" t="n">
         <v>78526</v>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>453808</v>
+        <v>453796</v>
       </c>
       <c r="R4" t="n">
-        <v>6807761</v>
+        <v>6807942</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -981,7 +981,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119591052</v>
+        <v>119591044</v>
       </c>
       <c r="B5" t="n">
         <v>78526</v>
@@ -1021,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>453755</v>
+        <v>453764</v>
       </c>
       <c r="R5" t="n">
-        <v>6807948</v>
+        <v>6807870</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1083,7 +1083,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119591069</v>
+        <v>119591041</v>
       </c>
       <c r="B6" t="n">
         <v>78526</v>
@@ -1123,10 +1123,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>453756</v>
+        <v>453773</v>
       </c>
       <c r="R6" t="n">
-        <v>6808048</v>
+        <v>6807791</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1185,7 +1185,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119591064</v>
+        <v>119591045</v>
       </c>
       <c r="B7" t="n">
         <v>78526</v>
@@ -1225,10 +1225,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>453761</v>
+        <v>453764</v>
       </c>
       <c r="R7" t="n">
-        <v>6807996</v>
+        <v>6807871</v>
       </c>
       <c r="S7" t="n">
         <v>15</v>
@@ -1287,10 +1287,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119591019</v>
+        <v>119591057</v>
       </c>
       <c r="B8" t="n">
-        <v>96865</v>
+        <v>78526</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1299,47 +1299,38 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>221946</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Mattlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lycopodium clavatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Rymån, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>453836</v>
+        <v>453736</v>
       </c>
       <c r="R8" t="n">
-        <v>6807799</v>
+        <v>6808004</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1398,10 +1389,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>119590975</v>
+        <v>119591028</v>
       </c>
       <c r="B9" t="n">
-        <v>79144</v>
+        <v>90580</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1414,21 +1405,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6453</v>
+        <v>5432</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1438,10 +1429,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>453828</v>
+        <v>453791</v>
       </c>
       <c r="R9" t="n">
-        <v>6807944</v>
+        <v>6807765</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1474,6 +1465,11 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2024-09-06</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Gamla fruktkroppar</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1500,7 +1496,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>119591050</v>
+        <v>119591067</v>
       </c>
       <c r="B10" t="n">
         <v>78526</v>
@@ -1540,10 +1536,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>453782</v>
+        <v>453775</v>
       </c>
       <c r="R10" t="n">
-        <v>6807956</v>
+        <v>6808032</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>
@@ -1602,10 +1598,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>119591042</v>
+        <v>119590979</v>
       </c>
       <c r="B11" t="n">
-        <v>78526</v>
+        <v>79144</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1618,21 +1614,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1642,10 +1638,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>453788</v>
+        <v>453807</v>
       </c>
       <c r="R11" t="n">
-        <v>6807792</v>
+        <v>6807719</v>
       </c>
       <c r="S11" t="n">
         <v>15</v>
@@ -1704,10 +1700,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>119591049</v>
+        <v>119590977</v>
       </c>
       <c r="B12" t="n">
-        <v>78526</v>
+        <v>79144</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1720,21 +1716,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1744,10 +1740,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>453796</v>
+        <v>453807</v>
       </c>
       <c r="R12" t="n">
-        <v>6807942</v>
+        <v>6807916</v>
       </c>
       <c r="S12" t="n">
         <v>15</v>
@@ -1806,10 +1802,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>119591011</v>
+        <v>119590986</v>
       </c>
       <c r="B13" t="n">
-        <v>96862</v>
+        <v>90562</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1818,25 +1814,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>221945</v>
+        <v>1202</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1846,10 +1842,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>453903</v>
+        <v>453795</v>
       </c>
       <c r="R13" t="n">
-        <v>6807986</v>
+        <v>6807770</v>
       </c>
       <c r="S13" t="n">
         <v>15</v>
@@ -1908,10 +1904,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>119590980</v>
+        <v>119591033</v>
       </c>
       <c r="B14" t="n">
-        <v>79144</v>
+        <v>78526</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1924,21 +1920,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1948,10 +1944,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>453791</v>
+        <v>453835</v>
       </c>
       <c r="R14" t="n">
-        <v>6807707</v>
+        <v>6807974</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -2010,7 +2006,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>119591028</v>
+        <v>119591029</v>
       </c>
       <c r="B15" t="n">
         <v>90580</v>
@@ -2050,10 +2046,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>453791</v>
+        <v>453861</v>
       </c>
       <c r="R15" t="n">
-        <v>6807765</v>
+        <v>6807970</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2086,11 +2082,6 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2024-09-06</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Gamla fruktkroppar</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2117,7 +2108,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>119591067</v>
+        <v>119591077</v>
       </c>
       <c r="B16" t="n">
         <v>78526</v>
@@ -2157,10 +2148,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>453775</v>
+        <v>453815</v>
       </c>
       <c r="R16" t="n">
-        <v>6808032</v>
+        <v>6808130</v>
       </c>
       <c r="S16" t="n">
         <v>15</v>
@@ -2219,7 +2210,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>119591035</v>
+        <v>119591051</v>
       </c>
       <c r="B17" t="n">
         <v>78526</v>
@@ -2259,10 +2250,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>453808</v>
+        <v>453755</v>
       </c>
       <c r="R17" t="n">
-        <v>6807890</v>
+        <v>6807941</v>
       </c>
       <c r="S17" t="n">
         <v>15</v>
@@ -2321,10 +2312,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>119591089</v>
+        <v>119590994</v>
       </c>
       <c r="B18" t="n">
-        <v>78526</v>
+        <v>103418</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2333,25 +2324,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>222412</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2361,10 +2352,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>453780</v>
+        <v>453893</v>
       </c>
       <c r="R18" t="n">
-        <v>6808055</v>
+        <v>6808027</v>
       </c>
       <c r="S18" t="n">
         <v>15</v>
@@ -2391,12 +2382,12 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2024-09-04</t>
+          <t>2024-09-06</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2024-09-04</t>
+          <t>2024-09-06</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2423,10 +2414,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>119591077</v>
+        <v>119590995</v>
       </c>
       <c r="B19" t="n">
-        <v>78526</v>
+        <v>103418</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2435,25 +2426,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>222412</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2463,10 +2454,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>453815</v>
+        <v>453897</v>
       </c>
       <c r="R19" t="n">
-        <v>6808130</v>
+        <v>6808024</v>
       </c>
       <c r="S19" t="n">
         <v>15</v>
@@ -2525,7 +2516,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>119591071</v>
+        <v>119591060</v>
       </c>
       <c r="B20" t="n">
         <v>78526</v>
@@ -2565,10 +2556,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>453788</v>
+        <v>453748</v>
       </c>
       <c r="R20" t="n">
-        <v>6808086</v>
+        <v>6808003</v>
       </c>
       <c r="S20" t="n">
         <v>15</v>
@@ -2627,10 +2618,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>119591008</v>
+        <v>119591048</v>
       </c>
       <c r="B21" t="n">
-        <v>57310</v>
+        <v>78526</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2643,39 +2634,34 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Rymån, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>453821</v>
+        <v>453788</v>
       </c>
       <c r="R21" t="n">
-        <v>6808117</v>
+        <v>6807903</v>
       </c>
       <c r="S21" t="n">
         <v>15</v>
@@ -2708,11 +2694,6 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2024-09-06</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Färska ringhack (gran)</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2739,10 +2720,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>119591009</v>
+        <v>119591015</v>
       </c>
       <c r="B22" t="n">
-        <v>57310</v>
+        <v>79635</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2751,43 +2732,38 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100109</v>
+        <v>6461</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Rymån, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>453815</v>
+        <v>453820</v>
       </c>
       <c r="R22" t="n">
-        <v>6808098</v>
+        <v>6808064</v>
       </c>
       <c r="S22" t="n">
         <v>15</v>
@@ -2820,11 +2796,6 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2024-09-06</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Färska ringhack (gran)</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2851,10 +2822,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>119591023</v>
+        <v>119590990</v>
       </c>
       <c r="B23" t="n">
-        <v>78263</v>
+        <v>57310</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2867,34 +2838,39 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>228912</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Rymån, Dlr</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>453770</v>
+        <v>453803</v>
       </c>
       <c r="R23" t="n">
-        <v>6807984</v>
+        <v>6807752</v>
       </c>
       <c r="S23" t="n">
         <v>15</v>
@@ -2953,10 +2929,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>119590997</v>
+        <v>119591007</v>
       </c>
       <c r="B24" t="n">
-        <v>57463</v>
+        <v>57310</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -2969,34 +2945,39 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Rymån, Dlr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>453806</v>
+        <v>453808</v>
       </c>
       <c r="R24" t="n">
-        <v>6808118</v>
+        <v>6808114</v>
       </c>
       <c r="S24" t="n">
         <v>15</v>
@@ -3029,6 +3010,11 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2024-09-06</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Färska ringhack (gran)</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3055,10 +3041,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>119591072</v>
+        <v>119591026</v>
       </c>
       <c r="B25" t="n">
-        <v>78526</v>
+        <v>78262</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3071,21 +3057,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3095,10 +3081,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>453773</v>
+        <v>453770</v>
       </c>
       <c r="R25" t="n">
-        <v>6808107</v>
+        <v>6807987</v>
       </c>
       <c r="S25" t="n">
         <v>15</v>
@@ -3157,7 +3143,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>119591083</v>
+        <v>119591080</v>
       </c>
       <c r="B26" t="n">
         <v>78526</v>
@@ -3197,10 +3183,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>453848</v>
+        <v>453829</v>
       </c>
       <c r="R26" t="n">
-        <v>6808029</v>
+        <v>6808069</v>
       </c>
       <c r="S26" t="n">
         <v>15</v>
@@ -3259,7 +3245,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>119591057</v>
+        <v>119591047</v>
       </c>
       <c r="B27" t="n">
         <v>78526</v>
@@ -3299,10 +3285,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>453736</v>
+        <v>453785</v>
       </c>
       <c r="R27" t="n">
-        <v>6808004</v>
+        <v>6807890</v>
       </c>
       <c r="S27" t="n">
         <v>15</v>
@@ -3361,10 +3347,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>119591022</v>
+        <v>119591037</v>
       </c>
       <c r="B28" t="n">
-        <v>78263</v>
+        <v>78526</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3377,21 +3363,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3401,10 +3387,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>453759</v>
+        <v>453829</v>
       </c>
       <c r="R28" t="n">
-        <v>6807967</v>
+        <v>6807768</v>
       </c>
       <c r="S28" t="n">
         <v>15</v>
@@ -3463,10 +3449,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>119591012</v>
+        <v>119591074</v>
       </c>
       <c r="B29" t="n">
-        <v>96862</v>
+        <v>78526</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3475,25 +3461,25 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3503,10 +3489,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>453875</v>
+        <v>453796</v>
       </c>
       <c r="R29" t="n">
-        <v>6808094</v>
+        <v>6808121</v>
       </c>
       <c r="S29" t="n">
         <v>15</v>
@@ -3565,10 +3551,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>119591004</v>
+        <v>119591035</v>
       </c>
       <c r="B30" t="n">
-        <v>91884</v>
+        <v>78526</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3581,21 +3567,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>5449</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3605,10 +3591,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>453785</v>
+        <v>453808</v>
       </c>
       <c r="R30" t="n">
-        <v>6808062</v>
+        <v>6807890</v>
       </c>
       <c r="S30" t="n">
         <v>15</v>
@@ -3667,10 +3653,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>119591053</v>
+        <v>119590982</v>
       </c>
       <c r="B31" t="n">
-        <v>78526</v>
+        <v>79144</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3683,21 +3669,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3707,10 +3693,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>453752</v>
+        <v>453794</v>
       </c>
       <c r="R31" t="n">
-        <v>6807968</v>
+        <v>6807980</v>
       </c>
       <c r="S31" t="n">
         <v>15</v>
@@ -3769,7 +3755,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>119591076</v>
+        <v>119591065</v>
       </c>
       <c r="B32" t="n">
         <v>78526</v>
@@ -3809,10 +3795,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>453811</v>
+        <v>453782</v>
       </c>
       <c r="R32" t="n">
-        <v>6808106</v>
+        <v>6807982</v>
       </c>
       <c r="S32" t="n">
         <v>15</v>
@@ -3871,7 +3857,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>119591080</v>
+        <v>119591068</v>
       </c>
       <c r="B33" t="n">
         <v>78526</v>
@@ -3911,10 +3897,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>453829</v>
+        <v>453770</v>
       </c>
       <c r="R33" t="n">
-        <v>6808069</v>
+        <v>6808029</v>
       </c>
       <c r="S33" t="n">
         <v>15</v>
@@ -3973,10 +3959,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>119591070</v>
+        <v>119591097</v>
       </c>
       <c r="B34" t="n">
-        <v>78526</v>
+        <v>57310</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -3989,34 +3975,39 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P34" t="inlineStr">
         <is>
           <t>Rymån, Dlr</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>453759</v>
+        <v>453849</v>
       </c>
       <c r="R34" t="n">
-        <v>6808051</v>
+        <v>6807844</v>
       </c>
       <c r="S34" t="n">
         <v>15</v>
@@ -4075,7 +4066,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>119591033</v>
+        <v>119591073</v>
       </c>
       <c r="B35" t="n">
         <v>78526</v>
@@ -4115,10 +4106,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>453835</v>
+        <v>453797</v>
       </c>
       <c r="R35" t="n">
-        <v>6807974</v>
+        <v>6808117</v>
       </c>
       <c r="S35" t="n">
         <v>15</v>
@@ -4177,10 +4168,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>119590978</v>
+        <v>119591084</v>
       </c>
       <c r="B36" t="n">
-        <v>79144</v>
+        <v>78526</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4193,21 +4184,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4217,10 +4208,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>453823</v>
+        <v>453835</v>
       </c>
       <c r="R36" t="n">
-        <v>6807778</v>
+        <v>6808031</v>
       </c>
       <c r="S36" t="n">
         <v>15</v>
@@ -4247,12 +4238,12 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2024-09-06</t>
+          <t>2024-09-04</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2024-09-06</t>
+          <t>2024-09-04</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4279,10 +4270,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>119591010</v>
+        <v>119591039</v>
       </c>
       <c r="B37" t="n">
-        <v>57310</v>
+        <v>78526</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4295,39 +4286,34 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P37" t="inlineStr">
         <is>
           <t>Rymån, Dlr</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>453805</v>
+        <v>453790</v>
       </c>
       <c r="R37" t="n">
-        <v>6808118</v>
+        <v>6807766</v>
       </c>
       <c r="S37" t="n">
         <v>15</v>
@@ -4354,17 +4340,12 @@
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>2024-09-04</t>
+          <t>2024-09-06</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2024-09-04</t>
-        </is>
-      </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>Färska ringhack (gran)</t>
+          <t>2024-09-06</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4391,10 +4372,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>119590994</v>
+        <v>119591096</v>
       </c>
       <c r="B38" t="n">
-        <v>103418</v>
+        <v>78526</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4403,25 +4384,25 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>222412</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4431,10 +4412,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>453893</v>
+        <v>453898</v>
       </c>
       <c r="R38" t="n">
-        <v>6808027</v>
+        <v>6808089</v>
       </c>
       <c r="S38" t="n">
         <v>15</v>
@@ -4493,10 +4474,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>119591056</v>
+        <v>119591101</v>
       </c>
       <c r="B39" t="n">
-        <v>78526</v>
+        <v>5169</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4505,25 +4486,25 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>100526</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4533,10 +4514,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>453742</v>
+        <v>453849</v>
       </c>
       <c r="R39" t="n">
-        <v>6807994</v>
+        <v>6807844</v>
       </c>
       <c r="S39" t="n">
         <v>15</v>
@@ -4595,10 +4576,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>119590996</v>
+        <v>119591083</v>
       </c>
       <c r="B40" t="n">
-        <v>57463</v>
+        <v>78526</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4611,21 +4592,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4635,10 +4616,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>453750</v>
+        <v>453848</v>
       </c>
       <c r="R40" t="n">
-        <v>6807861</v>
+        <v>6808029</v>
       </c>
       <c r="S40" t="n">
         <v>15</v>
@@ -4697,7 +4678,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>119591066</v>
+        <v>119591076</v>
       </c>
       <c r="B41" t="n">
         <v>78526</v>
@@ -4737,10 +4718,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>453787</v>
+        <v>453811</v>
       </c>
       <c r="R41" t="n">
-        <v>6808020</v>
+        <v>6808106</v>
       </c>
       <c r="S41" t="n">
         <v>15</v>
@@ -4799,10 +4780,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>119591029</v>
+        <v>119591091</v>
       </c>
       <c r="B42" t="n">
-        <v>90580</v>
+        <v>78526</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4815,21 +4796,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4839,10 +4820,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>453861</v>
+        <v>453798</v>
       </c>
       <c r="R42" t="n">
-        <v>6807970</v>
+        <v>6808108</v>
       </c>
       <c r="S42" t="n">
         <v>15</v>
@@ -4869,12 +4850,12 @@
       </c>
       <c r="Y42" t="inlineStr">
         <is>
-          <t>2024-09-06</t>
+          <t>2024-09-04</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>2024-09-06</t>
+          <t>2024-09-04</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -4901,10 +4882,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>119591006</v>
+        <v>119591050</v>
       </c>
       <c r="B43" t="n">
-        <v>57310</v>
+        <v>78526</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -4917,39 +4898,34 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
-      <c r="M43" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P43" t="inlineStr">
         <is>
           <t>Rymån, Dlr</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>453796</v>
+        <v>453782</v>
       </c>
       <c r="R43" t="n">
-        <v>6808114</v>
+        <v>6807956</v>
       </c>
       <c r="S43" t="n">
         <v>15</v>
@@ -4982,11 +4958,6 @@
       <c r="AA43" t="inlineStr">
         <is>
           <t>2024-09-06</t>
-        </is>
-      </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>Färska ringhack (gran)</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5013,7 +4984,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>119591087</v>
+        <v>119591055</v>
       </c>
       <c r="B44" t="n">
         <v>78526</v>
@@ -5053,10 +5024,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>453803</v>
+        <v>453747</v>
       </c>
       <c r="R44" t="n">
-        <v>6808020</v>
+        <v>6807979</v>
       </c>
       <c r="S44" t="n">
         <v>15</v>
@@ -5083,12 +5054,12 @@
       </c>
       <c r="Y44" t="inlineStr">
         <is>
-          <t>2024-09-04</t>
+          <t>2024-09-06</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>2024-09-04</t>
+          <t>2024-09-06</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5115,7 +5086,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>119591082</v>
+        <v>119591088</v>
       </c>
       <c r="B45" t="n">
         <v>78526</v>
@@ -5155,10 +5126,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>453850</v>
+        <v>453778</v>
       </c>
       <c r="R45" t="n">
-        <v>6808037</v>
+        <v>6808053</v>
       </c>
       <c r="S45" t="n">
         <v>15</v>
@@ -5185,12 +5156,12 @@
       </c>
       <c r="Y45" t="inlineStr">
         <is>
-          <t>2024-09-06</t>
+          <t>2024-09-04</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>2024-09-06</t>
+          <t>2024-09-04</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5217,7 +5188,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>119591032</v>
+        <v>119591085</v>
       </c>
       <c r="B46" t="n">
         <v>78526</v>
@@ -5257,10 +5228,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>453897</v>
+        <v>453830</v>
       </c>
       <c r="R46" t="n">
-        <v>6808009</v>
+        <v>6808029</v>
       </c>
       <c r="S46" t="n">
         <v>15</v>
@@ -5287,12 +5258,12 @@
       </c>
       <c r="Y46" t="inlineStr">
         <is>
-          <t>2024-09-06</t>
+          <t>2024-09-04</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>2024-09-06</t>
+          <t>2024-09-04</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5319,10 +5290,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>119591101</v>
+        <v>119591038</v>
       </c>
       <c r="B47" t="n">
-        <v>5169</v>
+        <v>78526</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5331,25 +5302,25 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>100526</v>
+        <v>6425</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5359,10 +5330,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>453849</v>
+        <v>453826</v>
       </c>
       <c r="R47" t="n">
-        <v>6807844</v>
+        <v>6807750</v>
       </c>
       <c r="S47" t="n">
         <v>15</v>
@@ -5421,7 +5392,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>119591059</v>
+        <v>119591046</v>
       </c>
       <c r="B48" t="n">
         <v>78526</v>
@@ -5461,10 +5432,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>453737</v>
+        <v>453792</v>
       </c>
       <c r="R48" t="n">
-        <v>6808007</v>
+        <v>6807881</v>
       </c>
       <c r="S48" t="n">
         <v>15</v>
@@ -5523,10 +5494,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>119591061</v>
+        <v>119591006</v>
       </c>
       <c r="B49" t="n">
-        <v>78526</v>
+        <v>57310</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5539,34 +5510,39 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P49" t="inlineStr">
         <is>
           <t>Rymån, Dlr</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>453756</v>
+        <v>453796</v>
       </c>
       <c r="R49" t="n">
-        <v>6808003</v>
+        <v>6808114</v>
       </c>
       <c r="S49" t="n">
         <v>15</v>
@@ -5599,6 +5575,11 @@
       <c r="AA49" t="inlineStr">
         <is>
           <t>2024-09-06</t>
+        </is>
+      </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>Färska ringhack (gran)</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5625,10 +5606,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>119591041</v>
+        <v>119590997</v>
       </c>
       <c r="B50" t="n">
-        <v>78526</v>
+        <v>57463</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5641,21 +5622,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5665,10 +5646,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>453773</v>
+        <v>453806</v>
       </c>
       <c r="R50" t="n">
-        <v>6807791</v>
+        <v>6808118</v>
       </c>
       <c r="S50" t="n">
         <v>15</v>
@@ -5727,10 +5708,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>119590972</v>
+        <v>119591025</v>
       </c>
       <c r="B51" t="n">
-        <v>74638</v>
+        <v>93935</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -5739,25 +5720,25 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6440</v>
+        <v>2387</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Källpraktmossa</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Pseudobryum cinclidioides</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Huebener) T.J.Kop.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5767,10 +5748,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>453874</v>
+        <v>453851</v>
       </c>
       <c r="R51" t="n">
-        <v>6808094</v>
+        <v>6807838</v>
       </c>
       <c r="S51" t="n">
         <v>15</v>
@@ -5829,10 +5810,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>119591073</v>
+        <v>119590987</v>
       </c>
       <c r="B52" t="n">
-        <v>78526</v>
+        <v>90562</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -5845,21 +5826,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5869,10 +5850,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>453797</v>
+        <v>453772</v>
       </c>
       <c r="R52" t="n">
-        <v>6808117</v>
+        <v>6807796</v>
       </c>
       <c r="S52" t="n">
         <v>15</v>
@@ -5931,10 +5912,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>119591030</v>
+        <v>119591042</v>
       </c>
       <c r="B53" t="n">
-        <v>90580</v>
+        <v>78526</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -5947,21 +5928,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5971,10 +5952,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>453779</v>
+        <v>453788</v>
       </c>
       <c r="R53" t="n">
-        <v>6807856</v>
+        <v>6807792</v>
       </c>
       <c r="S53" t="n">
         <v>15</v>
@@ -6033,10 +6014,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>119591055</v>
+        <v>119590976</v>
       </c>
       <c r="B54" t="n">
-        <v>78526</v>
+        <v>79144</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6049,21 +6030,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6073,10 +6054,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>453747</v>
+        <v>453836</v>
       </c>
       <c r="R54" t="n">
-        <v>6807979</v>
+        <v>6807943</v>
       </c>
       <c r="S54" t="n">
         <v>15</v>
@@ -6135,10 +6116,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>119590976</v>
+        <v>119591034</v>
       </c>
       <c r="B55" t="n">
-        <v>79144</v>
+        <v>78526</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6151,21 +6132,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6175,10 +6156,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>453836</v>
+        <v>453825</v>
       </c>
       <c r="R55" t="n">
-        <v>6807943</v>
+        <v>6807960</v>
       </c>
       <c r="S55" t="n">
         <v>15</v>
@@ -6237,7 +6218,7 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>119591084</v>
+        <v>119591071</v>
       </c>
       <c r="B56" t="n">
         <v>78526</v>
@@ -6277,10 +6258,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>453835</v>
+        <v>453788</v>
       </c>
       <c r="R56" t="n">
-        <v>6808031</v>
+        <v>6808086</v>
       </c>
       <c r="S56" t="n">
         <v>15</v>
@@ -6307,12 +6288,12 @@
       </c>
       <c r="Y56" t="inlineStr">
         <is>
-          <t>2024-09-04</t>
+          <t>2024-09-06</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
         <is>
-          <t>2024-09-04</t>
+          <t>2024-09-06</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6339,10 +6320,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>119590998</v>
+        <v>119591064</v>
       </c>
       <c r="B57" t="n">
-        <v>57463</v>
+        <v>78526</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6355,21 +6336,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6379,10 +6360,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>453861</v>
+        <v>453761</v>
       </c>
       <c r="R57" t="n">
-        <v>6808024</v>
+        <v>6807996</v>
       </c>
       <c r="S57" t="n">
         <v>15</v>
@@ -6441,10 +6422,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>119591025</v>
+        <v>119591089</v>
       </c>
       <c r="B58" t="n">
-        <v>93935</v>
+        <v>78526</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6453,25 +6434,25 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>2387</v>
+        <v>6425</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Källpraktmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Pseudobryum cinclidioides</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Huebener) T.J.Kop.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6481,10 +6462,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>453851</v>
+        <v>453780</v>
       </c>
       <c r="R58" t="n">
-        <v>6807838</v>
+        <v>6808055</v>
       </c>
       <c r="S58" t="n">
         <v>15</v>
@@ -6511,12 +6492,12 @@
       </c>
       <c r="Y58" t="inlineStr">
         <is>
-          <t>2024-09-06</t>
+          <t>2024-09-04</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
         <is>
-          <t>2024-09-06</t>
+          <t>2024-09-04</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6543,10 +6524,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>119591091</v>
+        <v>119591030</v>
       </c>
       <c r="B59" t="n">
-        <v>78526</v>
+        <v>90580</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -6559,21 +6540,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6583,10 +6564,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>453798</v>
+        <v>453779</v>
       </c>
       <c r="R59" t="n">
-        <v>6808108</v>
+        <v>6807856</v>
       </c>
       <c r="S59" t="n">
         <v>15</v>
@@ -6613,12 +6594,12 @@
       </c>
       <c r="Y59" t="inlineStr">
         <is>
-          <t>2024-09-04</t>
+          <t>2024-09-06</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
         <is>
-          <t>2024-09-04</t>
+          <t>2024-09-06</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6645,10 +6626,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>119591054</v>
+        <v>119591010</v>
       </c>
       <c r="B60" t="n">
-        <v>78526</v>
+        <v>57310</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -6661,34 +6642,39 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P60" t="inlineStr">
         <is>
           <t>Rymån, Dlr</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>453738</v>
+        <v>453805</v>
       </c>
       <c r="R60" t="n">
-        <v>6807973</v>
+        <v>6808118</v>
       </c>
       <c r="S60" t="n">
         <v>15</v>
@@ -6715,12 +6701,17 @@
       </c>
       <c r="Y60" t="inlineStr">
         <is>
-          <t>2024-09-06</t>
+          <t>2024-09-04</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
         <is>
-          <t>2024-09-06</t>
+          <t>2024-09-04</t>
+        </is>
+      </c>
+      <c r="AC60" t="inlineStr">
+        <is>
+          <t>Färska ringhack (gran)</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -6747,7 +6738,7 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>119591085</v>
+        <v>119591053</v>
       </c>
       <c r="B61" t="n">
         <v>78526</v>
@@ -6787,10 +6778,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>453830</v>
+        <v>453752</v>
       </c>
       <c r="R61" t="n">
-        <v>6808029</v>
+        <v>6807968</v>
       </c>
       <c r="S61" t="n">
         <v>15</v>
@@ -6817,12 +6808,12 @@
       </c>
       <c r="Y61" t="inlineStr">
         <is>
-          <t>2024-09-04</t>
+          <t>2024-09-06</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
         <is>
-          <t>2024-09-04</t>
+          <t>2024-09-06</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -6849,7 +6840,7 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>119591044</v>
+        <v>119591075</v>
       </c>
       <c r="B62" t="n">
         <v>78526</v>
@@ -6889,10 +6880,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>453764</v>
+        <v>453809</v>
       </c>
       <c r="R62" t="n">
-        <v>6807870</v>
+        <v>6808107</v>
       </c>
       <c r="S62" t="n">
         <v>15</v>
@@ -6951,10 +6942,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>119590982</v>
+        <v>119591082</v>
       </c>
       <c r="B63" t="n">
-        <v>79144</v>
+        <v>78526</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -6967,21 +6958,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -6991,10 +6982,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>453794</v>
+        <v>453850</v>
       </c>
       <c r="R63" t="n">
-        <v>6807980</v>
+        <v>6808037</v>
       </c>
       <c r="S63" t="n">
         <v>15</v>
@@ -7053,10 +7044,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>119591026</v>
+        <v>119591040</v>
       </c>
       <c r="B64" t="n">
-        <v>78262</v>
+        <v>78526</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7069,21 +7060,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7093,10 +7084,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>453770</v>
+        <v>453808</v>
       </c>
       <c r="R64" t="n">
-        <v>6807987</v>
+        <v>6807761</v>
       </c>
       <c r="S64" t="n">
         <v>15</v>
@@ -7155,7 +7146,7 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>119591065</v>
+        <v>119591036</v>
       </c>
       <c r="B65" t="n">
         <v>78526</v>
@@ -7195,10 +7186,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>453782</v>
+        <v>453849</v>
       </c>
       <c r="R65" t="n">
-        <v>6807982</v>
+        <v>6807844</v>
       </c>
       <c r="S65" t="n">
         <v>15</v>
@@ -7257,10 +7248,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>119591036</v>
+        <v>119591019</v>
       </c>
       <c r="B66" t="n">
-        <v>78526</v>
+        <v>96865</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7269,38 +7260,47 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6425</v>
+        <v>221946</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mattlummer</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium clavatum</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I66" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
       <c r="P66" t="inlineStr">
         <is>
           <t>Rymån, Dlr</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>453849</v>
+        <v>453836</v>
       </c>
       <c r="R66" t="n">
-        <v>6807844</v>
+        <v>6807799</v>
       </c>
       <c r="S66" t="n">
         <v>15</v>
@@ -7359,10 +7359,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>119590991</v>
+        <v>119590975</v>
       </c>
       <c r="B67" t="n">
-        <v>57310</v>
+        <v>79144</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -7375,39 +7375,34 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>100109</v>
+        <v>6453</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
-      <c r="M67" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P67" t="inlineStr">
         <is>
           <t>Rymån, Dlr</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>453887</v>
+        <v>453828</v>
       </c>
       <c r="R67" t="n">
-        <v>6808050</v>
+        <v>6807944</v>
       </c>
       <c r="S67" t="n">
         <v>15</v>
@@ -7466,10 +7461,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>119591097</v>
+        <v>119591058</v>
       </c>
       <c r="B68" t="n">
-        <v>57310</v>
+        <v>78526</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -7482,39 +7477,34 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
-      <c r="M68" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P68" t="inlineStr">
         <is>
           <t>Rymån, Dlr</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>453849</v>
+        <v>453734</v>
       </c>
       <c r="R68" t="n">
-        <v>6807844</v>
+        <v>6808007</v>
       </c>
       <c r="S68" t="n">
         <v>15</v>
@@ -7573,10 +7563,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>119591007</v>
+        <v>119591004</v>
       </c>
       <c r="B69" t="n">
-        <v>57310</v>
+        <v>91884</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -7589,39 +7579,34 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>100109</v>
+        <v>5449</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
-      <c r="M69" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P69" t="inlineStr">
         <is>
           <t>Rymån, Dlr</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>453808</v>
+        <v>453785</v>
       </c>
       <c r="R69" t="n">
-        <v>6808114</v>
+        <v>6808062</v>
       </c>
       <c r="S69" t="n">
         <v>15</v>
@@ -7654,11 +7639,6 @@
       <c r="AA69" t="inlineStr">
         <is>
           <t>2024-09-06</t>
-        </is>
-      </c>
-      <c r="AC69" t="inlineStr">
-        <is>
-          <t>Färska ringhack (gran)</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -7685,7 +7665,7 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>119591062</v>
+        <v>119591032</v>
       </c>
       <c r="B70" t="n">
         <v>78526</v>
@@ -7725,10 +7705,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>453761</v>
+        <v>453897</v>
       </c>
       <c r="R70" t="n">
-        <v>6808000</v>
+        <v>6808009</v>
       </c>
       <c r="S70" t="n">
         <v>15</v>
@@ -7787,7 +7767,7 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>119590981</v>
+        <v>119590978</v>
       </c>
       <c r="B71" t="n">
         <v>79144</v>
@@ -7827,10 +7807,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>453770</v>
+        <v>453823</v>
       </c>
       <c r="R71" t="n">
-        <v>6807987</v>
+        <v>6807778</v>
       </c>
       <c r="S71" t="n">
         <v>15</v>
@@ -7889,10 +7869,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>119591037</v>
+        <v>119590996</v>
       </c>
       <c r="B72" t="n">
-        <v>78526</v>
+        <v>57463</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -7905,21 +7885,21 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -7929,10 +7909,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>453829</v>
+        <v>453750</v>
       </c>
       <c r="R72" t="n">
-        <v>6807768</v>
+        <v>6807861</v>
       </c>
       <c r="S72" t="n">
         <v>15</v>
@@ -7991,10 +7971,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>119591034</v>
+        <v>119591012</v>
       </c>
       <c r="B73" t="n">
-        <v>78526</v>
+        <v>96862</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -8003,25 +7983,25 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -8031,10 +8011,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>453825</v>
+        <v>453875</v>
       </c>
       <c r="R73" t="n">
-        <v>6807960</v>
+        <v>6808094</v>
       </c>
       <c r="S73" t="n">
         <v>15</v>
@@ -8093,7 +8073,7 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>119591045</v>
+        <v>119591061</v>
       </c>
       <c r="B74" t="n">
         <v>78526</v>
@@ -8133,10 +8113,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>453764</v>
+        <v>453756</v>
       </c>
       <c r="R74" t="n">
-        <v>6807871</v>
+        <v>6808003</v>
       </c>
       <c r="S74" t="n">
         <v>15</v>
@@ -8195,7 +8175,7 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>119591046</v>
+        <v>119591059</v>
       </c>
       <c r="B75" t="n">
         <v>78526</v>
@@ -8235,10 +8215,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>453792</v>
+        <v>453737</v>
       </c>
       <c r="R75" t="n">
-        <v>6807881</v>
+        <v>6808007</v>
       </c>
       <c r="S75" t="n">
         <v>15</v>
@@ -8297,10 +8277,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>119591039</v>
+        <v>119590969</v>
       </c>
       <c r="B76" t="n">
-        <v>78526</v>
+        <v>57310</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -8313,34 +8293,39 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
+      <c r="M76" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P76" t="inlineStr">
         <is>
           <t>Rymån, Dlr</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>453790</v>
+        <v>453847</v>
       </c>
       <c r="R76" t="n">
-        <v>6807766</v>
+        <v>6807830</v>
       </c>
       <c r="S76" t="n">
         <v>15</v>
@@ -8373,6 +8358,11 @@
       <c r="AA76" t="inlineStr">
         <is>
           <t>2024-09-06</t>
+        </is>
+      </c>
+      <c r="AC76" t="inlineStr">
+        <is>
+          <t>Försett med naturvårdssnitsel</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8399,7 +8389,7 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>119591068</v>
+        <v>119591087</v>
       </c>
       <c r="B77" t="n">
         <v>78526</v>
@@ -8439,10 +8429,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>453770</v>
+        <v>453803</v>
       </c>
       <c r="R77" t="n">
-        <v>6808029</v>
+        <v>6808020</v>
       </c>
       <c r="S77" t="n">
         <v>15</v>
@@ -8469,12 +8459,12 @@
       </c>
       <c r="Y77" t="inlineStr">
         <is>
-          <t>2024-09-06</t>
+          <t>2024-09-04</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
         <is>
-          <t>2024-09-06</t>
+          <t>2024-09-04</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -8501,10 +8491,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>119591051</v>
+        <v>119590998</v>
       </c>
       <c r="B78" t="n">
-        <v>78526</v>
+        <v>57463</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -8517,21 +8507,21 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8541,10 +8531,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>453755</v>
+        <v>453861</v>
       </c>
       <c r="R78" t="n">
-        <v>6807941</v>
+        <v>6808024</v>
       </c>
       <c r="S78" t="n">
         <v>15</v>
@@ -8603,10 +8593,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>119590983</v>
+        <v>119591022</v>
       </c>
       <c r="B79" t="n">
-        <v>79144</v>
+        <v>78263</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -8619,21 +8609,21 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8643,10 +8633,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>453762</v>
+        <v>453759</v>
       </c>
       <c r="R79" t="n">
-        <v>6808048</v>
+        <v>6807967</v>
       </c>
       <c r="S79" t="n">
         <v>15</v>
@@ -8705,10 +8695,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>119590979</v>
+        <v>119591056</v>
       </c>
       <c r="B80" t="n">
-        <v>79144</v>
+        <v>78526</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -8721,21 +8711,21 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -8745,10 +8735,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>453807</v>
+        <v>453742</v>
       </c>
       <c r="R80" t="n">
-        <v>6807719</v>
+        <v>6807994</v>
       </c>
       <c r="S80" t="n">
         <v>15</v>
@@ -8807,10 +8797,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>119590969</v>
+        <v>119590999</v>
       </c>
       <c r="B81" t="n">
-        <v>57310</v>
+        <v>91463</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -8823,39 +8813,34 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>100109</v>
+        <v>4745</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tallriska</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lactarius musteus</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
-      <c r="M81" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P81" t="inlineStr">
         <is>
           <t>Rymån, Dlr</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>453847</v>
+        <v>453793</v>
       </c>
       <c r="R81" t="n">
-        <v>6807830</v>
+        <v>6808029</v>
       </c>
       <c r="S81" t="n">
         <v>15</v>
@@ -8882,17 +8867,12 @@
       </c>
       <c r="Y81" t="inlineStr">
         <is>
-          <t>2024-09-06</t>
+          <t>2024-09-04</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
         <is>
-          <t>2024-09-06</t>
-        </is>
-      </c>
-      <c r="AC81" t="inlineStr">
-        <is>
-          <t>Försett med naturvårdssnitsel</t>
+          <t>2024-09-04</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -8919,10 +8899,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>119590974</v>
+        <v>119591008</v>
       </c>
       <c r="B82" t="n">
-        <v>95455</v>
+        <v>57310</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -8935,34 +8915,39 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>53</v>
+        <v>100109</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
+      <c r="M82" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P82" t="inlineStr">
         <is>
           <t>Rymån, Dlr</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>453852</v>
+        <v>453821</v>
       </c>
       <c r="R82" t="n">
-        <v>6807959</v>
+        <v>6808117</v>
       </c>
       <c r="S82" t="n">
         <v>15</v>
@@ -8995,6 +8980,11 @@
       <c r="AA82" t="inlineStr">
         <is>
           <t>2024-09-06</t>
+        </is>
+      </c>
+      <c r="AC82" t="inlineStr">
+        <is>
+          <t>Färska ringhack (gran)</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9021,10 +9011,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>119591088</v>
+        <v>119591009</v>
       </c>
       <c r="B83" t="n">
-        <v>78526</v>
+        <v>57310</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -9037,34 +9027,39 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
+      <c r="M83" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P83" t="inlineStr">
         <is>
           <t>Rymån, Dlr</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>453778</v>
+        <v>453815</v>
       </c>
       <c r="R83" t="n">
-        <v>6808053</v>
+        <v>6808098</v>
       </c>
       <c r="S83" t="n">
         <v>15</v>
@@ -9091,12 +9086,17 @@
       </c>
       <c r="Y83" t="inlineStr">
         <is>
-          <t>2024-09-04</t>
+          <t>2024-09-06</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
         <is>
-          <t>2024-09-04</t>
+          <t>2024-09-06</t>
+        </is>
+      </c>
+      <c r="AC83" t="inlineStr">
+        <is>
+          <t>Färska ringhack (gran)</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -9123,10 +9123,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>119591090</v>
+        <v>119591011</v>
       </c>
       <c r="B84" t="n">
-        <v>78526</v>
+        <v>96862</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -9135,25 +9135,25 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -9163,10 +9163,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>453794</v>
+        <v>453903</v>
       </c>
       <c r="R84" t="n">
-        <v>6808097</v>
+        <v>6807986</v>
       </c>
       <c r="S84" t="n">
         <v>15</v>
@@ -9193,12 +9193,12 @@
       </c>
       <c r="Y84" t="inlineStr">
         <is>
-          <t>2024-09-04</t>
+          <t>2024-09-06</t>
         </is>
       </c>
       <c r="AA84" t="inlineStr">
         <is>
-          <t>2024-09-04</t>
+          <t>2024-09-06</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -9225,10 +9225,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>119590987</v>
+        <v>119590980</v>
       </c>
       <c r="B85" t="n">
-        <v>90562</v>
+        <v>79144</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -9241,21 +9241,21 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>1202</v>
+        <v>6453</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -9265,10 +9265,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>453772</v>
+        <v>453791</v>
       </c>
       <c r="R85" t="n">
-        <v>6807796</v>
+        <v>6807707</v>
       </c>
       <c r="S85" t="n">
         <v>15</v>
@@ -9327,10 +9327,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>119590986</v>
+        <v>119591031</v>
       </c>
       <c r="B86" t="n">
-        <v>90562</v>
+        <v>90580</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -9343,21 +9343,21 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -9367,10 +9367,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>453795</v>
+        <v>453886</v>
       </c>
       <c r="R86" t="n">
-        <v>6807770</v>
+        <v>6808055</v>
       </c>
       <c r="S86" t="n">
         <v>15</v>
@@ -9429,10 +9429,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>119591075</v>
+        <v>119590972</v>
       </c>
       <c r="B87" t="n">
-        <v>78526</v>
+        <v>74638</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -9445,21 +9445,21 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -9469,10 +9469,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>453809</v>
+        <v>453874</v>
       </c>
       <c r="R87" t="n">
-        <v>6808107</v>
+        <v>6808094</v>
       </c>
       <c r="S87" t="n">
         <v>15</v>
@@ -9531,10 +9531,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>119590995</v>
+        <v>119591086</v>
       </c>
       <c r="B88" t="n">
-        <v>103418</v>
+        <v>78526</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
@@ -9543,25 +9543,25 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>222412</v>
+        <v>6425</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -9571,10 +9571,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>453897</v>
+        <v>453820</v>
       </c>
       <c r="R88" t="n">
-        <v>6808024</v>
+        <v>6808020</v>
       </c>
       <c r="S88" t="n">
         <v>15</v>
@@ -9601,12 +9601,12 @@
       </c>
       <c r="Y88" t="inlineStr">
         <is>
-          <t>2024-09-06</t>
+          <t>2024-09-04</t>
         </is>
       </c>
       <c r="AA88" t="inlineStr">
         <is>
-          <t>2024-09-06</t>
+          <t>2024-09-04</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -9633,10 +9633,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>119590999</v>
+        <v>119590983</v>
       </c>
       <c r="B89" t="n">
-        <v>91463</v>
+        <v>79144</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
@@ -9649,21 +9649,21 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>4745</v>
+        <v>6453</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Tallriska</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Lactarius musteus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -9673,10 +9673,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>453793</v>
+        <v>453762</v>
       </c>
       <c r="R89" t="n">
-        <v>6808029</v>
+        <v>6808048</v>
       </c>
       <c r="S89" t="n">
         <v>15</v>
@@ -9703,12 +9703,12 @@
       </c>
       <c r="Y89" t="inlineStr">
         <is>
-          <t>2024-09-04</t>
+          <t>2024-09-06</t>
         </is>
       </c>
       <c r="AA89" t="inlineStr">
         <is>
-          <t>2024-09-04</t>
+          <t>2024-09-06</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -9735,10 +9735,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>119591015</v>
+        <v>119591052</v>
       </c>
       <c r="B90" t="n">
-        <v>79635</v>
+        <v>78526</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
@@ -9747,25 +9747,25 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>6461</v>
+        <v>6425</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -9775,10 +9775,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>453820</v>
+        <v>453755</v>
       </c>
       <c r="R90" t="n">
-        <v>6808064</v>
+        <v>6807948</v>
       </c>
       <c r="S90" t="n">
         <v>15</v>
@@ -9837,10 +9837,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>119591031</v>
+        <v>119590974</v>
       </c>
       <c r="B91" t="n">
-        <v>90580</v>
+        <v>95455</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
@@ -9853,21 +9853,21 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>5432</v>
+        <v>53</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -9877,10 +9877,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>453886</v>
+        <v>453852</v>
       </c>
       <c r="R91" t="n">
-        <v>6808055</v>
+        <v>6807959</v>
       </c>
       <c r="S91" t="n">
         <v>15</v>
@@ -9939,10 +9939,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>119591038</v>
+        <v>119590991</v>
       </c>
       <c r="B92" t="n">
-        <v>78526</v>
+        <v>57310</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
@@ -9955,34 +9955,39 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
+      <c r="M92" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P92" t="inlineStr">
         <is>
           <t>Rymån, Dlr</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>453826</v>
+        <v>453887</v>
       </c>
       <c r="R92" t="n">
-        <v>6807750</v>
+        <v>6808050</v>
       </c>
       <c r="S92" t="n">
         <v>15</v>
@@ -10041,7 +10046,7 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>119591060</v>
+        <v>119591062</v>
       </c>
       <c r="B93" t="n">
         <v>78526</v>
@@ -10081,10 +10086,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>453748</v>
+        <v>453761</v>
       </c>
       <c r="R93" t="n">
-        <v>6808003</v>
+        <v>6808000</v>
       </c>
       <c r="S93" t="n">
         <v>15</v>
@@ -10143,7 +10148,7 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>119591074</v>
+        <v>119591069</v>
       </c>
       <c r="B94" t="n">
         <v>78526</v>
@@ -10183,10 +10188,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>453796</v>
+        <v>453756</v>
       </c>
       <c r="R94" t="n">
-        <v>6808121</v>
+        <v>6808048</v>
       </c>
       <c r="S94" t="n">
         <v>15</v>
@@ -10245,10 +10250,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>119590990</v>
+        <v>119591043</v>
       </c>
       <c r="B95" t="n">
-        <v>57310</v>
+        <v>78526</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
@@ -10261,39 +10266,34 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
-      <c r="M95" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P95" t="inlineStr">
         <is>
           <t>Rymån, Dlr</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>453803</v>
+        <v>453774</v>
       </c>
       <c r="R95" t="n">
-        <v>6807752</v>
+        <v>6807849</v>
       </c>
       <c r="S95" t="n">
         <v>15</v>
@@ -10352,10 +10352,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>119590985</v>
+        <v>119591054</v>
       </c>
       <c r="B96" t="n">
-        <v>90562</v>
+        <v>78526</v>
       </c>
       <c r="C96" t="inlineStr">
         <is>
@@ -10368,21 +10368,21 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -10392,10 +10392,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>453839</v>
+        <v>453738</v>
       </c>
       <c r="R96" t="n">
-        <v>6807828</v>
+        <v>6807973</v>
       </c>
       <c r="S96" t="n">
         <v>15</v>
@@ -10454,10 +10454,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>119591043</v>
+        <v>119591023</v>
       </c>
       <c r="B97" t="n">
-        <v>78526</v>
+        <v>78263</v>
       </c>
       <c r="C97" t="inlineStr">
         <is>
@@ -10470,21 +10470,21 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -10494,10 +10494,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>453774</v>
+        <v>453770</v>
       </c>
       <c r="R97" t="n">
-        <v>6807849</v>
+        <v>6807984</v>
       </c>
       <c r="S97" t="n">
         <v>15</v>
@@ -10556,7 +10556,7 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>119591047</v>
+        <v>119591066</v>
       </c>
       <c r="B98" t="n">
         <v>78526</v>
@@ -10596,10 +10596,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>453785</v>
+        <v>453787</v>
       </c>
       <c r="R98" t="n">
-        <v>6807890</v>
+        <v>6808020</v>
       </c>
       <c r="S98" t="n">
         <v>15</v>
@@ -10658,7 +10658,7 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>119591086</v>
+        <v>119591070</v>
       </c>
       <c r="B99" t="n">
         <v>78526</v>
@@ -10698,10 +10698,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>453820</v>
+        <v>453759</v>
       </c>
       <c r="R99" t="n">
-        <v>6808020</v>
+        <v>6808051</v>
       </c>
       <c r="S99" t="n">
         <v>15</v>
@@ -10728,12 +10728,12 @@
       </c>
       <c r="Y99" t="inlineStr">
         <is>
-          <t>2024-09-04</t>
+          <t>2024-09-06</t>
         </is>
       </c>
       <c r="AA99" t="inlineStr">
         <is>
-          <t>2024-09-04</t>
+          <t>2024-09-06</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -10760,10 +10760,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>119591096</v>
+        <v>119590981</v>
       </c>
       <c r="B100" t="n">
-        <v>78526</v>
+        <v>79144</v>
       </c>
       <c r="C100" t="inlineStr">
         <is>
@@ -10776,21 +10776,21 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -10800,10 +10800,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>453898</v>
+        <v>453770</v>
       </c>
       <c r="R100" t="n">
-        <v>6808089</v>
+        <v>6807987</v>
       </c>
       <c r="S100" t="n">
         <v>15</v>
@@ -10862,10 +10862,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>119590977</v>
+        <v>119591090</v>
       </c>
       <c r="B101" t="n">
-        <v>79144</v>
+        <v>78526</v>
       </c>
       <c r="C101" t="inlineStr">
         <is>
@@ -10878,21 +10878,21 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
@@ -10902,10 +10902,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>453807</v>
+        <v>453794</v>
       </c>
       <c r="R101" t="n">
-        <v>6807916</v>
+        <v>6808097</v>
       </c>
       <c r="S101" t="n">
         <v>15</v>
@@ -10932,12 +10932,12 @@
       </c>
       <c r="Y101" t="inlineStr">
         <is>
-          <t>2024-09-06</t>
+          <t>2024-09-04</t>
         </is>
       </c>
       <c r="AA101" t="inlineStr">
         <is>
-          <t>2024-09-06</t>
+          <t>2024-09-04</t>
         </is>
       </c>
       <c r="AD101" t="b">

--- a/artfynd/A 31144-2024 artfynd.xlsx
+++ b/artfynd/A 31144-2024 artfynd.xlsx
@@ -1287,10 +1287,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119591057</v>
+        <v>119590979</v>
       </c>
       <c r="B8" t="n">
-        <v>78526</v>
+        <v>79144</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1303,21 +1303,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1327,10 +1327,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>453736</v>
+        <v>453807</v>
       </c>
       <c r="R8" t="n">
-        <v>6808004</v>
+        <v>6807719</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1389,10 +1389,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>119591028</v>
+        <v>119590977</v>
       </c>
       <c r="B9" t="n">
-        <v>90580</v>
+        <v>79144</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1405,21 +1405,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5432</v>
+        <v>6453</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1429,10 +1429,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>453791</v>
+        <v>453807</v>
       </c>
       <c r="R9" t="n">
-        <v>6807765</v>
+        <v>6807916</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1465,11 +1465,6 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2024-09-06</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Gamla fruktkroppar</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1496,7 +1491,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>119591067</v>
+        <v>119591057</v>
       </c>
       <c r="B10" t="n">
         <v>78526</v>
@@ -1536,10 +1531,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>453775</v>
+        <v>453736</v>
       </c>
       <c r="R10" t="n">
-        <v>6808032</v>
+        <v>6808004</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>
@@ -1598,10 +1593,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>119590979</v>
+        <v>119591028</v>
       </c>
       <c r="B11" t="n">
-        <v>79144</v>
+        <v>90580</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1614,21 +1609,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6453</v>
+        <v>5432</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1638,10 +1633,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>453807</v>
+        <v>453791</v>
       </c>
       <c r="R11" t="n">
-        <v>6807719</v>
+        <v>6807765</v>
       </c>
       <c r="S11" t="n">
         <v>15</v>
@@ -1674,6 +1669,11 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2024-09-06</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Gamla fruktkroppar</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1700,10 +1700,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>119590977</v>
+        <v>119591067</v>
       </c>
       <c r="B12" t="n">
-        <v>79144</v>
+        <v>78526</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1716,21 +1716,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1740,10 +1740,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>453807</v>
+        <v>453775</v>
       </c>
       <c r="R12" t="n">
-        <v>6807916</v>
+        <v>6808032</v>
       </c>
       <c r="S12" t="n">
         <v>15</v>
@@ -1802,10 +1802,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>119590986</v>
+        <v>119590994</v>
       </c>
       <c r="B13" t="n">
-        <v>90562</v>
+        <v>103418</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1814,25 +1814,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1202</v>
+        <v>222412</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1842,10 +1842,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>453795</v>
+        <v>453893</v>
       </c>
       <c r="R13" t="n">
-        <v>6807770</v>
+        <v>6808027</v>
       </c>
       <c r="S13" t="n">
         <v>15</v>
@@ -1904,10 +1904,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>119591033</v>
+        <v>119590986</v>
       </c>
       <c r="B14" t="n">
-        <v>78526</v>
+        <v>90562</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1920,21 +1920,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1944,10 +1944,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>453835</v>
+        <v>453795</v>
       </c>
       <c r="R14" t="n">
-        <v>6807974</v>
+        <v>6807770</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -2006,10 +2006,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>119591029</v>
+        <v>119591033</v>
       </c>
       <c r="B15" t="n">
-        <v>90580</v>
+        <v>78526</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2022,21 +2022,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2046,10 +2046,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>453861</v>
+        <v>453835</v>
       </c>
       <c r="R15" t="n">
-        <v>6807970</v>
+        <v>6807974</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2108,10 +2108,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>119591077</v>
+        <v>119591029</v>
       </c>
       <c r="B16" t="n">
-        <v>78526</v>
+        <v>90580</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2124,21 +2124,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2148,10 +2148,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>453815</v>
+        <v>453861</v>
       </c>
       <c r="R16" t="n">
-        <v>6808130</v>
+        <v>6807970</v>
       </c>
       <c r="S16" t="n">
         <v>15</v>
@@ -2210,7 +2210,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>119591051</v>
+        <v>119591077</v>
       </c>
       <c r="B17" t="n">
         <v>78526</v>
@@ -2250,10 +2250,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>453755</v>
+        <v>453815</v>
       </c>
       <c r="R17" t="n">
-        <v>6807941</v>
+        <v>6808130</v>
       </c>
       <c r="S17" t="n">
         <v>15</v>
@@ -2312,10 +2312,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>119590994</v>
+        <v>119591051</v>
       </c>
       <c r="B18" t="n">
-        <v>103418</v>
+        <v>78526</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2324,25 +2324,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>222412</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2352,10 +2352,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>453893</v>
+        <v>453755</v>
       </c>
       <c r="R18" t="n">
-        <v>6808027</v>
+        <v>6807941</v>
       </c>
       <c r="S18" t="n">
         <v>15</v>
@@ -2822,10 +2822,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>119590990</v>
+        <v>119591074</v>
       </c>
       <c r="B23" t="n">
-        <v>57310</v>
+        <v>78526</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2838,39 +2838,34 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Rymån, Dlr</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>453803</v>
+        <v>453796</v>
       </c>
       <c r="R23" t="n">
-        <v>6807752</v>
+        <v>6808121</v>
       </c>
       <c r="S23" t="n">
         <v>15</v>
@@ -2929,10 +2924,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>119591007</v>
+        <v>119591035</v>
       </c>
       <c r="B24" t="n">
-        <v>57310</v>
+        <v>78526</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -2945,29 +2940,24 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Rymån, Dlr</t>
@@ -2977,7 +2967,7 @@
         <v>453808</v>
       </c>
       <c r="R24" t="n">
-        <v>6808114</v>
+        <v>6807890</v>
       </c>
       <c r="S24" t="n">
         <v>15</v>
@@ -3010,11 +3000,6 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2024-09-06</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Färska ringhack (gran)</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3041,10 +3026,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>119591026</v>
+        <v>119590982</v>
       </c>
       <c r="B25" t="n">
-        <v>78262</v>
+        <v>79144</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3057,21 +3042,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3081,10 +3066,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>453770</v>
+        <v>453794</v>
       </c>
       <c r="R25" t="n">
-        <v>6807987</v>
+        <v>6807980</v>
       </c>
       <c r="S25" t="n">
         <v>15</v>
@@ -3143,10 +3128,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>119591080</v>
+        <v>119590990</v>
       </c>
       <c r="B26" t="n">
-        <v>78526</v>
+        <v>57310</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3159,34 +3144,39 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Rymån, Dlr</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>453829</v>
+        <v>453803</v>
       </c>
       <c r="R26" t="n">
-        <v>6808069</v>
+        <v>6807752</v>
       </c>
       <c r="S26" t="n">
         <v>15</v>
@@ -3245,10 +3235,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>119591047</v>
+        <v>119591007</v>
       </c>
       <c r="B27" t="n">
-        <v>78526</v>
+        <v>57310</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3261,34 +3251,39 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Rymån, Dlr</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>453785</v>
+        <v>453808</v>
       </c>
       <c r="R27" t="n">
-        <v>6807890</v>
+        <v>6808114</v>
       </c>
       <c r="S27" t="n">
         <v>15</v>
@@ -3321,6 +3316,11 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2024-09-06</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Färska ringhack (gran)</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3347,10 +3347,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>119591037</v>
+        <v>119591026</v>
       </c>
       <c r="B28" t="n">
-        <v>78526</v>
+        <v>78262</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3363,21 +3363,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3387,10 +3387,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>453829</v>
+        <v>453770</v>
       </c>
       <c r="R28" t="n">
-        <v>6807768</v>
+        <v>6807987</v>
       </c>
       <c r="S28" t="n">
         <v>15</v>
@@ -3449,7 +3449,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>119591074</v>
+        <v>119591047</v>
       </c>
       <c r="B29" t="n">
         <v>78526</v>
@@ -3489,10 +3489,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>453796</v>
+        <v>453785</v>
       </c>
       <c r="R29" t="n">
-        <v>6808121</v>
+        <v>6807890</v>
       </c>
       <c r="S29" t="n">
         <v>15</v>
@@ -3551,7 +3551,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>119591035</v>
+        <v>119591037</v>
       </c>
       <c r="B30" t="n">
         <v>78526</v>
@@ -3591,10 +3591,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>453808</v>
+        <v>453829</v>
       </c>
       <c r="R30" t="n">
-        <v>6807890</v>
+        <v>6807768</v>
       </c>
       <c r="S30" t="n">
         <v>15</v>
@@ -3653,10 +3653,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>119590982</v>
+        <v>119591080</v>
       </c>
       <c r="B31" t="n">
-        <v>79144</v>
+        <v>78526</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3669,21 +3669,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3693,10 +3693,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>453794</v>
+        <v>453829</v>
       </c>
       <c r="R31" t="n">
-        <v>6807980</v>
+        <v>6808069</v>
       </c>
       <c r="S31" t="n">
         <v>15</v>
@@ -7461,10 +7461,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>119591058</v>
+        <v>119590978</v>
       </c>
       <c r="B68" t="n">
-        <v>78526</v>
+        <v>79144</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -7477,21 +7477,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7501,10 +7501,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>453734</v>
+        <v>453823</v>
       </c>
       <c r="R68" t="n">
-        <v>6808007</v>
+        <v>6807778</v>
       </c>
       <c r="S68" t="n">
         <v>15</v>
@@ -7563,10 +7563,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>119591004</v>
+        <v>119590996</v>
       </c>
       <c r="B69" t="n">
-        <v>91884</v>
+        <v>57463</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -7579,21 +7579,21 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>5449</v>
+        <v>103021</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7603,10 +7603,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>453785</v>
+        <v>453750</v>
       </c>
       <c r="R69" t="n">
-        <v>6808062</v>
+        <v>6807861</v>
       </c>
       <c r="S69" t="n">
         <v>15</v>
@@ -7665,10 +7665,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>119591032</v>
+        <v>119591012</v>
       </c>
       <c r="B70" t="n">
-        <v>78526</v>
+        <v>96862</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -7677,25 +7677,25 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7705,10 +7705,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>453897</v>
+        <v>453875</v>
       </c>
       <c r="R70" t="n">
-        <v>6808009</v>
+        <v>6808094</v>
       </c>
       <c r="S70" t="n">
         <v>15</v>
@@ -7767,10 +7767,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>119590978</v>
+        <v>119591004</v>
       </c>
       <c r="B71" t="n">
-        <v>79144</v>
+        <v>91884</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -7783,21 +7783,21 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6453</v>
+        <v>5449</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -7807,10 +7807,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>453823</v>
+        <v>453785</v>
       </c>
       <c r="R71" t="n">
-        <v>6807778</v>
+        <v>6808062</v>
       </c>
       <c r="S71" t="n">
         <v>15</v>
@@ -7869,10 +7869,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>119590996</v>
+        <v>119591032</v>
       </c>
       <c r="B72" t="n">
-        <v>57463</v>
+        <v>78526</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -7885,21 +7885,21 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -7909,10 +7909,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>453750</v>
+        <v>453897</v>
       </c>
       <c r="R72" t="n">
-        <v>6807861</v>
+        <v>6808009</v>
       </c>
       <c r="S72" t="n">
         <v>15</v>
@@ -7971,10 +7971,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>119591012</v>
+        <v>119591058</v>
       </c>
       <c r="B73" t="n">
-        <v>96862</v>
+        <v>78526</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -7983,25 +7983,25 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -8011,10 +8011,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>453875</v>
+        <v>453734</v>
       </c>
       <c r="R73" t="n">
-        <v>6808094</v>
+        <v>6808007</v>
       </c>
       <c r="S73" t="n">
         <v>15</v>
@@ -9837,10 +9837,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>119590974</v>
+        <v>119591062</v>
       </c>
       <c r="B91" t="n">
-        <v>95455</v>
+        <v>78526</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
@@ -9853,21 +9853,21 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>53</v>
+        <v>6425</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -9877,10 +9877,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>453852</v>
+        <v>453761</v>
       </c>
       <c r="R91" t="n">
-        <v>6807959</v>
+        <v>6808000</v>
       </c>
       <c r="S91" t="n">
         <v>15</v>
@@ -9939,10 +9939,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>119590991</v>
+        <v>119591069</v>
       </c>
       <c r="B92" t="n">
-        <v>57310</v>
+        <v>78526</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
@@ -9955,39 +9955,34 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
-      <c r="M92" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P92" t="inlineStr">
         <is>
           <t>Rymån, Dlr</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>453887</v>
+        <v>453756</v>
       </c>
       <c r="R92" t="n">
-        <v>6808050</v>
+        <v>6808048</v>
       </c>
       <c r="S92" t="n">
         <v>15</v>
@@ -10046,7 +10041,7 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>119591062</v>
+        <v>119591043</v>
       </c>
       <c r="B93" t="n">
         <v>78526</v>
@@ -10086,10 +10081,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>453761</v>
+        <v>453774</v>
       </c>
       <c r="R93" t="n">
-        <v>6808000</v>
+        <v>6807849</v>
       </c>
       <c r="S93" t="n">
         <v>15</v>
@@ -10148,7 +10143,7 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>119591069</v>
+        <v>119591054</v>
       </c>
       <c r="B94" t="n">
         <v>78526</v>
@@ -10188,10 +10183,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>453756</v>
+        <v>453738</v>
       </c>
       <c r="R94" t="n">
-        <v>6808048</v>
+        <v>6807973</v>
       </c>
       <c r="S94" t="n">
         <v>15</v>
@@ -10250,10 +10245,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>119591043</v>
+        <v>119591023</v>
       </c>
       <c r="B95" t="n">
-        <v>78526</v>
+        <v>78263</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
@@ -10266,21 +10261,21 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -10290,10 +10285,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>453774</v>
+        <v>453770</v>
       </c>
       <c r="R95" t="n">
-        <v>6807849</v>
+        <v>6807984</v>
       </c>
       <c r="S95" t="n">
         <v>15</v>
@@ -10352,10 +10347,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>119591054</v>
+        <v>119590974</v>
       </c>
       <c r="B96" t="n">
-        <v>78526</v>
+        <v>95455</v>
       </c>
       <c r="C96" t="inlineStr">
         <is>
@@ -10368,21 +10363,21 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>6425</v>
+        <v>53</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -10392,10 +10387,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>453738</v>
+        <v>453852</v>
       </c>
       <c r="R96" t="n">
-        <v>6807973</v>
+        <v>6807959</v>
       </c>
       <c r="S96" t="n">
         <v>15</v>
@@ -10454,10 +10449,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>119591023</v>
+        <v>119590991</v>
       </c>
       <c r="B97" t="n">
-        <v>78263</v>
+        <v>57310</v>
       </c>
       <c r="C97" t="inlineStr">
         <is>
@@ -10470,34 +10465,39 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>228912</v>
+        <v>100109</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
+      <c r="M97" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P97" t="inlineStr">
         <is>
           <t>Rymån, Dlr</t>
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>453770</v>
+        <v>453887</v>
       </c>
       <c r="R97" t="n">
-        <v>6807984</v>
+        <v>6808050</v>
       </c>
       <c r="S97" t="n">
         <v>15</v>

--- a/artfynd/A 31144-2024 artfynd.xlsx
+++ b/artfynd/A 31144-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119590985</v>
+        <v>119591076</v>
       </c>
       <c r="B2" t="n">
-        <v>90562</v>
+        <v>78526</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>453839</v>
+        <v>453811</v>
       </c>
       <c r="R2" t="n">
-        <v>6807828</v>
+        <v>6808106</v>
       </c>
       <c r="S2" t="n">
         <v>15</v>
@@ -777,7 +777,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119591072</v>
+        <v>119591084</v>
       </c>
       <c r="B3" t="n">
         <v>78526</v>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>453773</v>
+        <v>453835</v>
       </c>
       <c r="R3" t="n">
-        <v>6808107</v>
+        <v>6808031</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -847,12 +847,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2024-09-06</t>
+          <t>2024-09-04</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2024-09-06</t>
+          <t>2024-09-04</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -879,7 +879,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119591049</v>
+        <v>119591037</v>
       </c>
       <c r="B4" t="n">
         <v>78526</v>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>453796</v>
+        <v>453829</v>
       </c>
       <c r="R4" t="n">
-        <v>6807942</v>
+        <v>6807768</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119591044</v>
+        <v>119590980</v>
       </c>
       <c r="B5" t="n">
-        <v>78526</v>
+        <v>79144</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -997,21 +997,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>453764</v>
+        <v>453791</v>
       </c>
       <c r="R5" t="n">
-        <v>6807870</v>
+        <v>6807707</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1083,7 +1083,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119591041</v>
+        <v>119591067</v>
       </c>
       <c r="B6" t="n">
         <v>78526</v>
@@ -1123,10 +1123,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>453773</v>
+        <v>453775</v>
       </c>
       <c r="R6" t="n">
-        <v>6807791</v>
+        <v>6808032</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1185,7 +1185,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119591045</v>
+        <v>119591040</v>
       </c>
       <c r="B7" t="n">
         <v>78526</v>
@@ -1225,10 +1225,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>453764</v>
+        <v>453808</v>
       </c>
       <c r="R7" t="n">
-        <v>6807871</v>
+        <v>6807761</v>
       </c>
       <c r="S7" t="n">
         <v>15</v>
@@ -1287,10 +1287,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119590979</v>
+        <v>119591101</v>
       </c>
       <c r="B8" t="n">
-        <v>79144</v>
+        <v>5169</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1299,25 +1299,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6453</v>
+        <v>100526</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1327,10 +1327,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>453807</v>
+        <v>453849</v>
       </c>
       <c r="R8" t="n">
-        <v>6807719</v>
+        <v>6807844</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1389,10 +1389,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>119590977</v>
+        <v>119591083</v>
       </c>
       <c r="B9" t="n">
-        <v>79144</v>
+        <v>78526</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1405,21 +1405,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1429,10 +1429,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>453807</v>
+        <v>453848</v>
       </c>
       <c r="R9" t="n">
-        <v>6807916</v>
+        <v>6808029</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1491,7 +1491,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>119591057</v>
+        <v>119591077</v>
       </c>
       <c r="B10" t="n">
         <v>78526</v>
@@ -1531,10 +1531,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>453736</v>
+        <v>453815</v>
       </c>
       <c r="R10" t="n">
-        <v>6808004</v>
+        <v>6808130</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>
@@ -1593,10 +1593,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>119591028</v>
+        <v>119591039</v>
       </c>
       <c r="B11" t="n">
-        <v>90580</v>
+        <v>78526</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1609,21 +1609,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1633,10 +1633,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>453791</v>
+        <v>453790</v>
       </c>
       <c r="R11" t="n">
-        <v>6807765</v>
+        <v>6807766</v>
       </c>
       <c r="S11" t="n">
         <v>15</v>
@@ -1669,11 +1669,6 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2024-09-06</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Gamla fruktkroppar</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1700,10 +1695,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>119591067</v>
+        <v>119591015</v>
       </c>
       <c r="B12" t="n">
-        <v>78526</v>
+        <v>79635</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1712,25 +1707,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>6461</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1740,10 +1735,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>453775</v>
+        <v>453820</v>
       </c>
       <c r="R12" t="n">
-        <v>6808032</v>
+        <v>6808064</v>
       </c>
       <c r="S12" t="n">
         <v>15</v>
@@ -1802,10 +1797,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>119590994</v>
+        <v>119591045</v>
       </c>
       <c r="B13" t="n">
-        <v>103418</v>
+        <v>78526</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1814,25 +1809,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>222412</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1842,10 +1837,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>453893</v>
+        <v>453764</v>
       </c>
       <c r="R13" t="n">
-        <v>6808027</v>
+        <v>6807871</v>
       </c>
       <c r="S13" t="n">
         <v>15</v>
@@ -1904,10 +1899,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>119590986</v>
+        <v>119591080</v>
       </c>
       <c r="B14" t="n">
-        <v>90562</v>
+        <v>78526</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1920,21 +1915,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1944,10 +1939,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>453795</v>
+        <v>453829</v>
       </c>
       <c r="R14" t="n">
-        <v>6807770</v>
+        <v>6808069</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -2006,10 +2001,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>119591033</v>
+        <v>119591031</v>
       </c>
       <c r="B15" t="n">
-        <v>78526</v>
+        <v>90580</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2022,21 +2017,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2046,10 +2041,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>453835</v>
+        <v>453886</v>
       </c>
       <c r="R15" t="n">
-        <v>6807974</v>
+        <v>6808055</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2108,10 +2103,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>119591029</v>
+        <v>119591025</v>
       </c>
       <c r="B16" t="n">
-        <v>90580</v>
+        <v>93935</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2120,25 +2115,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>5432</v>
+        <v>2387</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Källpraktmossa</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Pseudobryum cinclidioides</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Huebener) T.J.Kop.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2148,10 +2143,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>453861</v>
+        <v>453851</v>
       </c>
       <c r="R16" t="n">
-        <v>6807970</v>
+        <v>6807838</v>
       </c>
       <c r="S16" t="n">
         <v>15</v>
@@ -2210,10 +2205,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>119591077</v>
+        <v>119590972</v>
       </c>
       <c r="B17" t="n">
-        <v>78526</v>
+        <v>74638</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2226,21 +2221,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2250,10 +2245,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>453815</v>
+        <v>453874</v>
       </c>
       <c r="R17" t="n">
-        <v>6808130</v>
+        <v>6808094</v>
       </c>
       <c r="S17" t="n">
         <v>15</v>
@@ -2312,7 +2307,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>119591051</v>
+        <v>119591033</v>
       </c>
       <c r="B18" t="n">
         <v>78526</v>
@@ -2352,10 +2347,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>453755</v>
+        <v>453835</v>
       </c>
       <c r="R18" t="n">
-        <v>6807941</v>
+        <v>6807974</v>
       </c>
       <c r="S18" t="n">
         <v>15</v>
@@ -2414,10 +2409,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>119590995</v>
+        <v>119591059</v>
       </c>
       <c r="B19" t="n">
-        <v>103418</v>
+        <v>78526</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2426,25 +2421,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>222412</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2454,10 +2449,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>453897</v>
+        <v>453737</v>
       </c>
       <c r="R19" t="n">
-        <v>6808024</v>
+        <v>6808007</v>
       </c>
       <c r="S19" t="n">
         <v>15</v>
@@ -2516,10 +2511,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>119591060</v>
+        <v>119590990</v>
       </c>
       <c r="B20" t="n">
-        <v>78526</v>
+        <v>57310</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2532,34 +2527,39 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Rymån, Dlr</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>453748</v>
+        <v>453803</v>
       </c>
       <c r="R20" t="n">
-        <v>6808003</v>
+        <v>6807752</v>
       </c>
       <c r="S20" t="n">
         <v>15</v>
@@ -2618,10 +2618,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>119591048</v>
+        <v>119591028</v>
       </c>
       <c r="B21" t="n">
-        <v>78526</v>
+        <v>90580</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2634,21 +2634,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2658,10 +2658,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>453788</v>
+        <v>453791</v>
       </c>
       <c r="R21" t="n">
-        <v>6807903</v>
+        <v>6807765</v>
       </c>
       <c r="S21" t="n">
         <v>15</v>
@@ -2694,6 +2694,11 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2024-09-06</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Gamla fruktkroppar</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2720,10 +2725,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>119591015</v>
+        <v>119591004</v>
       </c>
       <c r="B22" t="n">
-        <v>79635</v>
+        <v>91884</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2732,25 +2737,25 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6461</v>
+        <v>5449</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2760,10 +2765,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>453820</v>
+        <v>453785</v>
       </c>
       <c r="R22" t="n">
-        <v>6808064</v>
+        <v>6808062</v>
       </c>
       <c r="S22" t="n">
         <v>15</v>
@@ -2822,10 +2827,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>119591074</v>
+        <v>119591011</v>
       </c>
       <c r="B23" t="n">
-        <v>78526</v>
+        <v>96862</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2834,25 +2839,25 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2862,10 +2867,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>453796</v>
+        <v>453903</v>
       </c>
       <c r="R23" t="n">
-        <v>6808121</v>
+        <v>6807986</v>
       </c>
       <c r="S23" t="n">
         <v>15</v>
@@ -2924,10 +2929,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>119591035</v>
+        <v>119590996</v>
       </c>
       <c r="B24" t="n">
-        <v>78526</v>
+        <v>57463</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -2940,21 +2945,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2964,10 +2969,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>453808</v>
+        <v>453750</v>
       </c>
       <c r="R24" t="n">
-        <v>6807890</v>
+        <v>6807861</v>
       </c>
       <c r="S24" t="n">
         <v>15</v>
@@ -3026,10 +3031,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>119590982</v>
+        <v>119590987</v>
       </c>
       <c r="B25" t="n">
-        <v>79144</v>
+        <v>90562</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3042,21 +3047,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6453</v>
+        <v>1202</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3066,10 +3071,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>453794</v>
+        <v>453772</v>
       </c>
       <c r="R25" t="n">
-        <v>6807980</v>
+        <v>6807796</v>
       </c>
       <c r="S25" t="n">
         <v>15</v>
@@ -3128,10 +3133,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>119590990</v>
+        <v>119591068</v>
       </c>
       <c r="B26" t="n">
-        <v>57310</v>
+        <v>78526</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3144,39 +3149,34 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Rymån, Dlr</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>453803</v>
+        <v>453770</v>
       </c>
       <c r="R26" t="n">
-        <v>6807752</v>
+        <v>6808029</v>
       </c>
       <c r="S26" t="n">
         <v>15</v>
@@ -3235,10 +3235,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>119591007</v>
+        <v>119591074</v>
       </c>
       <c r="B27" t="n">
-        <v>57310</v>
+        <v>78526</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3251,39 +3251,34 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Rymån, Dlr</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>453808</v>
+        <v>453796</v>
       </c>
       <c r="R27" t="n">
-        <v>6808114</v>
+        <v>6808121</v>
       </c>
       <c r="S27" t="n">
         <v>15</v>
@@ -3316,11 +3311,6 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2024-09-06</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>Färska ringhack (gran)</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3347,10 +3337,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>119591026</v>
+        <v>119591082</v>
       </c>
       <c r="B28" t="n">
-        <v>78262</v>
+        <v>78526</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3363,21 +3353,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3387,10 +3377,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>453770</v>
+        <v>453850</v>
       </c>
       <c r="R28" t="n">
-        <v>6807987</v>
+        <v>6808037</v>
       </c>
       <c r="S28" t="n">
         <v>15</v>
@@ -3449,10 +3439,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>119591047</v>
+        <v>119590977</v>
       </c>
       <c r="B29" t="n">
-        <v>78526</v>
+        <v>79144</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3465,21 +3455,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3489,10 +3479,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>453785</v>
+        <v>453807</v>
       </c>
       <c r="R29" t="n">
-        <v>6807890</v>
+        <v>6807916</v>
       </c>
       <c r="S29" t="n">
         <v>15</v>
@@ -3551,10 +3541,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>119591037</v>
+        <v>119590969</v>
       </c>
       <c r="B30" t="n">
-        <v>78526</v>
+        <v>57310</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3567,34 +3557,39 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Rymån, Dlr</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>453829</v>
+        <v>453847</v>
       </c>
       <c r="R30" t="n">
-        <v>6807768</v>
+        <v>6807830</v>
       </c>
       <c r="S30" t="n">
         <v>15</v>
@@ -3627,6 +3622,11 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2024-09-06</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Försett med naturvårdssnitsel</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3653,10 +3653,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>119591080</v>
+        <v>119591010</v>
       </c>
       <c r="B31" t="n">
-        <v>78526</v>
+        <v>57310</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3669,34 +3669,39 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Rymån, Dlr</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>453829</v>
+        <v>453805</v>
       </c>
       <c r="R31" t="n">
-        <v>6808069</v>
+        <v>6808118</v>
       </c>
       <c r="S31" t="n">
         <v>15</v>
@@ -3723,12 +3728,17 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2024-09-06</t>
+          <t>2024-09-04</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2024-09-06</t>
+          <t>2024-09-04</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>Färska ringhack (gran)</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3755,7 +3765,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>119591065</v>
+        <v>119591051</v>
       </c>
       <c r="B32" t="n">
         <v>78526</v>
@@ -3795,10 +3805,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>453782</v>
+        <v>453755</v>
       </c>
       <c r="R32" t="n">
-        <v>6807982</v>
+        <v>6807941</v>
       </c>
       <c r="S32" t="n">
         <v>15</v>
@@ -3857,7 +3867,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>119591068</v>
+        <v>119591072</v>
       </c>
       <c r="B33" t="n">
         <v>78526</v>
@@ -3897,10 +3907,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>453770</v>
+        <v>453773</v>
       </c>
       <c r="R33" t="n">
-        <v>6808029</v>
+        <v>6808107</v>
       </c>
       <c r="S33" t="n">
         <v>15</v>
@@ -3959,10 +3969,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>119591097</v>
+        <v>119591047</v>
       </c>
       <c r="B34" t="n">
-        <v>57310</v>
+        <v>78526</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -3975,39 +3985,34 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P34" t="inlineStr">
         <is>
           <t>Rymån, Dlr</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>453849</v>
+        <v>453785</v>
       </c>
       <c r="R34" t="n">
-        <v>6807844</v>
+        <v>6807890</v>
       </c>
       <c r="S34" t="n">
         <v>15</v>
@@ -4066,7 +4071,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>119591073</v>
+        <v>119591057</v>
       </c>
       <c r="B35" t="n">
         <v>78526</v>
@@ -4106,10 +4111,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>453797</v>
+        <v>453736</v>
       </c>
       <c r="R35" t="n">
-        <v>6808117</v>
+        <v>6808004</v>
       </c>
       <c r="S35" t="n">
         <v>15</v>
@@ -4168,7 +4173,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>119591084</v>
+        <v>119591060</v>
       </c>
       <c r="B36" t="n">
         <v>78526</v>
@@ -4208,10 +4213,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>453835</v>
+        <v>453748</v>
       </c>
       <c r="R36" t="n">
-        <v>6808031</v>
+        <v>6808003</v>
       </c>
       <c r="S36" t="n">
         <v>15</v>
@@ -4238,12 +4243,12 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2024-09-04</t>
+          <t>2024-09-06</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2024-09-04</t>
+          <t>2024-09-06</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4270,10 +4275,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>119591039</v>
+        <v>119590983</v>
       </c>
       <c r="B37" t="n">
-        <v>78526</v>
+        <v>79144</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4286,21 +4291,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4310,10 +4315,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>453790</v>
+        <v>453762</v>
       </c>
       <c r="R37" t="n">
-        <v>6807766</v>
+        <v>6808048</v>
       </c>
       <c r="S37" t="n">
         <v>15</v>
@@ -4372,10 +4377,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>119591096</v>
+        <v>119591097</v>
       </c>
       <c r="B38" t="n">
-        <v>78526</v>
+        <v>57310</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4388,34 +4393,39 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P38" t="inlineStr">
         <is>
           <t>Rymån, Dlr</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>453898</v>
+        <v>453849</v>
       </c>
       <c r="R38" t="n">
-        <v>6808089</v>
+        <v>6807844</v>
       </c>
       <c r="S38" t="n">
         <v>15</v>
@@ -4474,10 +4484,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>119591101</v>
+        <v>119591009</v>
       </c>
       <c r="B39" t="n">
-        <v>5169</v>
+        <v>57310</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4486,38 +4496,43 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100526</v>
+        <v>100109</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P39" t="inlineStr">
         <is>
           <t>Rymån, Dlr</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>453849</v>
+        <v>453815</v>
       </c>
       <c r="R39" t="n">
-        <v>6807844</v>
+        <v>6808098</v>
       </c>
       <c r="S39" t="n">
         <v>15</v>
@@ -4550,6 +4565,11 @@
       <c r="AA39" t="inlineStr">
         <is>
           <t>2024-09-06</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>Färska ringhack (gran)</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4576,10 +4596,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>119591083</v>
+        <v>119591022</v>
       </c>
       <c r="B40" t="n">
-        <v>78526</v>
+        <v>78263</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4592,21 +4612,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4616,10 +4636,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>453848</v>
+        <v>453759</v>
       </c>
       <c r="R40" t="n">
-        <v>6808029</v>
+        <v>6807967</v>
       </c>
       <c r="S40" t="n">
         <v>15</v>
@@ -4678,10 +4698,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>119591076</v>
+        <v>119591012</v>
       </c>
       <c r="B41" t="n">
-        <v>78526</v>
+        <v>96862</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4690,25 +4710,25 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4718,10 +4738,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>453811</v>
+        <v>453875</v>
       </c>
       <c r="R41" t="n">
-        <v>6808106</v>
+        <v>6808094</v>
       </c>
       <c r="S41" t="n">
         <v>15</v>
@@ -4780,7 +4800,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>119591091</v>
+        <v>119591088</v>
       </c>
       <c r="B42" t="n">
         <v>78526</v>
@@ -4820,10 +4840,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>453798</v>
+        <v>453778</v>
       </c>
       <c r="R42" t="n">
-        <v>6808108</v>
+        <v>6808053</v>
       </c>
       <c r="S42" t="n">
         <v>15</v>
@@ -4882,10 +4902,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>119591050</v>
+        <v>119591026</v>
       </c>
       <c r="B43" t="n">
-        <v>78526</v>
+        <v>78262</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -4898,21 +4918,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4922,10 +4942,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>453782</v>
+        <v>453770</v>
       </c>
       <c r="R43" t="n">
-        <v>6807956</v>
+        <v>6807987</v>
       </c>
       <c r="S43" t="n">
         <v>15</v>
@@ -4984,7 +5004,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>119591055</v>
+        <v>119591046</v>
       </c>
       <c r="B44" t="n">
         <v>78526</v>
@@ -5024,10 +5044,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>453747</v>
+        <v>453792</v>
       </c>
       <c r="R44" t="n">
-        <v>6807979</v>
+        <v>6807881</v>
       </c>
       <c r="S44" t="n">
         <v>15</v>
@@ -5086,7 +5106,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>119591088</v>
+        <v>119591061</v>
       </c>
       <c r="B45" t="n">
         <v>78526</v>
@@ -5126,10 +5146,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>453778</v>
+        <v>453756</v>
       </c>
       <c r="R45" t="n">
-        <v>6808053</v>
+        <v>6808003</v>
       </c>
       <c r="S45" t="n">
         <v>15</v>
@@ -5156,12 +5176,12 @@
       </c>
       <c r="Y45" t="inlineStr">
         <is>
-          <t>2024-09-04</t>
+          <t>2024-09-06</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>2024-09-04</t>
+          <t>2024-09-06</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5188,7 +5208,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>119591085</v>
+        <v>119591049</v>
       </c>
       <c r="B46" t="n">
         <v>78526</v>
@@ -5228,10 +5248,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>453830</v>
+        <v>453796</v>
       </c>
       <c r="R46" t="n">
-        <v>6808029</v>
+        <v>6807942</v>
       </c>
       <c r="S46" t="n">
         <v>15</v>
@@ -5258,12 +5278,12 @@
       </c>
       <c r="Y46" t="inlineStr">
         <is>
-          <t>2024-09-04</t>
+          <t>2024-09-06</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>2024-09-04</t>
+          <t>2024-09-06</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5290,7 +5310,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>119591038</v>
+        <v>119591070</v>
       </c>
       <c r="B47" t="n">
         <v>78526</v>
@@ -5330,10 +5350,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>453826</v>
+        <v>453759</v>
       </c>
       <c r="R47" t="n">
-        <v>6807750</v>
+        <v>6808051</v>
       </c>
       <c r="S47" t="n">
         <v>15</v>
@@ -5392,10 +5412,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>119591046</v>
+        <v>119590975</v>
       </c>
       <c r="B48" t="n">
-        <v>78526</v>
+        <v>79144</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5408,21 +5428,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5432,10 +5452,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>453792</v>
+        <v>453828</v>
       </c>
       <c r="R48" t="n">
-        <v>6807881</v>
+        <v>6807944</v>
       </c>
       <c r="S48" t="n">
         <v>15</v>
@@ -5494,10 +5514,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>119591006</v>
+        <v>119591041</v>
       </c>
       <c r="B49" t="n">
-        <v>57310</v>
+        <v>78526</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5510,39 +5530,34 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
-      <c r="M49" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P49" t="inlineStr">
         <is>
           <t>Rymån, Dlr</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>453796</v>
+        <v>453773</v>
       </c>
       <c r="R49" t="n">
-        <v>6808114</v>
+        <v>6807791</v>
       </c>
       <c r="S49" t="n">
         <v>15</v>
@@ -5575,11 +5590,6 @@
       <c r="AA49" t="inlineStr">
         <is>
           <t>2024-09-06</t>
-        </is>
-      </c>
-      <c r="AC49" t="inlineStr">
-        <is>
-          <t>Färska ringhack (gran)</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5606,10 +5616,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>119590997</v>
+        <v>119591075</v>
       </c>
       <c r="B50" t="n">
-        <v>57463</v>
+        <v>78526</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5622,21 +5632,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5646,10 +5656,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>453806</v>
+        <v>453809</v>
       </c>
       <c r="R50" t="n">
-        <v>6808118</v>
+        <v>6808107</v>
       </c>
       <c r="S50" t="n">
         <v>15</v>
@@ -5708,10 +5718,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>119591025</v>
+        <v>119590999</v>
       </c>
       <c r="B51" t="n">
-        <v>93935</v>
+        <v>91463</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -5720,25 +5730,25 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>2387</v>
+        <v>4745</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Källpraktmossa</t>
+          <t>Tallriska</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Pseudobryum cinclidioides</t>
+          <t>Lactarius musteus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Huebener) T.J.Kop.</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5748,10 +5758,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>453851</v>
+        <v>453793</v>
       </c>
       <c r="R51" t="n">
-        <v>6807838</v>
+        <v>6808029</v>
       </c>
       <c r="S51" t="n">
         <v>15</v>
@@ -5778,12 +5788,12 @@
       </c>
       <c r="Y51" t="inlineStr">
         <is>
-          <t>2024-09-06</t>
+          <t>2024-09-04</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>2024-09-06</t>
+          <t>2024-09-04</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -5810,10 +5820,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>119590987</v>
+        <v>119590976</v>
       </c>
       <c r="B52" t="n">
-        <v>90562</v>
+        <v>79144</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -5826,21 +5836,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>1202</v>
+        <v>6453</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5850,10 +5860,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>453772</v>
+        <v>453836</v>
       </c>
       <c r="R52" t="n">
-        <v>6807796</v>
+        <v>6807943</v>
       </c>
       <c r="S52" t="n">
         <v>15</v>
@@ -5912,7 +5922,7 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>119591042</v>
+        <v>119591058</v>
       </c>
       <c r="B53" t="n">
         <v>78526</v>
@@ -5952,10 +5962,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>453788</v>
+        <v>453734</v>
       </c>
       <c r="R53" t="n">
-        <v>6807792</v>
+        <v>6808007</v>
       </c>
       <c r="S53" t="n">
         <v>15</v>
@@ -6014,10 +6024,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>119590976</v>
+        <v>119591091</v>
       </c>
       <c r="B54" t="n">
-        <v>79144</v>
+        <v>78526</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6030,21 +6040,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6054,10 +6064,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>453836</v>
+        <v>453798</v>
       </c>
       <c r="R54" t="n">
-        <v>6807943</v>
+        <v>6808108</v>
       </c>
       <c r="S54" t="n">
         <v>15</v>
@@ -6084,12 +6094,12 @@
       </c>
       <c r="Y54" t="inlineStr">
         <is>
-          <t>2024-09-06</t>
+          <t>2024-09-04</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
         <is>
-          <t>2024-09-06</t>
+          <t>2024-09-04</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6116,7 +6126,7 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>119591034</v>
+        <v>119591044</v>
       </c>
       <c r="B55" t="n">
         <v>78526</v>
@@ -6156,10 +6166,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>453825</v>
+        <v>453764</v>
       </c>
       <c r="R55" t="n">
-        <v>6807960</v>
+        <v>6807870</v>
       </c>
       <c r="S55" t="n">
         <v>15</v>
@@ -6320,10 +6330,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>119591064</v>
+        <v>119591030</v>
       </c>
       <c r="B57" t="n">
-        <v>78526</v>
+        <v>90580</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6336,21 +6346,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6360,10 +6370,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>453761</v>
+        <v>453779</v>
       </c>
       <c r="R57" t="n">
-        <v>6807996</v>
+        <v>6807856</v>
       </c>
       <c r="S57" t="n">
         <v>15</v>
@@ -6422,7 +6432,7 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>119591089</v>
+        <v>119591090</v>
       </c>
       <c r="B58" t="n">
         <v>78526</v>
@@ -6462,10 +6472,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>453780</v>
+        <v>453794</v>
       </c>
       <c r="R58" t="n">
-        <v>6808055</v>
+        <v>6808097</v>
       </c>
       <c r="S58" t="n">
         <v>15</v>
@@ -6524,10 +6534,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>119591030</v>
+        <v>119591053</v>
       </c>
       <c r="B59" t="n">
-        <v>90580</v>
+        <v>78526</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -6540,21 +6550,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6564,10 +6574,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>453779</v>
+        <v>453752</v>
       </c>
       <c r="R59" t="n">
-        <v>6807856</v>
+        <v>6807968</v>
       </c>
       <c r="S59" t="n">
         <v>15</v>
@@ -6626,10 +6636,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>119591010</v>
+        <v>119591062</v>
       </c>
       <c r="B60" t="n">
-        <v>57310</v>
+        <v>78526</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -6642,39 +6652,34 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
-      <c r="M60" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P60" t="inlineStr">
         <is>
           <t>Rymån, Dlr</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>453805</v>
+        <v>453761</v>
       </c>
       <c r="R60" t="n">
-        <v>6808118</v>
+        <v>6808000</v>
       </c>
       <c r="S60" t="n">
         <v>15</v>
@@ -6701,17 +6706,12 @@
       </c>
       <c r="Y60" t="inlineStr">
         <is>
-          <t>2024-09-04</t>
+          <t>2024-09-06</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
         <is>
-          <t>2024-09-04</t>
-        </is>
-      </c>
-      <c r="AC60" t="inlineStr">
-        <is>
-          <t>Färska ringhack (gran)</t>
+          <t>2024-09-06</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -6738,10 +6738,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>119591053</v>
+        <v>119590991</v>
       </c>
       <c r="B61" t="n">
-        <v>78526</v>
+        <v>57310</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -6754,34 +6754,39 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P61" t="inlineStr">
         <is>
           <t>Rymån, Dlr</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>453752</v>
+        <v>453887</v>
       </c>
       <c r="R61" t="n">
-        <v>6807968</v>
+        <v>6808050</v>
       </c>
       <c r="S61" t="n">
         <v>15</v>
@@ -6840,7 +6845,7 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>119591075</v>
+        <v>119591032</v>
       </c>
       <c r="B62" t="n">
         <v>78526</v>
@@ -6880,10 +6885,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>453809</v>
+        <v>453897</v>
       </c>
       <c r="R62" t="n">
-        <v>6808107</v>
+        <v>6808009</v>
       </c>
       <c r="S62" t="n">
         <v>15</v>
@@ -6942,7 +6947,7 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>119591082</v>
+        <v>119591056</v>
       </c>
       <c r="B63" t="n">
         <v>78526</v>
@@ -6982,10 +6987,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>453850</v>
+        <v>453742</v>
       </c>
       <c r="R63" t="n">
-        <v>6808037</v>
+        <v>6807994</v>
       </c>
       <c r="S63" t="n">
         <v>15</v>
@@ -7044,7 +7049,7 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>119591040</v>
+        <v>119591043</v>
       </c>
       <c r="B64" t="n">
         <v>78526</v>
@@ -7084,10 +7089,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>453808</v>
+        <v>453774</v>
       </c>
       <c r="R64" t="n">
-        <v>6807761</v>
+        <v>6807849</v>
       </c>
       <c r="S64" t="n">
         <v>15</v>
@@ -7146,10 +7151,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>119591036</v>
+        <v>119590997</v>
       </c>
       <c r="B65" t="n">
-        <v>78526</v>
+        <v>57463</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7162,21 +7167,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7186,10 +7191,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>453849</v>
+        <v>453806</v>
       </c>
       <c r="R65" t="n">
-        <v>6807844</v>
+        <v>6808118</v>
       </c>
       <c r="S65" t="n">
         <v>15</v>
@@ -7248,10 +7253,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>119591019</v>
+        <v>119591065</v>
       </c>
       <c r="B66" t="n">
-        <v>96865</v>
+        <v>78526</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7260,47 +7265,38 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>221946</v>
+        <v>6425</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Mattlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Lycopodium clavatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I66" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J66" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
           <t>Rymån, Dlr</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>453836</v>
+        <v>453782</v>
       </c>
       <c r="R66" t="n">
-        <v>6807799</v>
+        <v>6807982</v>
       </c>
       <c r="S66" t="n">
         <v>15</v>
@@ -7359,7 +7355,7 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>119590975</v>
+        <v>119590982</v>
       </c>
       <c r="B67" t="n">
         <v>79144</v>
@@ -7399,10 +7395,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>453828</v>
+        <v>453794</v>
       </c>
       <c r="R67" t="n">
-        <v>6807944</v>
+        <v>6807980</v>
       </c>
       <c r="S67" t="n">
         <v>15</v>
@@ -7461,10 +7457,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>119590978</v>
+        <v>119591008</v>
       </c>
       <c r="B68" t="n">
-        <v>79144</v>
+        <v>57310</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -7477,34 +7473,39 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6453</v>
+        <v>100109</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P68" t="inlineStr">
         <is>
           <t>Rymån, Dlr</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>453823</v>
+        <v>453821</v>
       </c>
       <c r="R68" t="n">
-        <v>6807778</v>
+        <v>6808117</v>
       </c>
       <c r="S68" t="n">
         <v>15</v>
@@ -7537,6 +7538,11 @@
       <c r="AA68" t="inlineStr">
         <is>
           <t>2024-09-06</t>
+        </is>
+      </c>
+      <c r="AC68" t="inlineStr">
+        <is>
+          <t>Färska ringhack (gran)</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7563,10 +7569,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>119590996</v>
+        <v>119591048</v>
       </c>
       <c r="B69" t="n">
-        <v>57463</v>
+        <v>78526</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -7579,21 +7585,21 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7603,10 +7609,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>453750</v>
+        <v>453788</v>
       </c>
       <c r="R69" t="n">
-        <v>6807861</v>
+        <v>6807903</v>
       </c>
       <c r="S69" t="n">
         <v>15</v>
@@ -7665,10 +7671,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>119591012</v>
+        <v>119590985</v>
       </c>
       <c r="B70" t="n">
-        <v>96862</v>
+        <v>90562</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -7677,25 +7683,25 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>221945</v>
+        <v>1202</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7705,10 +7711,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>453875</v>
+        <v>453839</v>
       </c>
       <c r="R70" t="n">
-        <v>6808094</v>
+        <v>6807828</v>
       </c>
       <c r="S70" t="n">
         <v>15</v>
@@ -7767,10 +7773,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>119591004</v>
+        <v>119591087</v>
       </c>
       <c r="B71" t="n">
-        <v>91884</v>
+        <v>78526</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -7783,21 +7789,21 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>5449</v>
+        <v>6425</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -7807,10 +7813,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>453785</v>
+        <v>453803</v>
       </c>
       <c r="R71" t="n">
-        <v>6808062</v>
+        <v>6808020</v>
       </c>
       <c r="S71" t="n">
         <v>15</v>
@@ -7837,12 +7843,12 @@
       </c>
       <c r="Y71" t="inlineStr">
         <is>
-          <t>2024-09-06</t>
+          <t>2024-09-04</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
         <is>
-          <t>2024-09-06</t>
+          <t>2024-09-04</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -7869,7 +7875,7 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>119591032</v>
+        <v>119591089</v>
       </c>
       <c r="B72" t="n">
         <v>78526</v>
@@ -7909,10 +7915,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>453897</v>
+        <v>453780</v>
       </c>
       <c r="R72" t="n">
-        <v>6808009</v>
+        <v>6808055</v>
       </c>
       <c r="S72" t="n">
         <v>15</v>
@@ -7939,12 +7945,12 @@
       </c>
       <c r="Y72" t="inlineStr">
         <is>
-          <t>2024-09-06</t>
+          <t>2024-09-04</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
         <is>
-          <t>2024-09-06</t>
+          <t>2024-09-04</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -7971,7 +7977,7 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>119591058</v>
+        <v>119591086</v>
       </c>
       <c r="B73" t="n">
         <v>78526</v>
@@ -8011,10 +8017,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>453734</v>
+        <v>453820</v>
       </c>
       <c r="R73" t="n">
-        <v>6808007</v>
+        <v>6808020</v>
       </c>
       <c r="S73" t="n">
         <v>15</v>
@@ -8041,12 +8047,12 @@
       </c>
       <c r="Y73" t="inlineStr">
         <is>
-          <t>2024-09-06</t>
+          <t>2024-09-04</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
         <is>
-          <t>2024-09-06</t>
+          <t>2024-09-04</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8073,7 +8079,7 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>119591061</v>
+        <v>119591066</v>
       </c>
       <c r="B74" t="n">
         <v>78526</v>
@@ -8113,10 +8119,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>453756</v>
+        <v>453787</v>
       </c>
       <c r="R74" t="n">
-        <v>6808003</v>
+        <v>6808020</v>
       </c>
       <c r="S74" t="n">
         <v>15</v>
@@ -8175,10 +8181,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>119591059</v>
+        <v>119591029</v>
       </c>
       <c r="B75" t="n">
-        <v>78526</v>
+        <v>90580</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -8191,21 +8197,21 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8215,10 +8221,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>453737</v>
+        <v>453861</v>
       </c>
       <c r="R75" t="n">
-        <v>6808007</v>
+        <v>6807970</v>
       </c>
       <c r="S75" t="n">
         <v>15</v>
@@ -8277,10 +8283,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>119590969</v>
+        <v>119590995</v>
       </c>
       <c r="B76" t="n">
-        <v>57310</v>
+        <v>103418</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -8289,43 +8295,38 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>100109</v>
+        <v>222412</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
-      <c r="M76" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P76" t="inlineStr">
         <is>
           <t>Rymån, Dlr</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>453847</v>
+        <v>453897</v>
       </c>
       <c r="R76" t="n">
-        <v>6807830</v>
+        <v>6808024</v>
       </c>
       <c r="S76" t="n">
         <v>15</v>
@@ -8358,11 +8359,6 @@
       <c r="AA76" t="inlineStr">
         <is>
           <t>2024-09-06</t>
-        </is>
-      </c>
-      <c r="AC76" t="inlineStr">
-        <is>
-          <t>Försett med naturvårdssnitsel</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8389,7 +8385,7 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>119591087</v>
+        <v>119591035</v>
       </c>
       <c r="B77" t="n">
         <v>78526</v>
@@ -8429,10 +8425,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>453803</v>
+        <v>453808</v>
       </c>
       <c r="R77" t="n">
-        <v>6808020</v>
+        <v>6807890</v>
       </c>
       <c r="S77" t="n">
         <v>15</v>
@@ -8459,12 +8455,12 @@
       </c>
       <c r="Y77" t="inlineStr">
         <is>
-          <t>2024-09-04</t>
+          <t>2024-09-06</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
         <is>
-          <t>2024-09-04</t>
+          <t>2024-09-06</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -8491,10 +8487,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>119590998</v>
+        <v>119591006</v>
       </c>
       <c r="B78" t="n">
-        <v>57463</v>
+        <v>57310</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -8507,34 +8503,39 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
+      <c r="M78" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P78" t="inlineStr">
         <is>
           <t>Rymån, Dlr</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>453861</v>
+        <v>453796</v>
       </c>
       <c r="R78" t="n">
-        <v>6808024</v>
+        <v>6808114</v>
       </c>
       <c r="S78" t="n">
         <v>15</v>
@@ -8567,6 +8568,11 @@
       <c r="AA78" t="inlineStr">
         <is>
           <t>2024-09-06</t>
+        </is>
+      </c>
+      <c r="AC78" t="inlineStr">
+        <is>
+          <t>Färska ringhack (gran)</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -8593,10 +8599,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>119591022</v>
+        <v>119591042</v>
       </c>
       <c r="B79" t="n">
-        <v>78263</v>
+        <v>78526</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -8609,21 +8615,21 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8633,10 +8639,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>453759</v>
+        <v>453788</v>
       </c>
       <c r="R79" t="n">
-        <v>6807967</v>
+        <v>6807792</v>
       </c>
       <c r="S79" t="n">
         <v>15</v>
@@ -8695,10 +8701,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>119591056</v>
+        <v>119590978</v>
       </c>
       <c r="B80" t="n">
-        <v>78526</v>
+        <v>79144</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -8711,21 +8717,21 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -8735,10 +8741,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>453742</v>
+        <v>453823</v>
       </c>
       <c r="R80" t="n">
-        <v>6807994</v>
+        <v>6807778</v>
       </c>
       <c r="S80" t="n">
         <v>15</v>
@@ -8797,10 +8803,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>119590999</v>
+        <v>119591069</v>
       </c>
       <c r="B81" t="n">
-        <v>91463</v>
+        <v>78526</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -8813,21 +8819,21 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>4745</v>
+        <v>6425</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Tallriska</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Lactarius musteus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -8837,10 +8843,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>453793</v>
+        <v>453756</v>
       </c>
       <c r="R81" t="n">
-        <v>6808029</v>
+        <v>6808048</v>
       </c>
       <c r="S81" t="n">
         <v>15</v>
@@ -8867,12 +8873,12 @@
       </c>
       <c r="Y81" t="inlineStr">
         <is>
-          <t>2024-09-04</t>
+          <t>2024-09-06</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
         <is>
-          <t>2024-09-04</t>
+          <t>2024-09-06</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -8899,10 +8905,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>119591008</v>
+        <v>119590974</v>
       </c>
       <c r="B82" t="n">
-        <v>57310</v>
+        <v>95455</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -8915,39 +8921,34 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>100109</v>
+        <v>53</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
-      <c r="M82" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P82" t="inlineStr">
         <is>
           <t>Rymån, Dlr</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>453821</v>
+        <v>453852</v>
       </c>
       <c r="R82" t="n">
-        <v>6808117</v>
+        <v>6807959</v>
       </c>
       <c r="S82" t="n">
         <v>15</v>
@@ -8980,11 +8981,6 @@
       <c r="AA82" t="inlineStr">
         <is>
           <t>2024-09-06</t>
-        </is>
-      </c>
-      <c r="AC82" t="inlineStr">
-        <is>
-          <t>Färska ringhack (gran)</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9011,7 +9007,7 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>119591009</v>
+        <v>119591007</v>
       </c>
       <c r="B83" t="n">
         <v>57310</v>
@@ -9056,10 +9052,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>453815</v>
+        <v>453808</v>
       </c>
       <c r="R83" t="n">
-        <v>6808098</v>
+        <v>6808114</v>
       </c>
       <c r="S83" t="n">
         <v>15</v>
@@ -9123,10 +9119,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>119591011</v>
+        <v>119590994</v>
       </c>
       <c r="B84" t="n">
-        <v>96862</v>
+        <v>103418</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -9139,16 +9135,16 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>221945</v>
+        <v>222412</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
@@ -9163,10 +9159,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>453903</v>
+        <v>453893</v>
       </c>
       <c r="R84" t="n">
-        <v>6807986</v>
+        <v>6808027</v>
       </c>
       <c r="S84" t="n">
         <v>15</v>
@@ -9225,10 +9221,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>119590980</v>
+        <v>119591096</v>
       </c>
       <c r="B85" t="n">
-        <v>79144</v>
+        <v>78526</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -9241,21 +9237,21 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -9265,10 +9261,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>453791</v>
+        <v>453898</v>
       </c>
       <c r="R85" t="n">
-        <v>6807707</v>
+        <v>6808089</v>
       </c>
       <c r="S85" t="n">
         <v>15</v>
@@ -9327,10 +9323,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>119591031</v>
+        <v>119591023</v>
       </c>
       <c r="B86" t="n">
-        <v>90580</v>
+        <v>78263</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -9343,21 +9339,21 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>5432</v>
+        <v>228912</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -9367,10 +9363,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>453886</v>
+        <v>453770</v>
       </c>
       <c r="R86" t="n">
-        <v>6808055</v>
+        <v>6807984</v>
       </c>
       <c r="S86" t="n">
         <v>15</v>
@@ -9429,10 +9425,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>119590972</v>
+        <v>119590986</v>
       </c>
       <c r="B87" t="n">
-        <v>74638</v>
+        <v>90562</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -9445,21 +9441,21 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>6440</v>
+        <v>1202</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -9469,10 +9465,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>453874</v>
+        <v>453795</v>
       </c>
       <c r="R87" t="n">
-        <v>6808094</v>
+        <v>6807770</v>
       </c>
       <c r="S87" t="n">
         <v>15</v>
@@ -9531,10 +9527,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>119591086</v>
+        <v>119590981</v>
       </c>
       <c r="B88" t="n">
-        <v>78526</v>
+        <v>79144</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
@@ -9547,21 +9543,21 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -9571,10 +9567,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>453820</v>
+        <v>453770</v>
       </c>
       <c r="R88" t="n">
-        <v>6808020</v>
+        <v>6807987</v>
       </c>
       <c r="S88" t="n">
         <v>15</v>
@@ -9601,12 +9597,12 @@
       </c>
       <c r="Y88" t="inlineStr">
         <is>
-          <t>2024-09-04</t>
+          <t>2024-09-06</t>
         </is>
       </c>
       <c r="AA88" t="inlineStr">
         <is>
-          <t>2024-09-04</t>
+          <t>2024-09-06</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -9633,10 +9629,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>119590983</v>
+        <v>119591034</v>
       </c>
       <c r="B89" t="n">
-        <v>79144</v>
+        <v>78526</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
@@ -9649,21 +9645,21 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -9673,10 +9669,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>453762</v>
+        <v>453825</v>
       </c>
       <c r="R89" t="n">
-        <v>6808048</v>
+        <v>6807960</v>
       </c>
       <c r="S89" t="n">
         <v>15</v>
@@ -9837,7 +9833,7 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>119591062</v>
+        <v>119591073</v>
       </c>
       <c r="B91" t="n">
         <v>78526</v>
@@ -9877,10 +9873,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>453761</v>
+        <v>453797</v>
       </c>
       <c r="R91" t="n">
-        <v>6808000</v>
+        <v>6808117</v>
       </c>
       <c r="S91" t="n">
         <v>15</v>
@@ -9939,7 +9935,7 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>119591069</v>
+        <v>119591038</v>
       </c>
       <c r="B92" t="n">
         <v>78526</v>
@@ -9979,10 +9975,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>453756</v>
+        <v>453826</v>
       </c>
       <c r="R92" t="n">
-        <v>6808048</v>
+        <v>6807750</v>
       </c>
       <c r="S92" t="n">
         <v>15</v>
@@ -10041,7 +10037,7 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>119591043</v>
+        <v>119591055</v>
       </c>
       <c r="B93" t="n">
         <v>78526</v>
@@ -10081,10 +10077,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>453774</v>
+        <v>453747</v>
       </c>
       <c r="R93" t="n">
-        <v>6807849</v>
+        <v>6807979</v>
       </c>
       <c r="S93" t="n">
         <v>15</v>
@@ -10143,7 +10139,7 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>119591054</v>
+        <v>119591036</v>
       </c>
       <c r="B94" t="n">
         <v>78526</v>
@@ -10183,10 +10179,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>453738</v>
+        <v>453849</v>
       </c>
       <c r="R94" t="n">
-        <v>6807973</v>
+        <v>6807844</v>
       </c>
       <c r="S94" t="n">
         <v>15</v>
@@ -10245,10 +10241,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>119591023</v>
+        <v>119590998</v>
       </c>
       <c r="B95" t="n">
-        <v>78263</v>
+        <v>57463</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
@@ -10261,21 +10257,21 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>228912</v>
+        <v>103021</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -10285,10 +10281,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>453770</v>
+        <v>453861</v>
       </c>
       <c r="R95" t="n">
-        <v>6807984</v>
+        <v>6808024</v>
       </c>
       <c r="S95" t="n">
         <v>15</v>
@@ -10347,10 +10343,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>119590974</v>
+        <v>119591050</v>
       </c>
       <c r="B96" t="n">
-        <v>95455</v>
+        <v>78526</v>
       </c>
       <c r="C96" t="inlineStr">
         <is>
@@ -10363,21 +10359,21 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>53</v>
+        <v>6425</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -10387,10 +10383,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>453852</v>
+        <v>453782</v>
       </c>
       <c r="R96" t="n">
-        <v>6807959</v>
+        <v>6807956</v>
       </c>
       <c r="S96" t="n">
         <v>15</v>
@@ -10449,10 +10445,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>119590991</v>
+        <v>119591054</v>
       </c>
       <c r="B97" t="n">
-        <v>57310</v>
+        <v>78526</v>
       </c>
       <c r="C97" t="inlineStr">
         <is>
@@ -10465,39 +10461,34 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
-      <c r="M97" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P97" t="inlineStr">
         <is>
           <t>Rymån, Dlr</t>
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>453887</v>
+        <v>453738</v>
       </c>
       <c r="R97" t="n">
-        <v>6808050</v>
+        <v>6807973</v>
       </c>
       <c r="S97" t="n">
         <v>15</v>
@@ -10556,10 +10547,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>119591066</v>
+        <v>119590979</v>
       </c>
       <c r="B98" t="n">
-        <v>78526</v>
+        <v>79144</v>
       </c>
       <c r="C98" t="inlineStr">
         <is>
@@ -10572,21 +10563,21 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -10596,10 +10587,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>453787</v>
+        <v>453807</v>
       </c>
       <c r="R98" t="n">
-        <v>6808020</v>
+        <v>6807719</v>
       </c>
       <c r="S98" t="n">
         <v>15</v>
@@ -10658,7 +10649,7 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>119591070</v>
+        <v>119591085</v>
       </c>
       <c r="B99" t="n">
         <v>78526</v>
@@ -10698,10 +10689,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>453759</v>
+        <v>453830</v>
       </c>
       <c r="R99" t="n">
-        <v>6808051</v>
+        <v>6808029</v>
       </c>
       <c r="S99" t="n">
         <v>15</v>
@@ -10728,12 +10719,12 @@
       </c>
       <c r="Y99" t="inlineStr">
         <is>
-          <t>2024-09-06</t>
+          <t>2024-09-04</t>
         </is>
       </c>
       <c r="AA99" t="inlineStr">
         <is>
-          <t>2024-09-06</t>
+          <t>2024-09-04</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -10760,10 +10751,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>119590981</v>
+        <v>119591064</v>
       </c>
       <c r="B100" t="n">
-        <v>79144</v>
+        <v>78526</v>
       </c>
       <c r="C100" t="inlineStr">
         <is>
@@ -10776,21 +10767,21 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -10800,10 +10791,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>453770</v>
+        <v>453761</v>
       </c>
       <c r="R100" t="n">
-        <v>6807987</v>
+        <v>6807996</v>
       </c>
       <c r="S100" t="n">
         <v>15</v>
@@ -10862,10 +10853,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>119591090</v>
+        <v>119591019</v>
       </c>
       <c r="B101" t="n">
-        <v>78526</v>
+        <v>96865</v>
       </c>
       <c r="C101" t="inlineStr">
         <is>
@@ -10874,38 +10865,47 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>6425</v>
+        <v>221946</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mattlummer</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium clavatum</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I101" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I101" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J101" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
       <c r="P101" t="inlineStr">
         <is>
           <t>Rymån, Dlr</t>
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>453794</v>
+        <v>453836</v>
       </c>
       <c r="R101" t="n">
-        <v>6808097</v>
+        <v>6807799</v>
       </c>
       <c r="S101" t="n">
         <v>15</v>
@@ -10932,12 +10932,12 @@
       </c>
       <c r="Y101" t="inlineStr">
         <is>
-          <t>2024-09-04</t>
+          <t>2024-09-06</t>
         </is>
       </c>
       <c r="AA101" t="inlineStr">
         <is>
-          <t>2024-09-04</t>
+          <t>2024-09-06</t>
         </is>
       </c>
       <c r="AD101" t="b">

--- a/artfynd/A 31144-2024 artfynd.xlsx
+++ b/artfynd/A 31144-2024 artfynd.xlsx
@@ -2514,7 +2514,7 @@
         <v>119590990</v>
       </c>
       <c r="B20" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -3544,7 +3544,7 @@
         <v>119590969</v>
       </c>
       <c r="B30" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3656,7 +3656,7 @@
         <v>119591010</v>
       </c>
       <c r="B31" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4380,7 +4380,7 @@
         <v>119591097</v>
       </c>
       <c r="B38" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4487,7 +4487,7 @@
         <v>119591009</v>
       </c>
       <c r="B39" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -6741,7 +6741,7 @@
         <v>119590991</v>
       </c>
       <c r="B61" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -7460,7 +7460,7 @@
         <v>119591008</v>
       </c>
       <c r="B68" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -8490,7 +8490,7 @@
         <v>119591006</v>
       </c>
       <c r="B78" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -9010,7 +9010,7 @@
         <v>119591007</v>
       </c>
       <c r="B83" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>

--- a/artfynd/A 31144-2024 artfynd.xlsx
+++ b/artfynd/A 31144-2024 artfynd.xlsx
@@ -10964,10 +10964,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>124467102</v>
+        <v>124467080</v>
       </c>
       <c r="B102" t="n">
-        <v>57513</v>
+        <v>78810</v>
       </c>
       <c r="C102" t="inlineStr">
         <is>
@@ -10980,39 +10980,34 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
-      <c r="M102" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P102" t="inlineStr">
         <is>
           <t>Rymån, Dlr</t>
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>453847</v>
+        <v>453826</v>
       </c>
       <c r="R102" t="n">
-        <v>6808007</v>
+        <v>6808085</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -11071,10 +11066,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>124467097</v>
+        <v>124467078</v>
       </c>
       <c r="B103" t="n">
-        <v>57513</v>
+        <v>78810</v>
       </c>
       <c r="C103" t="inlineStr">
         <is>
@@ -11087,39 +11082,34 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
-      <c r="M103" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P103" t="inlineStr">
         <is>
           <t>Rymån, Dlr</t>
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>453864</v>
+        <v>453872</v>
       </c>
       <c r="R103" t="n">
-        <v>6807819</v>
+        <v>6807869</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -11178,10 +11168,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>124467085</v>
+        <v>124467094</v>
       </c>
       <c r="B104" t="n">
-        <v>78810</v>
+        <v>57513</v>
       </c>
       <c r="C104" t="inlineStr">
         <is>
@@ -11194,34 +11184,39 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
+      <c r="M104" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P104" t="inlineStr">
         <is>
           <t>Rymån, Dlr</t>
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>453807</v>
+        <v>453866</v>
       </c>
       <c r="R104" t="n">
-        <v>6808128</v>
+        <v>6807817</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -11280,10 +11275,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>124467067</v>
+        <v>124467097</v>
       </c>
       <c r="B105" t="n">
-        <v>74901</v>
+        <v>57513</v>
       </c>
       <c r="C105" t="inlineStr">
         <is>
@@ -11296,34 +11291,39 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>6440</v>
+        <v>100109</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
+      <c r="M105" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P105" t="inlineStr">
         <is>
           <t>Rymån, Dlr</t>
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>453900</v>
+        <v>453864</v>
       </c>
       <c r="R105" t="n">
-        <v>6808014</v>
+        <v>6807819</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11382,10 +11382,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>124467082</v>
+        <v>124467067</v>
       </c>
       <c r="B106" t="n">
-        <v>78810</v>
+        <v>74901</v>
       </c>
       <c r="C106" t="inlineStr">
         <is>
@@ -11398,21 +11398,21 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
@@ -11422,10 +11422,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>453811</v>
+        <v>453900</v>
       </c>
       <c r="R106" t="n">
-        <v>6808100</v>
+        <v>6808014</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11484,7 +11484,7 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>124467094</v>
+        <v>124467099</v>
       </c>
       <c r="B107" t="n">
         <v>57513</v>
@@ -11529,10 +11529,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>453866</v>
+        <v>453871</v>
       </c>
       <c r="R107" t="n">
-        <v>6807817</v>
+        <v>6807887</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -11591,7 +11591,7 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>124467078</v>
+        <v>124467085</v>
       </c>
       <c r="B108" t="n">
         <v>78810</v>
@@ -11631,10 +11631,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>453872</v>
+        <v>453807</v>
       </c>
       <c r="R108" t="n">
-        <v>6807869</v>
+        <v>6808128</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -11693,10 +11693,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>124467099</v>
+        <v>124467082</v>
       </c>
       <c r="B109" t="n">
-        <v>57513</v>
+        <v>78810</v>
       </c>
       <c r="C109" t="inlineStr">
         <is>
@@ -11709,39 +11709,34 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
-      <c r="M109" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P109" t="inlineStr">
         <is>
           <t>Rymån, Dlr</t>
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>453871</v>
+        <v>453811</v>
       </c>
       <c r="R109" t="n">
-        <v>6807887</v>
+        <v>6808100</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -11800,10 +11795,10 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>124467080</v>
+        <v>124467093</v>
       </c>
       <c r="B110" t="n">
-        <v>78810</v>
+        <v>5176</v>
       </c>
       <c r="C110" t="inlineStr">
         <is>
@@ -11812,38 +11807,43 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E110" t="n">
-        <v>6425</v>
+        <v>100526</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
+      <c r="M110" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P110" t="inlineStr">
         <is>
           <t>Rymån, Dlr</t>
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>453826</v>
+        <v>453835</v>
       </c>
       <c r="R110" t="n">
-        <v>6808085</v>
+        <v>6808062</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -11902,10 +11902,10 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>124467093</v>
+        <v>124467102</v>
       </c>
       <c r="B111" t="n">
-        <v>5176</v>
+        <v>57513</v>
       </c>
       <c r="C111" t="inlineStr">
         <is>
@@ -11914,31 +11914,31 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E111" t="n">
-        <v>100526</v>
+        <v>100109</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
       <c r="M111" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P111" t="inlineStr">
@@ -11947,10 +11947,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>453835</v>
+        <v>453847</v>
       </c>
       <c r="R111" t="n">
-        <v>6808062</v>
+        <v>6808007</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>

--- a/artfynd/A 31144-2024 artfynd.xlsx
+++ b/artfynd/A 31144-2024 artfynd.xlsx
@@ -10964,10 +10964,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>124467080</v>
+        <v>124467102</v>
       </c>
       <c r="B102" t="n">
-        <v>78810</v>
+        <v>57513</v>
       </c>
       <c r="C102" t="inlineStr">
         <is>
@@ -10980,34 +10980,39 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
+      <c r="M102" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P102" t="inlineStr">
         <is>
           <t>Rymån, Dlr</t>
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>453826</v>
+        <v>453847</v>
       </c>
       <c r="R102" t="n">
-        <v>6808085</v>
+        <v>6808007</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -11168,10 +11173,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>124467094</v>
+        <v>124467080</v>
       </c>
       <c r="B104" t="n">
-        <v>57513</v>
+        <v>78810</v>
       </c>
       <c r="C104" t="inlineStr">
         <is>
@@ -11184,39 +11189,34 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
-      <c r="M104" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P104" t="inlineStr">
         <is>
           <t>Rymån, Dlr</t>
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>453866</v>
+        <v>453826</v>
       </c>
       <c r="R104" t="n">
-        <v>6807817</v>
+        <v>6808085</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -11275,10 +11275,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>124467097</v>
+        <v>124467093</v>
       </c>
       <c r="B105" t="n">
-        <v>57513</v>
+        <v>5176</v>
       </c>
       <c r="C105" t="inlineStr">
         <is>
@@ -11287,31 +11287,31 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E105" t="n">
-        <v>100109</v>
+        <v>100526</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
       <c r="M105" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P105" t="inlineStr">
@@ -11320,10 +11320,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>453864</v>
+        <v>453835</v>
       </c>
       <c r="R105" t="n">
-        <v>6807819</v>
+        <v>6808062</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11382,10 +11382,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>124467067</v>
+        <v>124467082</v>
       </c>
       <c r="B106" t="n">
-        <v>74901</v>
+        <v>78810</v>
       </c>
       <c r="C106" t="inlineStr">
         <is>
@@ -11398,21 +11398,21 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
@@ -11422,10 +11422,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>453900</v>
+        <v>453811</v>
       </c>
       <c r="R106" t="n">
-        <v>6808014</v>
+        <v>6808100</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11484,7 +11484,7 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>124467099</v>
+        <v>124467097</v>
       </c>
       <c r="B107" t="n">
         <v>57513</v>
@@ -11529,10 +11529,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>453871</v>
+        <v>453864</v>
       </c>
       <c r="R107" t="n">
-        <v>6807887</v>
+        <v>6807819</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -11591,10 +11591,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>124467085</v>
+        <v>124467099</v>
       </c>
       <c r="B108" t="n">
-        <v>78810</v>
+        <v>57513</v>
       </c>
       <c r="C108" t="inlineStr">
         <is>
@@ -11607,34 +11607,39 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
+      <c r="M108" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P108" t="inlineStr">
         <is>
           <t>Rymån, Dlr</t>
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>453807</v>
+        <v>453871</v>
       </c>
       <c r="R108" t="n">
-        <v>6808128</v>
+        <v>6807887</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -11693,10 +11698,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>124467082</v>
+        <v>124467094</v>
       </c>
       <c r="B109" t="n">
-        <v>78810</v>
+        <v>57513</v>
       </c>
       <c r="C109" t="inlineStr">
         <is>
@@ -11709,34 +11714,39 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
+      <c r="M109" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P109" t="inlineStr">
         <is>
           <t>Rymån, Dlr</t>
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>453811</v>
+        <v>453866</v>
       </c>
       <c r="R109" t="n">
-        <v>6808100</v>
+        <v>6807817</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -11795,10 +11805,10 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>124467093</v>
+        <v>124467085</v>
       </c>
       <c r="B110" t="n">
-        <v>5176</v>
+        <v>78810</v>
       </c>
       <c r="C110" t="inlineStr">
         <is>
@@ -11807,43 +11817,38 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E110" t="n">
-        <v>100526</v>
+        <v>6425</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
-      <c r="M110" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P110" t="inlineStr">
         <is>
           <t>Rymån, Dlr</t>
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>453835</v>
+        <v>453807</v>
       </c>
       <c r="R110" t="n">
-        <v>6808062</v>
+        <v>6808128</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -11902,10 +11907,10 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>124467102</v>
+        <v>124467067</v>
       </c>
       <c r="B111" t="n">
-        <v>57513</v>
+        <v>74901</v>
       </c>
       <c r="C111" t="inlineStr">
         <is>
@@ -11918,39 +11923,34 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>100109</v>
+        <v>6440</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
-      <c r="M111" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P111" t="inlineStr">
         <is>
           <t>Rymån, Dlr</t>
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>453847</v>
+        <v>453900</v>
       </c>
       <c r="R111" t="n">
-        <v>6808007</v>
+        <v>6808014</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>

--- a/artfynd/A 31144-2024 artfynd.xlsx
+++ b/artfynd/A 31144-2024 artfynd.xlsx
@@ -10964,10 +10964,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>124467102</v>
+        <v>124467078</v>
       </c>
       <c r="B102" t="n">
-        <v>57513</v>
+        <v>78810</v>
       </c>
       <c r="C102" t="inlineStr">
         <is>
@@ -10980,39 +10980,34 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
-      <c r="M102" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P102" t="inlineStr">
         <is>
           <t>Rymån, Dlr</t>
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>453847</v>
+        <v>453872</v>
       </c>
       <c r="R102" t="n">
-        <v>6808007</v>
+        <v>6807869</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -11071,10 +11066,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>124467078</v>
+        <v>124467067</v>
       </c>
       <c r="B103" t="n">
-        <v>78810</v>
+        <v>74901</v>
       </c>
       <c r="C103" t="inlineStr">
         <is>
@@ -11087,21 +11082,21 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
@@ -11111,10 +11106,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>453872</v>
+        <v>453900</v>
       </c>
       <c r="R103" t="n">
-        <v>6807869</v>
+        <v>6808014</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -11173,7 +11168,7 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>124467080</v>
+        <v>124467085</v>
       </c>
       <c r="B104" t="n">
         <v>78810</v>
@@ -11213,10 +11208,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>453826</v>
+        <v>453807</v>
       </c>
       <c r="R104" t="n">
-        <v>6808085</v>
+        <v>6808128</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -11382,10 +11377,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>124467082</v>
+        <v>124467094</v>
       </c>
       <c r="B106" t="n">
-        <v>78810</v>
+        <v>57513</v>
       </c>
       <c r="C106" t="inlineStr">
         <is>
@@ -11398,34 +11393,39 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
+      <c r="M106" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P106" t="inlineStr">
         <is>
           <t>Rymån, Dlr</t>
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>453811</v>
+        <v>453866</v>
       </c>
       <c r="R106" t="n">
-        <v>6808100</v>
+        <v>6807817</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11484,7 +11484,7 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>124467097</v>
+        <v>124467099</v>
       </c>
       <c r="B107" t="n">
         <v>57513</v>
@@ -11529,10 +11529,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>453864</v>
+        <v>453871</v>
       </c>
       <c r="R107" t="n">
-        <v>6807819</v>
+        <v>6807887</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -11591,7 +11591,7 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>124467099</v>
+        <v>124467097</v>
       </c>
       <c r="B108" t="n">
         <v>57513</v>
@@ -11636,10 +11636,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>453871</v>
+        <v>453864</v>
       </c>
       <c r="R108" t="n">
-        <v>6807887</v>
+        <v>6807819</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -11698,7 +11698,7 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>124467094</v>
+        <v>124467102</v>
       </c>
       <c r="B109" t="n">
         <v>57513</v>
@@ -11743,10 +11743,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>453866</v>
+        <v>453847</v>
       </c>
       <c r="R109" t="n">
-        <v>6807817</v>
+        <v>6808007</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -11805,7 +11805,7 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>124467085</v>
+        <v>124467080</v>
       </c>
       <c r="B110" t="n">
         <v>78810</v>
@@ -11845,10 +11845,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>453807</v>
+        <v>453826</v>
       </c>
       <c r="R110" t="n">
-        <v>6808128</v>
+        <v>6808085</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -11907,10 +11907,10 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>124467067</v>
+        <v>124467082</v>
       </c>
       <c r="B111" t="n">
-        <v>74901</v>
+        <v>78810</v>
       </c>
       <c r="C111" t="inlineStr">
         <is>
@@ -11923,21 +11923,21 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
@@ -11947,10 +11947,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>453900</v>
+        <v>453811</v>
       </c>
       <c r="R111" t="n">
-        <v>6808014</v>
+        <v>6808100</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>

--- a/artfynd/A 31144-2024 artfynd.xlsx
+++ b/artfynd/A 31144-2024 artfynd.xlsx
@@ -10964,10 +10964,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>124467078</v>
+        <v>124467099</v>
       </c>
       <c r="B102" t="n">
-        <v>78810</v>
+        <v>57513</v>
       </c>
       <c r="C102" t="inlineStr">
         <is>
@@ -10980,34 +10980,39 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
+      <c r="M102" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P102" t="inlineStr">
         <is>
           <t>Rymån, Dlr</t>
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>453872</v>
+        <v>453871</v>
       </c>
       <c r="R102" t="n">
-        <v>6807869</v>
+        <v>6807887</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -11066,10 +11071,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>124467067</v>
+        <v>124467078</v>
       </c>
       <c r="B103" t="n">
-        <v>74901</v>
+        <v>78810</v>
       </c>
       <c r="C103" t="inlineStr">
         <is>
@@ -11082,21 +11087,21 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
@@ -11106,10 +11111,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>453900</v>
+        <v>453872</v>
       </c>
       <c r="R103" t="n">
-        <v>6808014</v>
+        <v>6807869</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -11168,10 +11173,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>124467085</v>
+        <v>124467067</v>
       </c>
       <c r="B104" t="n">
-        <v>78810</v>
+        <v>74901</v>
       </c>
       <c r="C104" t="inlineStr">
         <is>
@@ -11184,21 +11189,21 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
@@ -11208,10 +11213,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>453807</v>
+        <v>453900</v>
       </c>
       <c r="R104" t="n">
-        <v>6808128</v>
+        <v>6808014</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -11270,10 +11275,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>124467093</v>
+        <v>124467082</v>
       </c>
       <c r="B105" t="n">
-        <v>5176</v>
+        <v>78810</v>
       </c>
       <c r="C105" t="inlineStr">
         <is>
@@ -11282,43 +11287,38 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E105" t="n">
-        <v>100526</v>
+        <v>6425</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
-      <c r="M105" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P105" t="inlineStr">
         <is>
           <t>Rymån, Dlr</t>
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>453835</v>
+        <v>453811</v>
       </c>
       <c r="R105" t="n">
-        <v>6808062</v>
+        <v>6808100</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11377,10 +11377,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>124467094</v>
+        <v>124467093</v>
       </c>
       <c r="B106" t="n">
-        <v>57513</v>
+        <v>5176</v>
       </c>
       <c r="C106" t="inlineStr">
         <is>
@@ -11389,31 +11389,31 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E106" t="n">
-        <v>100109</v>
+        <v>100526</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
       <c r="M106" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P106" t="inlineStr">
@@ -11422,10 +11422,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>453866</v>
+        <v>453835</v>
       </c>
       <c r="R106" t="n">
-        <v>6807817</v>
+        <v>6808062</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11484,10 +11484,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>124467099</v>
+        <v>124467080</v>
       </c>
       <c r="B107" t="n">
-        <v>57513</v>
+        <v>78810</v>
       </c>
       <c r="C107" t="inlineStr">
         <is>
@@ -11500,39 +11500,34 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
-      <c r="M107" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P107" t="inlineStr">
         <is>
           <t>Rymån, Dlr</t>
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>453871</v>
+        <v>453826</v>
       </c>
       <c r="R107" t="n">
-        <v>6807887</v>
+        <v>6808085</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -11591,7 +11586,7 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>124467097</v>
+        <v>124467102</v>
       </c>
       <c r="B108" t="n">
         <v>57513</v>
@@ -11636,10 +11631,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>453864</v>
+        <v>453847</v>
       </c>
       <c r="R108" t="n">
-        <v>6807819</v>
+        <v>6808007</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -11698,7 +11693,7 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>124467102</v>
+        <v>124467094</v>
       </c>
       <c r="B109" t="n">
         <v>57513</v>
@@ -11743,10 +11738,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>453847</v>
+        <v>453866</v>
       </c>
       <c r="R109" t="n">
-        <v>6808007</v>
+        <v>6807817</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -11805,10 +11800,10 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>124467080</v>
+        <v>124467097</v>
       </c>
       <c r="B110" t="n">
-        <v>78810</v>
+        <v>57513</v>
       </c>
       <c r="C110" t="inlineStr">
         <is>
@@ -11821,34 +11816,39 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
+      <c r="M110" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P110" t="inlineStr">
         <is>
           <t>Rymån, Dlr</t>
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>453826</v>
+        <v>453864</v>
       </c>
       <c r="R110" t="n">
-        <v>6808085</v>
+        <v>6807819</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -11907,7 +11907,7 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>124467082</v>
+        <v>124467085</v>
       </c>
       <c r="B111" t="n">
         <v>78810</v>
@@ -11947,10 +11947,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>453811</v>
+        <v>453807</v>
       </c>
       <c r="R111" t="n">
-        <v>6808100</v>
+        <v>6808128</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>

--- a/artfynd/A 31144-2024 artfynd.xlsx
+++ b/artfynd/A 31144-2024 artfynd.xlsx
@@ -10964,10 +10964,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>124467099</v>
+        <v>124467067</v>
       </c>
       <c r="B102" t="n">
-        <v>57513</v>
+        <v>74901</v>
       </c>
       <c r="C102" t="inlineStr">
         <is>
@@ -10980,39 +10980,34 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>100109</v>
+        <v>6440</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
-      <c r="M102" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P102" t="inlineStr">
         <is>
           <t>Rymån, Dlr</t>
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>453871</v>
+        <v>453900</v>
       </c>
       <c r="R102" t="n">
-        <v>6807887</v>
+        <v>6808014</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -11071,10 +11066,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>124467078</v>
+        <v>124467097</v>
       </c>
       <c r="B103" t="n">
-        <v>78810</v>
+        <v>57513</v>
       </c>
       <c r="C103" t="inlineStr">
         <is>
@@ -11087,34 +11082,39 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
+      <c r="M103" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P103" t="inlineStr">
         <is>
           <t>Rymån, Dlr</t>
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>453872</v>
+        <v>453864</v>
       </c>
       <c r="R103" t="n">
-        <v>6807869</v>
+        <v>6807819</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -11173,10 +11173,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>124467067</v>
+        <v>124467080</v>
       </c>
       <c r="B104" t="n">
-        <v>74901</v>
+        <v>78810</v>
       </c>
       <c r="C104" t="inlineStr">
         <is>
@@ -11189,21 +11189,21 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
@@ -11213,10 +11213,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>453900</v>
+        <v>453826</v>
       </c>
       <c r="R104" t="n">
-        <v>6808014</v>
+        <v>6808085</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -11275,10 +11275,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>124467082</v>
+        <v>124467093</v>
       </c>
       <c r="B105" t="n">
-        <v>78810</v>
+        <v>5176</v>
       </c>
       <c r="C105" t="inlineStr">
         <is>
@@ -11287,38 +11287,43 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E105" t="n">
-        <v>6425</v>
+        <v>100526</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
+      <c r="M105" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P105" t="inlineStr">
         <is>
           <t>Rymån, Dlr</t>
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>453811</v>
+        <v>453835</v>
       </c>
       <c r="R105" t="n">
-        <v>6808100</v>
+        <v>6808062</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11377,10 +11382,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>124467093</v>
+        <v>124467094</v>
       </c>
       <c r="B106" t="n">
-        <v>5176</v>
+        <v>57513</v>
       </c>
       <c r="C106" t="inlineStr">
         <is>
@@ -11389,31 +11394,31 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E106" t="n">
-        <v>100526</v>
+        <v>100109</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
       <c r="M106" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P106" t="inlineStr">
@@ -11422,10 +11427,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>453835</v>
+        <v>453866</v>
       </c>
       <c r="R106" t="n">
-        <v>6808062</v>
+        <v>6807817</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11484,10 +11489,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>124467080</v>
+        <v>124467102</v>
       </c>
       <c r="B107" t="n">
-        <v>78810</v>
+        <v>57513</v>
       </c>
       <c r="C107" t="inlineStr">
         <is>
@@ -11500,34 +11505,39 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
+      <c r="M107" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P107" t="inlineStr">
         <is>
           <t>Rymån, Dlr</t>
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>453826</v>
+        <v>453847</v>
       </c>
       <c r="R107" t="n">
-        <v>6808085</v>
+        <v>6808007</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -11586,10 +11596,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>124467102</v>
+        <v>124467078</v>
       </c>
       <c r="B108" t="n">
-        <v>57513</v>
+        <v>78810</v>
       </c>
       <c r="C108" t="inlineStr">
         <is>
@@ -11602,39 +11612,34 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
-      <c r="M108" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P108" t="inlineStr">
         <is>
           <t>Rymån, Dlr</t>
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>453847</v>
+        <v>453872</v>
       </c>
       <c r="R108" t="n">
-        <v>6808007</v>
+        <v>6807869</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -11693,10 +11698,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>124467094</v>
+        <v>124467085</v>
       </c>
       <c r="B109" t="n">
-        <v>57513</v>
+        <v>78810</v>
       </c>
       <c r="C109" t="inlineStr">
         <is>
@@ -11709,39 +11714,34 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
-      <c r="M109" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P109" t="inlineStr">
         <is>
           <t>Rymån, Dlr</t>
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>453866</v>
+        <v>453807</v>
       </c>
       <c r="R109" t="n">
-        <v>6807817</v>
+        <v>6808128</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -11800,10 +11800,10 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>124467097</v>
+        <v>124467082</v>
       </c>
       <c r="B110" t="n">
-        <v>57513</v>
+        <v>78810</v>
       </c>
       <c r="C110" t="inlineStr">
         <is>
@@ -11816,39 +11816,34 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
-      <c r="M110" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P110" t="inlineStr">
         <is>
           <t>Rymån, Dlr</t>
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>453864</v>
+        <v>453811</v>
       </c>
       <c r="R110" t="n">
-        <v>6807819</v>
+        <v>6808100</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -11907,10 +11902,10 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>124467085</v>
+        <v>124467099</v>
       </c>
       <c r="B111" t="n">
-        <v>78810</v>
+        <v>57513</v>
       </c>
       <c r="C111" t="inlineStr">
         <is>
@@ -11923,34 +11918,39 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
+      <c r="M111" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P111" t="inlineStr">
         <is>
           <t>Rymån, Dlr</t>
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>453807</v>
+        <v>453871</v>
       </c>
       <c r="R111" t="n">
-        <v>6808128</v>
+        <v>6807887</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>

--- a/artfynd/A 31144-2024 artfynd.xlsx
+++ b/artfynd/A 31144-2024 artfynd.xlsx
@@ -10964,10 +10964,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>124467067</v>
+        <v>124467085</v>
       </c>
       <c r="B102" t="n">
-        <v>74901</v>
+        <v>78810</v>
       </c>
       <c r="C102" t="inlineStr">
         <is>
@@ -10980,21 +10980,21 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -11004,10 +11004,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>453900</v>
+        <v>453807</v>
       </c>
       <c r="R102" t="n">
-        <v>6808014</v>
+        <v>6808128</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -11066,10 +11066,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>124467097</v>
+        <v>124467093</v>
       </c>
       <c r="B103" t="n">
-        <v>57513</v>
+        <v>5176</v>
       </c>
       <c r="C103" t="inlineStr">
         <is>
@@ -11078,31 +11078,31 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>100109</v>
+        <v>100526</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
       <c r="M103" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P103" t="inlineStr">
@@ -11111,10 +11111,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>453864</v>
+        <v>453835</v>
       </c>
       <c r="R103" t="n">
-        <v>6807819</v>
+        <v>6808062</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -11173,10 +11173,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>124467080</v>
+        <v>124467094</v>
       </c>
       <c r="B104" t="n">
-        <v>78810</v>
+        <v>57513</v>
       </c>
       <c r="C104" t="inlineStr">
         <is>
@@ -11189,34 +11189,39 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
+      <c r="M104" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P104" t="inlineStr">
         <is>
           <t>Rymån, Dlr</t>
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>453826</v>
+        <v>453866</v>
       </c>
       <c r="R104" t="n">
-        <v>6808085</v>
+        <v>6807817</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -11275,10 +11280,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>124467093</v>
+        <v>124467080</v>
       </c>
       <c r="B105" t="n">
-        <v>5176</v>
+        <v>78810</v>
       </c>
       <c r="C105" t="inlineStr">
         <is>
@@ -11287,43 +11292,38 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E105" t="n">
-        <v>100526</v>
+        <v>6425</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
-      <c r="M105" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P105" t="inlineStr">
         <is>
           <t>Rymån, Dlr</t>
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>453835</v>
+        <v>453826</v>
       </c>
       <c r="R105" t="n">
-        <v>6808062</v>
+        <v>6808085</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11382,7 +11382,7 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>124467094</v>
+        <v>124467102</v>
       </c>
       <c r="B106" t="n">
         <v>57513</v>
@@ -11427,10 +11427,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>453866</v>
+        <v>453847</v>
       </c>
       <c r="R106" t="n">
-        <v>6807817</v>
+        <v>6808007</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11489,10 +11489,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>124467102</v>
+        <v>124467067</v>
       </c>
       <c r="B107" t="n">
-        <v>57513</v>
+        <v>74901</v>
       </c>
       <c r="C107" t="inlineStr">
         <is>
@@ -11505,39 +11505,34 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>100109</v>
+        <v>6440</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
-      <c r="M107" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P107" t="inlineStr">
         <is>
           <t>Rymån, Dlr</t>
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>453847</v>
+        <v>453900</v>
       </c>
       <c r="R107" t="n">
-        <v>6808007</v>
+        <v>6808014</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -11596,7 +11591,7 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>124467078</v>
+        <v>124467082</v>
       </c>
       <c r="B108" t="n">
         <v>78810</v>
@@ -11636,10 +11631,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>453872</v>
+        <v>453811</v>
       </c>
       <c r="R108" t="n">
-        <v>6807869</v>
+        <v>6808100</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -11698,10 +11693,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>124467085</v>
+        <v>124467097</v>
       </c>
       <c r="B109" t="n">
-        <v>78810</v>
+        <v>57513</v>
       </c>
       <c r="C109" t="inlineStr">
         <is>
@@ -11714,34 +11709,39 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
+      <c r="M109" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P109" t="inlineStr">
         <is>
           <t>Rymån, Dlr</t>
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>453807</v>
+        <v>453864</v>
       </c>
       <c r="R109" t="n">
-        <v>6808128</v>
+        <v>6807819</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -11800,7 +11800,7 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>124467082</v>
+        <v>124467078</v>
       </c>
       <c r="B110" t="n">
         <v>78810</v>
@@ -11840,10 +11840,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>453811</v>
+        <v>453872</v>
       </c>
       <c r="R110" t="n">
-        <v>6808100</v>
+        <v>6807869</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>

--- a/artfynd/A 31144-2024 artfynd.xlsx
+++ b/artfynd/A 31144-2024 artfynd.xlsx
@@ -10964,10 +10964,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>124467085</v>
+        <v>124467097</v>
       </c>
       <c r="B102" t="n">
-        <v>78810</v>
+        <v>57513</v>
       </c>
       <c r="C102" t="inlineStr">
         <is>
@@ -10980,34 +10980,39 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
+      <c r="M102" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P102" t="inlineStr">
         <is>
           <t>Rymån, Dlr</t>
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>453807</v>
+        <v>453864</v>
       </c>
       <c r="R102" t="n">
-        <v>6808128</v>
+        <v>6807819</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -11066,10 +11071,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>124467093</v>
+        <v>124467085</v>
       </c>
       <c r="B103" t="n">
-        <v>5176</v>
+        <v>78810</v>
       </c>
       <c r="C103" t="inlineStr">
         <is>
@@ -11078,43 +11083,38 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>100526</v>
+        <v>6425</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
-      <c r="M103" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P103" t="inlineStr">
         <is>
           <t>Rymån, Dlr</t>
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>453835</v>
+        <v>453807</v>
       </c>
       <c r="R103" t="n">
-        <v>6808062</v>
+        <v>6808128</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -11173,7 +11173,7 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>124467094</v>
+        <v>124467102</v>
       </c>
       <c r="B104" t="n">
         <v>57513</v>
@@ -11218,10 +11218,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>453866</v>
+        <v>453847</v>
       </c>
       <c r="R104" t="n">
-        <v>6807817</v>
+        <v>6808007</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -11280,7 +11280,7 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>124467080</v>
+        <v>124467082</v>
       </c>
       <c r="B105" t="n">
         <v>78810</v>
@@ -11320,10 +11320,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>453826</v>
+        <v>453811</v>
       </c>
       <c r="R105" t="n">
-        <v>6808085</v>
+        <v>6808100</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11382,10 +11382,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>124467102</v>
+        <v>124467080</v>
       </c>
       <c r="B106" t="n">
-        <v>57513</v>
+        <v>78810</v>
       </c>
       <c r="C106" t="inlineStr">
         <is>
@@ -11398,39 +11398,34 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
-      <c r="M106" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P106" t="inlineStr">
         <is>
           <t>Rymån, Dlr</t>
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>453847</v>
+        <v>453826</v>
       </c>
       <c r="R106" t="n">
-        <v>6808007</v>
+        <v>6808085</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11489,10 +11484,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>124467067</v>
+        <v>124467099</v>
       </c>
       <c r="B107" t="n">
-        <v>74901</v>
+        <v>57513</v>
       </c>
       <c r="C107" t="inlineStr">
         <is>
@@ -11505,34 +11500,39 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>6440</v>
+        <v>100109</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
+      <c r="M107" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P107" t="inlineStr">
         <is>
           <t>Rymån, Dlr</t>
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>453900</v>
+        <v>453871</v>
       </c>
       <c r="R107" t="n">
-        <v>6808014</v>
+        <v>6807887</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -11591,10 +11591,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>124467082</v>
+        <v>124467067</v>
       </c>
       <c r="B108" t="n">
-        <v>78810</v>
+        <v>74901</v>
       </c>
       <c r="C108" t="inlineStr">
         <is>
@@ -11607,21 +11607,21 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
@@ -11631,10 +11631,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>453811</v>
+        <v>453900</v>
       </c>
       <c r="R108" t="n">
-        <v>6808100</v>
+        <v>6808014</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -11693,10 +11693,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>124467097</v>
+        <v>124467078</v>
       </c>
       <c r="B109" t="n">
-        <v>57513</v>
+        <v>78810</v>
       </c>
       <c r="C109" t="inlineStr">
         <is>
@@ -11709,39 +11709,34 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
-      <c r="M109" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P109" t="inlineStr">
         <is>
           <t>Rymån, Dlr</t>
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>453864</v>
+        <v>453872</v>
       </c>
       <c r="R109" t="n">
-        <v>6807819</v>
+        <v>6807869</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -11800,10 +11795,10 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>124467078</v>
+        <v>124467093</v>
       </c>
       <c r="B110" t="n">
-        <v>78810</v>
+        <v>5176</v>
       </c>
       <c r="C110" t="inlineStr">
         <is>
@@ -11812,38 +11807,43 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E110" t="n">
-        <v>6425</v>
+        <v>100526</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
+      <c r="M110" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P110" t="inlineStr">
         <is>
           <t>Rymån, Dlr</t>
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>453872</v>
+        <v>453835</v>
       </c>
       <c r="R110" t="n">
-        <v>6807869</v>
+        <v>6808062</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -11902,7 +11902,7 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>124467099</v>
+        <v>124467094</v>
       </c>
       <c r="B111" t="n">
         <v>57513</v>
@@ -11947,10 +11947,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>453871</v>
+        <v>453866</v>
       </c>
       <c r="R111" t="n">
-        <v>6807887</v>
+        <v>6807817</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>

--- a/artfynd/A 31144-2024 artfynd.xlsx
+++ b/artfynd/A 31144-2024 artfynd.xlsx
@@ -11173,10 +11173,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>124467102</v>
+        <v>124467082</v>
       </c>
       <c r="B104" t="n">
-        <v>57513</v>
+        <v>78810</v>
       </c>
       <c r="C104" t="inlineStr">
         <is>
@@ -11189,39 +11189,34 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
-      <c r="M104" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P104" t="inlineStr">
         <is>
           <t>Rymån, Dlr</t>
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>453847</v>
+        <v>453811</v>
       </c>
       <c r="R104" t="n">
-        <v>6808007</v>
+        <v>6808100</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -11280,10 +11275,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>124467082</v>
+        <v>124467102</v>
       </c>
       <c r="B105" t="n">
-        <v>78810</v>
+        <v>57513</v>
       </c>
       <c r="C105" t="inlineStr">
         <is>
@@ -11296,34 +11291,39 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
+      <c r="M105" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P105" t="inlineStr">
         <is>
           <t>Rymån, Dlr</t>
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>453811</v>
+        <v>453847</v>
       </c>
       <c r="R105" t="n">
-        <v>6808100</v>
+        <v>6808007</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>

--- a/artfynd/A 31144-2024 artfynd.xlsx
+++ b/artfynd/A 31144-2024 artfynd.xlsx
@@ -10964,10 +10964,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>124467097</v>
+        <v>124467085</v>
       </c>
       <c r="B102" t="n">
-        <v>57513</v>
+        <v>78810</v>
       </c>
       <c r="C102" t="inlineStr">
         <is>
@@ -10980,39 +10980,34 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
-      <c r="M102" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P102" t="inlineStr">
         <is>
           <t>Rymån, Dlr</t>
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>453864</v>
+        <v>453807</v>
       </c>
       <c r="R102" t="n">
-        <v>6807819</v>
+        <v>6808128</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -11071,7 +11066,7 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>124467085</v>
+        <v>124467080</v>
       </c>
       <c r="B103" t="n">
         <v>78810</v>
@@ -11111,10 +11106,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>453807</v>
+        <v>453826</v>
       </c>
       <c r="R103" t="n">
-        <v>6808128</v>
+        <v>6808085</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -11173,10 +11168,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>124467082</v>
+        <v>124467097</v>
       </c>
       <c r="B104" t="n">
-        <v>78810</v>
+        <v>57513</v>
       </c>
       <c r="C104" t="inlineStr">
         <is>
@@ -11189,34 +11184,39 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
+      <c r="M104" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P104" t="inlineStr">
         <is>
           <t>Rymån, Dlr</t>
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>453811</v>
+        <v>453864</v>
       </c>
       <c r="R104" t="n">
-        <v>6808100</v>
+        <v>6807819</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -11275,10 +11275,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>124467102</v>
+        <v>124467078</v>
       </c>
       <c r="B105" t="n">
-        <v>57513</v>
+        <v>78810</v>
       </c>
       <c r="C105" t="inlineStr">
         <is>
@@ -11291,39 +11291,34 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
-      <c r="M105" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P105" t="inlineStr">
         <is>
           <t>Rymån, Dlr</t>
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>453847</v>
+        <v>453872</v>
       </c>
       <c r="R105" t="n">
-        <v>6808007</v>
+        <v>6807869</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11382,7 +11377,7 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>124467080</v>
+        <v>124467082</v>
       </c>
       <c r="B106" t="n">
         <v>78810</v>
@@ -11422,10 +11417,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>453826</v>
+        <v>453811</v>
       </c>
       <c r="R106" t="n">
-        <v>6808085</v>
+        <v>6808100</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11484,10 +11479,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>124467099</v>
+        <v>124467067</v>
       </c>
       <c r="B107" t="n">
-        <v>57513</v>
+        <v>74901</v>
       </c>
       <c r="C107" t="inlineStr">
         <is>
@@ -11500,39 +11495,34 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>100109</v>
+        <v>6440</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
-      <c r="M107" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P107" t="inlineStr">
         <is>
           <t>Rymån, Dlr</t>
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>453871</v>
+        <v>453900</v>
       </c>
       <c r="R107" t="n">
-        <v>6807887</v>
+        <v>6808014</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -11591,10 +11581,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>124467067</v>
+        <v>124467093</v>
       </c>
       <c r="B108" t="n">
-        <v>74901</v>
+        <v>5176</v>
       </c>
       <c r="C108" t="inlineStr">
         <is>
@@ -11603,38 +11593,43 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E108" t="n">
-        <v>6440</v>
+        <v>100526</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
+      <c r="M108" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P108" t="inlineStr">
         <is>
           <t>Rymån, Dlr</t>
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>453900</v>
+        <v>453835</v>
       </c>
       <c r="R108" t="n">
-        <v>6808014</v>
+        <v>6808062</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -11693,10 +11688,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>124467078</v>
+        <v>124467099</v>
       </c>
       <c r="B109" t="n">
-        <v>78810</v>
+        <v>57513</v>
       </c>
       <c r="C109" t="inlineStr">
         <is>
@@ -11709,34 +11704,39 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
+      <c r="M109" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P109" t="inlineStr">
         <is>
           <t>Rymån, Dlr</t>
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>453872</v>
+        <v>453871</v>
       </c>
       <c r="R109" t="n">
-        <v>6807869</v>
+        <v>6807887</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -11795,10 +11795,10 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>124467093</v>
+        <v>124467102</v>
       </c>
       <c r="B110" t="n">
-        <v>5176</v>
+        <v>57513</v>
       </c>
       <c r="C110" t="inlineStr">
         <is>
@@ -11807,31 +11807,31 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E110" t="n">
-        <v>100526</v>
+        <v>100109</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
       <c r="M110" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P110" t="inlineStr">
@@ -11840,10 +11840,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>453835</v>
+        <v>453847</v>
       </c>
       <c r="R110" t="n">
-        <v>6808062</v>
+        <v>6808007</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>

--- a/artfynd/A 31144-2024 artfynd.xlsx
+++ b/artfynd/A 31144-2024 artfynd.xlsx
@@ -10964,7 +10964,7 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>124467085</v>
+        <v>124467082</v>
       </c>
       <c r="B102" t="n">
         <v>78810</v>
@@ -11004,10 +11004,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>453807</v>
+        <v>453811</v>
       </c>
       <c r="R102" t="n">
-        <v>6808128</v>
+        <v>6808100</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -11066,7 +11066,7 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>124467080</v>
+        <v>124467078</v>
       </c>
       <c r="B103" t="n">
         <v>78810</v>
@@ -11106,10 +11106,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>453826</v>
+        <v>453872</v>
       </c>
       <c r="R103" t="n">
-        <v>6808085</v>
+        <v>6807869</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -11168,10 +11168,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>124467097</v>
+        <v>124467093</v>
       </c>
       <c r="B104" t="n">
-        <v>57513</v>
+        <v>5176</v>
       </c>
       <c r="C104" t="inlineStr">
         <is>
@@ -11180,31 +11180,31 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E104" t="n">
-        <v>100109</v>
+        <v>100526</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
       <c r="M104" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P104" t="inlineStr">
@@ -11213,10 +11213,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>453864</v>
+        <v>453835</v>
       </c>
       <c r="R104" t="n">
-        <v>6807819</v>
+        <v>6808062</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -11275,10 +11275,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>124467078</v>
+        <v>124467094</v>
       </c>
       <c r="B105" t="n">
-        <v>78810</v>
+        <v>57513</v>
       </c>
       <c r="C105" t="inlineStr">
         <is>
@@ -11291,34 +11291,39 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
+      <c r="M105" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P105" t="inlineStr">
         <is>
           <t>Rymån, Dlr</t>
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>453872</v>
+        <v>453866</v>
       </c>
       <c r="R105" t="n">
-        <v>6807869</v>
+        <v>6807817</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11377,7 +11382,7 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>124467082</v>
+        <v>124467080</v>
       </c>
       <c r="B106" t="n">
         <v>78810</v>
@@ -11417,10 +11422,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>453811</v>
+        <v>453826</v>
       </c>
       <c r="R106" t="n">
-        <v>6808100</v>
+        <v>6808085</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11581,10 +11586,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>124467093</v>
+        <v>124467085</v>
       </c>
       <c r="B108" t="n">
-        <v>5176</v>
+        <v>78810</v>
       </c>
       <c r="C108" t="inlineStr">
         <is>
@@ -11593,43 +11598,38 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E108" t="n">
-        <v>100526</v>
+        <v>6425</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
-      <c r="M108" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P108" t="inlineStr">
         <is>
           <t>Rymån, Dlr</t>
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>453835</v>
+        <v>453807</v>
       </c>
       <c r="R108" t="n">
-        <v>6808062</v>
+        <v>6808128</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -11688,7 +11688,7 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>124467099</v>
+        <v>124467097</v>
       </c>
       <c r="B109" t="n">
         <v>57513</v>
@@ -11733,10 +11733,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>453871</v>
+        <v>453864</v>
       </c>
       <c r="R109" t="n">
-        <v>6807887</v>
+        <v>6807819</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -11902,7 +11902,7 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>124467094</v>
+        <v>124467099</v>
       </c>
       <c r="B111" t="n">
         <v>57513</v>
@@ -11947,10 +11947,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>453866</v>
+        <v>453871</v>
       </c>
       <c r="R111" t="n">
-        <v>6807817</v>
+        <v>6807887</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>

--- a/artfynd/A 31144-2024 artfynd.xlsx
+++ b/artfynd/A 31144-2024 artfynd.xlsx
@@ -10964,10 +10964,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>124467082</v>
+        <v>124467094</v>
       </c>
       <c r="B102" t="n">
-        <v>78810</v>
+        <v>57513</v>
       </c>
       <c r="C102" t="inlineStr">
         <is>
@@ -10980,34 +10980,39 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
+      <c r="M102" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P102" t="inlineStr">
         <is>
           <t>Rymån, Dlr</t>
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>453811</v>
+        <v>453866</v>
       </c>
       <c r="R102" t="n">
-        <v>6808100</v>
+        <v>6807817</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -11066,7 +11071,7 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>124467078</v>
+        <v>124467080</v>
       </c>
       <c r="B103" t="n">
         <v>78810</v>
@@ -11106,10 +11111,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>453872</v>
+        <v>453826</v>
       </c>
       <c r="R103" t="n">
-        <v>6807869</v>
+        <v>6808085</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -11168,10 +11173,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>124467093</v>
+        <v>124467099</v>
       </c>
       <c r="B104" t="n">
-        <v>5176</v>
+        <v>57513</v>
       </c>
       <c r="C104" t="inlineStr">
         <is>
@@ -11180,31 +11185,31 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E104" t="n">
-        <v>100526</v>
+        <v>100109</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
       <c r="M104" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P104" t="inlineStr">
@@ -11213,10 +11218,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>453835</v>
+        <v>453871</v>
       </c>
       <c r="R104" t="n">
-        <v>6808062</v>
+        <v>6807887</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -11275,10 +11280,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>124467094</v>
+        <v>124467085</v>
       </c>
       <c r="B105" t="n">
-        <v>57513</v>
+        <v>78810</v>
       </c>
       <c r="C105" t="inlineStr">
         <is>
@@ -11291,39 +11296,34 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
-      <c r="M105" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P105" t="inlineStr">
         <is>
           <t>Rymån, Dlr</t>
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>453866</v>
+        <v>453807</v>
       </c>
       <c r="R105" t="n">
-        <v>6807817</v>
+        <v>6808128</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11382,10 +11382,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>124467080</v>
+        <v>124467097</v>
       </c>
       <c r="B106" t="n">
-        <v>78810</v>
+        <v>57513</v>
       </c>
       <c r="C106" t="inlineStr">
         <is>
@@ -11398,34 +11398,39 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
+      <c r="M106" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P106" t="inlineStr">
         <is>
           <t>Rymån, Dlr</t>
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>453826</v>
+        <v>453864</v>
       </c>
       <c r="R106" t="n">
-        <v>6808085</v>
+        <v>6807819</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11586,7 +11591,7 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>124467085</v>
+        <v>124467082</v>
       </c>
       <c r="B108" t="n">
         <v>78810</v>
@@ -11626,10 +11631,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>453807</v>
+        <v>453811</v>
       </c>
       <c r="R108" t="n">
-        <v>6808128</v>
+        <v>6808100</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -11688,7 +11693,7 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>124467097</v>
+        <v>124467102</v>
       </c>
       <c r="B109" t="n">
         <v>57513</v>
@@ -11733,10 +11738,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>453864</v>
+        <v>453847</v>
       </c>
       <c r="R109" t="n">
-        <v>6807819</v>
+        <v>6808007</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -11795,10 +11800,10 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>124467102</v>
+        <v>124467078</v>
       </c>
       <c r="B110" t="n">
-        <v>57513</v>
+        <v>78810</v>
       </c>
       <c r="C110" t="inlineStr">
         <is>
@@ -11811,39 +11816,34 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
-      <c r="M110" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P110" t="inlineStr">
         <is>
           <t>Rymån, Dlr</t>
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>453847</v>
+        <v>453872</v>
       </c>
       <c r="R110" t="n">
-        <v>6808007</v>
+        <v>6807869</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -11902,10 +11902,10 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>124467099</v>
+        <v>124467093</v>
       </c>
       <c r="B111" t="n">
-        <v>57513</v>
+        <v>5176</v>
       </c>
       <c r="C111" t="inlineStr">
         <is>
@@ -11914,31 +11914,31 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E111" t="n">
-        <v>100109</v>
+        <v>100526</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
       <c r="M111" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P111" t="inlineStr">
@@ -11947,10 +11947,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>453871</v>
+        <v>453835</v>
       </c>
       <c r="R111" t="n">
-        <v>6807887</v>
+        <v>6808062</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>

--- a/artfynd/A 31144-2024 artfynd.xlsx
+++ b/artfynd/A 31144-2024 artfynd.xlsx
@@ -11591,10 +11591,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>124467082</v>
+        <v>124467102</v>
       </c>
       <c r="B108" t="n">
-        <v>78810</v>
+        <v>57513</v>
       </c>
       <c r="C108" t="inlineStr">
         <is>
@@ -11607,34 +11607,39 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
+      <c r="M108" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P108" t="inlineStr">
         <is>
           <t>Rymån, Dlr</t>
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>453811</v>
+        <v>453847</v>
       </c>
       <c r="R108" t="n">
-        <v>6808100</v>
+        <v>6808007</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -11693,10 +11698,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>124467102</v>
+        <v>124467082</v>
       </c>
       <c r="B109" t="n">
-        <v>57513</v>
+        <v>78810</v>
       </c>
       <c r="C109" t="inlineStr">
         <is>
@@ -11709,39 +11714,34 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
-      <c r="M109" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P109" t="inlineStr">
         <is>
           <t>Rymån, Dlr</t>
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>453847</v>
+        <v>453811</v>
       </c>
       <c r="R109" t="n">
-        <v>6808007</v>
+        <v>6808100</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>

--- a/artfynd/A 31144-2024 artfynd.xlsx
+++ b/artfynd/A 31144-2024 artfynd.xlsx
@@ -10964,10 +10964,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>124467094</v>
+        <v>124467080</v>
       </c>
       <c r="B102" t="n">
-        <v>57513</v>
+        <v>78810</v>
       </c>
       <c r="C102" t="inlineStr">
         <is>
@@ -10980,39 +10980,34 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
-      <c r="M102" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P102" t="inlineStr">
         <is>
           <t>Rymån, Dlr</t>
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>453866</v>
+        <v>453826</v>
       </c>
       <c r="R102" t="n">
-        <v>6807817</v>
+        <v>6808085</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -11071,10 +11066,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>124467080</v>
+        <v>124467094</v>
       </c>
       <c r="B103" t="n">
-        <v>78810</v>
+        <v>57513</v>
       </c>
       <c r="C103" t="inlineStr">
         <is>
@@ -11087,34 +11082,39 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
+      <c r="M103" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P103" t="inlineStr">
         <is>
           <t>Rymån, Dlr</t>
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>453826</v>
+        <v>453866</v>
       </c>
       <c r="R103" t="n">
-        <v>6808085</v>
+        <v>6807817</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -11280,10 +11280,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>124467085</v>
+        <v>124467093</v>
       </c>
       <c r="B105" t="n">
-        <v>78810</v>
+        <v>5176</v>
       </c>
       <c r="C105" t="inlineStr">
         <is>
@@ -11292,38 +11292,43 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E105" t="n">
-        <v>6425</v>
+        <v>100526</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
+      <c r="M105" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P105" t="inlineStr">
         <is>
           <t>Rymån, Dlr</t>
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>453807</v>
+        <v>453835</v>
       </c>
       <c r="R105" t="n">
-        <v>6808128</v>
+        <v>6808062</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11382,7 +11387,7 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>124467097</v>
+        <v>124467102</v>
       </c>
       <c r="B106" t="n">
         <v>57513</v>
@@ -11427,10 +11432,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>453864</v>
+        <v>453847</v>
       </c>
       <c r="R106" t="n">
-        <v>6807819</v>
+        <v>6808007</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11489,10 +11494,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>124467067</v>
+        <v>124467078</v>
       </c>
       <c r="B107" t="n">
-        <v>74901</v>
+        <v>78810</v>
       </c>
       <c r="C107" t="inlineStr">
         <is>
@@ -11505,21 +11510,21 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
@@ -11529,10 +11534,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>453900</v>
+        <v>453872</v>
       </c>
       <c r="R107" t="n">
-        <v>6808014</v>
+        <v>6807869</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -11591,10 +11596,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>124467102</v>
+        <v>124467085</v>
       </c>
       <c r="B108" t="n">
-        <v>57513</v>
+        <v>78810</v>
       </c>
       <c r="C108" t="inlineStr">
         <is>
@@ -11607,39 +11612,34 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
-      <c r="M108" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P108" t="inlineStr">
         <is>
           <t>Rymån, Dlr</t>
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>453847</v>
+        <v>453807</v>
       </c>
       <c r="R108" t="n">
-        <v>6808007</v>
+        <v>6808128</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -11698,10 +11698,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>124467082</v>
+        <v>124467067</v>
       </c>
       <c r="B109" t="n">
-        <v>78810</v>
+        <v>74901</v>
       </c>
       <c r="C109" t="inlineStr">
         <is>
@@ -11714,21 +11714,21 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
@@ -11738,10 +11738,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>453811</v>
+        <v>453900</v>
       </c>
       <c r="R109" t="n">
-        <v>6808100</v>
+        <v>6808014</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -11800,7 +11800,7 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>124467078</v>
+        <v>124467082</v>
       </c>
       <c r="B110" t="n">
         <v>78810</v>
@@ -11840,10 +11840,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>453872</v>
+        <v>453811</v>
       </c>
       <c r="R110" t="n">
-        <v>6807869</v>
+        <v>6808100</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -11902,10 +11902,10 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>124467093</v>
+        <v>124467097</v>
       </c>
       <c r="B111" t="n">
-        <v>5176</v>
+        <v>57513</v>
       </c>
       <c r="C111" t="inlineStr">
         <is>
@@ -11914,31 +11914,31 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E111" t="n">
-        <v>100526</v>
+        <v>100109</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
       <c r="M111" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P111" t="inlineStr">
@@ -11947,10 +11947,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>453835</v>
+        <v>453864</v>
       </c>
       <c r="R111" t="n">
-        <v>6808062</v>
+        <v>6807819</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>

--- a/artfynd/A 31144-2024 artfynd.xlsx
+++ b/artfynd/A 31144-2024 artfynd.xlsx
@@ -10964,10 +10964,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>124467080</v>
+        <v>124467097</v>
       </c>
       <c r="B102" t="n">
-        <v>78810</v>
+        <v>57513</v>
       </c>
       <c r="C102" t="inlineStr">
         <is>
@@ -10980,34 +10980,39 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
+      <c r="M102" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P102" t="inlineStr">
         <is>
           <t>Rymån, Dlr</t>
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>453826</v>
+        <v>453864</v>
       </c>
       <c r="R102" t="n">
-        <v>6808085</v>
+        <v>6807819</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -11173,10 +11178,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>124467099</v>
+        <v>124467093</v>
       </c>
       <c r="B104" t="n">
-        <v>57513</v>
+        <v>5176</v>
       </c>
       <c r="C104" t="inlineStr">
         <is>
@@ -11185,31 +11190,31 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E104" t="n">
-        <v>100109</v>
+        <v>100526</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
       <c r="M104" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P104" t="inlineStr">
@@ -11218,10 +11223,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>453871</v>
+        <v>453835</v>
       </c>
       <c r="R104" t="n">
-        <v>6807887</v>
+        <v>6808062</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -11280,10 +11285,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>124467093</v>
+        <v>124467080</v>
       </c>
       <c r="B105" t="n">
-        <v>5176</v>
+        <v>78810</v>
       </c>
       <c r="C105" t="inlineStr">
         <is>
@@ -11292,43 +11297,38 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E105" t="n">
-        <v>100526</v>
+        <v>6425</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
-      <c r="M105" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P105" t="inlineStr">
         <is>
           <t>Rymån, Dlr</t>
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>453835</v>
+        <v>453826</v>
       </c>
       <c r="R105" t="n">
-        <v>6808062</v>
+        <v>6808085</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11387,10 +11387,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>124467102</v>
+        <v>124467085</v>
       </c>
       <c r="B106" t="n">
-        <v>57513</v>
+        <v>78810</v>
       </c>
       <c r="C106" t="inlineStr">
         <is>
@@ -11403,39 +11403,34 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
-      <c r="M106" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P106" t="inlineStr">
         <is>
           <t>Rymån, Dlr</t>
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>453847</v>
+        <v>453807</v>
       </c>
       <c r="R106" t="n">
-        <v>6808007</v>
+        <v>6808128</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11494,10 +11489,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>124467078</v>
+        <v>124467099</v>
       </c>
       <c r="B107" t="n">
-        <v>78810</v>
+        <v>57513</v>
       </c>
       <c r="C107" t="inlineStr">
         <is>
@@ -11510,34 +11505,39 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
+      <c r="M107" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P107" t="inlineStr">
         <is>
           <t>Rymån, Dlr</t>
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>453872</v>
+        <v>453871</v>
       </c>
       <c r="R107" t="n">
-        <v>6807869</v>
+        <v>6807887</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -11596,7 +11596,7 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>124467085</v>
+        <v>124467078</v>
       </c>
       <c r="B108" t="n">
         <v>78810</v>
@@ -11636,10 +11636,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>453807</v>
+        <v>453872</v>
       </c>
       <c r="R108" t="n">
-        <v>6808128</v>
+        <v>6807869</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -11800,10 +11800,10 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>124467082</v>
+        <v>124467102</v>
       </c>
       <c r="B110" t="n">
-        <v>78810</v>
+        <v>57513</v>
       </c>
       <c r="C110" t="inlineStr">
         <is>
@@ -11816,34 +11816,39 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
+      <c r="M110" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P110" t="inlineStr">
         <is>
           <t>Rymån, Dlr</t>
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>453811</v>
+        <v>453847</v>
       </c>
       <c r="R110" t="n">
-        <v>6808100</v>
+        <v>6808007</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -11902,10 +11907,10 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>124467097</v>
+        <v>124467082</v>
       </c>
       <c r="B111" t="n">
-        <v>57513</v>
+        <v>78810</v>
       </c>
       <c r="C111" t="inlineStr">
         <is>
@@ -11918,39 +11923,34 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
-      <c r="M111" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P111" t="inlineStr">
         <is>
           <t>Rymån, Dlr</t>
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>453864</v>
+        <v>453811</v>
       </c>
       <c r="R111" t="n">
-        <v>6807819</v>
+        <v>6808100</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>

--- a/artfynd/A 31144-2024 artfynd.xlsx
+++ b/artfynd/A 31144-2024 artfynd.xlsx
@@ -10964,10 +10964,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>124467097</v>
+        <v>124467085</v>
       </c>
       <c r="B102" t="n">
-        <v>57513</v>
+        <v>78810</v>
       </c>
       <c r="C102" t="inlineStr">
         <is>
@@ -10980,39 +10980,34 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
-      <c r="M102" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P102" t="inlineStr">
         <is>
           <t>Rymån, Dlr</t>
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>453864</v>
+        <v>453807</v>
       </c>
       <c r="R102" t="n">
-        <v>6807819</v>
+        <v>6808128</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -11071,7 +11066,7 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>124467094</v>
+        <v>124467097</v>
       </c>
       <c r="B103" t="n">
         <v>57513</v>
@@ -11116,10 +11111,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>453866</v>
+        <v>453864</v>
       </c>
       <c r="R103" t="n">
-        <v>6807817</v>
+        <v>6807819</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -11178,10 +11173,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>124467093</v>
+        <v>124467099</v>
       </c>
       <c r="B104" t="n">
-        <v>5176</v>
+        <v>57513</v>
       </c>
       <c r="C104" t="inlineStr">
         <is>
@@ -11190,31 +11185,31 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E104" t="n">
-        <v>100526</v>
+        <v>100109</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
       <c r="M104" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P104" t="inlineStr">
@@ -11223,10 +11218,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>453835</v>
+        <v>453871</v>
       </c>
       <c r="R104" t="n">
-        <v>6808062</v>
+        <v>6807887</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -11387,10 +11382,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>124467085</v>
+        <v>124467067</v>
       </c>
       <c r="B106" t="n">
-        <v>78810</v>
+        <v>74901</v>
       </c>
       <c r="C106" t="inlineStr">
         <is>
@@ -11403,21 +11398,21 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
@@ -11427,10 +11422,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>453807</v>
+        <v>453900</v>
       </c>
       <c r="R106" t="n">
-        <v>6808128</v>
+        <v>6808014</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11489,7 +11484,7 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>124467099</v>
+        <v>124467102</v>
       </c>
       <c r="B107" t="n">
         <v>57513</v>
@@ -11534,10 +11529,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>453871</v>
+        <v>453847</v>
       </c>
       <c r="R107" t="n">
-        <v>6807887</v>
+        <v>6808007</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -11698,10 +11693,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>124467067</v>
+        <v>124467094</v>
       </c>
       <c r="B109" t="n">
-        <v>74901</v>
+        <v>57513</v>
       </c>
       <c r="C109" t="inlineStr">
         <is>
@@ -11714,34 +11709,39 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>6440</v>
+        <v>100109</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
+      <c r="M109" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P109" t="inlineStr">
         <is>
           <t>Rymån, Dlr</t>
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>453900</v>
+        <v>453866</v>
       </c>
       <c r="R109" t="n">
-        <v>6808014</v>
+        <v>6807817</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -11800,10 +11800,10 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>124467102</v>
+        <v>124467082</v>
       </c>
       <c r="B110" t="n">
-        <v>57513</v>
+        <v>78810</v>
       </c>
       <c r="C110" t="inlineStr">
         <is>
@@ -11816,39 +11816,34 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
-      <c r="M110" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P110" t="inlineStr">
         <is>
           <t>Rymån, Dlr</t>
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>453847</v>
+        <v>453811</v>
       </c>
       <c r="R110" t="n">
-        <v>6808007</v>
+        <v>6808100</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -11907,10 +11902,10 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>124467082</v>
+        <v>124467093</v>
       </c>
       <c r="B111" t="n">
-        <v>78810</v>
+        <v>5176</v>
       </c>
       <c r="C111" t="inlineStr">
         <is>
@@ -11919,38 +11914,43 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E111" t="n">
-        <v>6425</v>
+        <v>100526</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
+      <c r="M111" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P111" t="inlineStr">
         <is>
           <t>Rymån, Dlr</t>
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>453811</v>
+        <v>453835</v>
       </c>
       <c r="R111" t="n">
-        <v>6808100</v>
+        <v>6808062</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>

--- a/artfynd/A 31144-2024 artfynd.xlsx
+++ b/artfynd/A 31144-2024 artfynd.xlsx
@@ -11066,10 +11066,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>124467097</v>
+        <v>124467082</v>
       </c>
       <c r="B103" t="n">
-        <v>57513</v>
+        <v>78810</v>
       </c>
       <c r="C103" t="inlineStr">
         <is>
@@ -11082,39 +11082,34 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
-      <c r="M103" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P103" t="inlineStr">
         <is>
           <t>Rymån, Dlr</t>
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>453864</v>
+        <v>453811</v>
       </c>
       <c r="R103" t="n">
-        <v>6807819</v>
+        <v>6808100</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -11280,7 +11275,7 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>124467080</v>
+        <v>124467078</v>
       </c>
       <c r="B105" t="n">
         <v>78810</v>
@@ -11320,10 +11315,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>453826</v>
+        <v>453872</v>
       </c>
       <c r="R105" t="n">
-        <v>6808085</v>
+        <v>6807869</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11382,10 +11377,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>124467067</v>
+        <v>124467097</v>
       </c>
       <c r="B106" t="n">
-        <v>74901</v>
+        <v>57513</v>
       </c>
       <c r="C106" t="inlineStr">
         <is>
@@ -11398,34 +11393,39 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>6440</v>
+        <v>100109</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
+      <c r="M106" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P106" t="inlineStr">
         <is>
           <t>Rymån, Dlr</t>
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>453900</v>
+        <v>453864</v>
       </c>
       <c r="R106" t="n">
-        <v>6808014</v>
+        <v>6807819</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11484,7 +11484,7 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>124467102</v>
+        <v>124467094</v>
       </c>
       <c r="B107" t="n">
         <v>57513</v>
@@ -11529,10 +11529,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>453847</v>
+        <v>453866</v>
       </c>
       <c r="R107" t="n">
-        <v>6808007</v>
+        <v>6807817</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -11591,10 +11591,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>124467078</v>
+        <v>124467102</v>
       </c>
       <c r="B108" t="n">
-        <v>78810</v>
+        <v>57513</v>
       </c>
       <c r="C108" t="inlineStr">
         <is>
@@ -11607,34 +11607,39 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
+      <c r="M108" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P108" t="inlineStr">
         <is>
           <t>Rymån, Dlr</t>
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>453872</v>
+        <v>453847</v>
       </c>
       <c r="R108" t="n">
-        <v>6807869</v>
+        <v>6808007</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -11693,10 +11698,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>124467094</v>
+        <v>124467067</v>
       </c>
       <c r="B109" t="n">
-        <v>57513</v>
+        <v>74901</v>
       </c>
       <c r="C109" t="inlineStr">
         <is>
@@ -11709,39 +11714,34 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>100109</v>
+        <v>6440</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
-      <c r="M109" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P109" t="inlineStr">
         <is>
           <t>Rymån, Dlr</t>
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>453866</v>
+        <v>453900</v>
       </c>
       <c r="R109" t="n">
-        <v>6807817</v>
+        <v>6808014</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -11800,7 +11800,7 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>124467082</v>
+        <v>124467080</v>
       </c>
       <c r="B110" t="n">
         <v>78810</v>
@@ -11840,10 +11840,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>453811</v>
+        <v>453826</v>
       </c>
       <c r="R110" t="n">
-        <v>6808100</v>
+        <v>6808085</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>

--- a/artfynd/A 31144-2024 artfynd.xlsx
+++ b/artfynd/A 31144-2024 artfynd.xlsx
@@ -10964,10 +10964,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>124467085</v>
+        <v>124467094</v>
       </c>
       <c r="B102" t="n">
-        <v>78810</v>
+        <v>57513</v>
       </c>
       <c r="C102" t="inlineStr">
         <is>
@@ -10980,34 +10980,39 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
+      <c r="M102" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P102" t="inlineStr">
         <is>
           <t>Rymån, Dlr</t>
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>453807</v>
+        <v>453866</v>
       </c>
       <c r="R102" t="n">
-        <v>6808128</v>
+        <v>6807817</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -11066,7 +11071,7 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>124467082</v>
+        <v>124467078</v>
       </c>
       <c r="B103" t="n">
         <v>78810</v>
@@ -11106,10 +11111,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>453811</v>
+        <v>453872</v>
       </c>
       <c r="R103" t="n">
-        <v>6808100</v>
+        <v>6807869</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -11168,7 +11173,7 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>124467099</v>
+        <v>124467097</v>
       </c>
       <c r="B104" t="n">
         <v>57513</v>
@@ -11213,10 +11218,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>453871</v>
+        <v>453864</v>
       </c>
       <c r="R104" t="n">
-        <v>6807887</v>
+        <v>6807819</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -11275,7 +11280,7 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>124467078</v>
+        <v>124467080</v>
       </c>
       <c r="B105" t="n">
         <v>78810</v>
@@ -11315,10 +11320,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>453872</v>
+        <v>453826</v>
       </c>
       <c r="R105" t="n">
-        <v>6807869</v>
+        <v>6808085</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11377,10 +11382,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>124467097</v>
+        <v>124467082</v>
       </c>
       <c r="B106" t="n">
-        <v>57513</v>
+        <v>78810</v>
       </c>
       <c r="C106" t="inlineStr">
         <is>
@@ -11393,39 +11398,34 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
-      <c r="M106" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P106" t="inlineStr">
         <is>
           <t>Rymån, Dlr</t>
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>453864</v>
+        <v>453811</v>
       </c>
       <c r="R106" t="n">
-        <v>6807819</v>
+        <v>6808100</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11484,10 +11484,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>124467094</v>
+        <v>124467067</v>
       </c>
       <c r="B107" t="n">
-        <v>57513</v>
+        <v>74901</v>
       </c>
       <c r="C107" t="inlineStr">
         <is>
@@ -11500,39 +11500,34 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>100109</v>
+        <v>6440</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
-      <c r="M107" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P107" t="inlineStr">
         <is>
           <t>Rymån, Dlr</t>
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>453866</v>
+        <v>453900</v>
       </c>
       <c r="R107" t="n">
-        <v>6807817</v>
+        <v>6808014</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -11591,10 +11586,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>124467102</v>
+        <v>124467085</v>
       </c>
       <c r="B108" t="n">
-        <v>57513</v>
+        <v>78810</v>
       </c>
       <c r="C108" t="inlineStr">
         <is>
@@ -11607,39 +11602,34 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
-      <c r="M108" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P108" t="inlineStr">
         <is>
           <t>Rymån, Dlr</t>
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>453847</v>
+        <v>453807</v>
       </c>
       <c r="R108" t="n">
-        <v>6808007</v>
+        <v>6808128</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -11698,10 +11688,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>124467067</v>
+        <v>124467102</v>
       </c>
       <c r="B109" t="n">
-        <v>74901</v>
+        <v>57513</v>
       </c>
       <c r="C109" t="inlineStr">
         <is>
@@ -11714,34 +11704,39 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>6440</v>
+        <v>100109</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
+      <c r="M109" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P109" t="inlineStr">
         <is>
           <t>Rymån, Dlr</t>
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>453900</v>
+        <v>453847</v>
       </c>
       <c r="R109" t="n">
-        <v>6808014</v>
+        <v>6808007</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -11800,10 +11795,10 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>124467080</v>
+        <v>124467099</v>
       </c>
       <c r="B110" t="n">
-        <v>78810</v>
+        <v>57513</v>
       </c>
       <c r="C110" t="inlineStr">
         <is>
@@ -11816,34 +11811,39 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
+      <c r="M110" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P110" t="inlineStr">
         <is>
           <t>Rymån, Dlr</t>
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>453826</v>
+        <v>453871</v>
       </c>
       <c r="R110" t="n">
-        <v>6808085</v>
+        <v>6807887</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>

--- a/artfynd/A 31144-2024 artfynd.xlsx
+++ b/artfynd/A 31144-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY121"/>
+  <dimension ref="A1:AZ121"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119590974</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119590985</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -963,6 +978,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119590986</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1060,6 +1080,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119590987</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1157,6 +1182,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119590988</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1254,6 +1284,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119591025</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1352,6 +1387,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119590970</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1458,6 +1498,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119591100</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1555,6 +1600,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119590999</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1652,6 +1702,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119591001</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1749,6 +1804,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119591002</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1846,6 +1906,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119591003</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1943,6 +2008,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119591099</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2040,6 +2110,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119591032</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2137,6 +2212,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119591033</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2234,6 +2314,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119591034</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2331,6 +2416,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119591035</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2428,6 +2518,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119591036</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2525,6 +2620,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119591037</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2622,6 +2722,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119591038</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2719,6 +2824,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119591039</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2816,6 +2926,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119591040</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -2913,6 +3028,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119591041</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3010,6 +3130,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119591042</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3107,6 +3232,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119591043</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3204,6 +3334,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119591044</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3301,6 +3436,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119591045</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3398,6 +3538,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119591046</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3495,6 +3640,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119591047</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3592,6 +3742,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119591048</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3689,6 +3844,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119591049</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -3786,6 +3946,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119591050</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -3883,6 +4048,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119591051</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -3980,6 +4150,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119591052</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4077,6 +4252,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119591053</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4174,6 +4354,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119591054</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4271,6 +4456,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119591055</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4368,6 +4558,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119591056</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4465,6 +4660,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119591057</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -4562,6 +4762,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119591058</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -4659,6 +4864,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119591059</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -4756,6 +4966,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119591060</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -4853,6 +5068,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119591061</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -4950,6 +5170,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119591062</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5047,6 +5272,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119591064</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5144,6 +5374,11 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119591065</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5241,6 +5476,11 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119591066</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -5338,6 +5578,11 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119591067</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -5435,6 +5680,11 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119591068</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -5532,6 +5782,11 @@
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119591069</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -5629,6 +5884,11 @@
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119591070</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -5726,6 +5986,11 @@
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119591071</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -5823,6 +6088,11 @@
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119591072</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -5920,6 +6190,11 @@
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119591073</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -6017,6 +6292,11 @@
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119591074</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -6114,6 +6394,11 @@
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119591075</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -6211,6 +6496,11 @@
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119591076</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -6308,6 +6598,11 @@
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119591077</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -6405,6 +6700,11 @@
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119591078</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -6502,6 +6802,11 @@
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119591079</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -6599,6 +6904,11 @@
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119591080</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -6696,6 +7006,11 @@
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119591082</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -6793,6 +7108,11 @@
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119591083</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -6890,6 +7210,11 @@
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
+      <c r="AZ65" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119591084</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -6987,6 +7312,11 @@
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
+      <c r="AZ66" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119591085</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -7084,6 +7414,11 @@
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
+      <c r="AZ67" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119591086</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -7181,6 +7516,11 @@
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
+      <c r="AZ68" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119591087</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -7278,6 +7618,11 @@
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
+      <c r="AZ69" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119591088</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -7375,6 +7720,11 @@
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
+      <c r="AZ70" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119591089</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -7472,6 +7822,11 @@
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
+      <c r="AZ71" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119591090</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -7569,6 +7924,11 @@
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
+      <c r="AZ72" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119591091</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -7666,6 +8026,11 @@
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
+      <c r="AZ73" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119591093</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -7763,6 +8128,11 @@
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
+      <c r="AZ74" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119591096</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -7860,6 +8230,11 @@
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
+      <c r="AZ75" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124467078</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -7957,6 +8332,11 @@
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
+      <c r="AZ76" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124467080</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -8054,6 +8434,11 @@
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
+      <c r="AZ77" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124467082</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -8151,6 +8536,11 @@
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
+      <c r="AZ78" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124467085</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -8248,6 +8638,11 @@
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
+      <c r="AZ79" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119590972</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
@@ -8345,6 +8740,11 @@
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
+      <c r="AZ80" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119590973</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
@@ -8442,6 +8842,11 @@
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
+      <c r="AZ81" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124467067</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
@@ -8539,6 +8944,11 @@
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
+      <c r="AZ82" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124467073</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
@@ -8636,6 +9046,11 @@
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
+      <c r="AZ83" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119591026</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
@@ -8733,6 +9148,11 @@
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
+      <c r="AZ84" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119590975</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
@@ -8830,6 +9250,11 @@
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
+      <c r="AZ85" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119590976</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
@@ -8927,6 +9352,11 @@
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
+      <c r="AZ86" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119590977</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
@@ -9024,6 +9454,11 @@
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
+      <c r="AZ87" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119590978</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
@@ -9121,6 +9556,11 @@
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
+      <c r="AZ88" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119590979</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
@@ -9218,6 +9658,11 @@
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
+      <c r="AZ89" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119590980</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
@@ -9315,6 +9760,11 @@
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
+      <c r="AZ90" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119590981</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
@@ -9412,6 +9862,11 @@
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
+      <c r="AZ91" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119590982</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
@@ -9509,6 +9964,11 @@
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
+      <c r="AZ92" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119590983</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
@@ -9606,6 +10066,11 @@
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>
+      <c r="AZ93" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119591015</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
@@ -9713,6 +10178,11 @@
         </is>
       </c>
       <c r="AY94" t="inlineStr"/>
+      <c r="AZ94" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119590969</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
@@ -9815,6 +10285,11 @@
         </is>
       </c>
       <c r="AY95" t="inlineStr"/>
+      <c r="AZ95" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119590990</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
@@ -9917,6 +10392,11 @@
         </is>
       </c>
       <c r="AY96" t="inlineStr"/>
+      <c r="AZ96" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119590991</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
@@ -10019,6 +10499,11 @@
         </is>
       </c>
       <c r="AY97" t="inlineStr"/>
+      <c r="AZ97" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119590992</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
@@ -10126,6 +10611,11 @@
         </is>
       </c>
       <c r="AY98" t="inlineStr"/>
+      <c r="AZ98" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119591006</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
@@ -10233,6 +10723,11 @@
         </is>
       </c>
       <c r="AY99" t="inlineStr"/>
+      <c r="AZ99" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119591007</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
@@ -10340,6 +10835,11 @@
         </is>
       </c>
       <c r="AY100" t="inlineStr"/>
+      <c r="AZ100" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119591008</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
@@ -10447,6 +10947,11 @@
         </is>
       </c>
       <c r="AY101" t="inlineStr"/>
+      <c r="AZ101" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119591009</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="n">
@@ -10554,6 +11059,11 @@
         </is>
       </c>
       <c r="AY102" t="inlineStr"/>
+      <c r="AZ102" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119591010</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
@@ -10656,6 +11166,11 @@
         </is>
       </c>
       <c r="AY103" t="inlineStr"/>
+      <c r="AZ103" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119591097</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="n">
@@ -10758,6 +11273,11 @@
         </is>
       </c>
       <c r="AY104" t="inlineStr"/>
+      <c r="AZ104" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124467075</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="n">
@@ -10860,6 +11380,11 @@
         </is>
       </c>
       <c r="AY105" t="inlineStr"/>
+      <c r="AZ105" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124467094</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="n">
@@ -10962,6 +11487,11 @@
         </is>
       </c>
       <c r="AY106" t="inlineStr"/>
+      <c r="AZ106" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124467097</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="n">
@@ -11064,6 +11594,11 @@
         </is>
       </c>
       <c r="AY107" t="inlineStr"/>
+      <c r="AZ107" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124467099</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="n">
@@ -11166,6 +11701,11 @@
         </is>
       </c>
       <c r="AY108" t="inlineStr"/>
+      <c r="AZ108" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124467102</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="n">
@@ -11263,6 +11803,11 @@
         </is>
       </c>
       <c r="AY109" t="inlineStr"/>
+      <c r="AZ109" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119591101</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="n">
@@ -11365,6 +11910,11 @@
         </is>
       </c>
       <c r="AY110" t="inlineStr"/>
+      <c r="AZ110" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124467093</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="n">
@@ -11462,6 +12012,11 @@
         </is>
       </c>
       <c r="AY111" t="inlineStr"/>
+      <c r="AZ111" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119590996</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="n">
@@ -11559,6 +12114,11 @@
         </is>
       </c>
       <c r="AY112" t="inlineStr"/>
+      <c r="AZ112" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119590997</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="n">
@@ -11656,6 +12216,11 @@
         </is>
       </c>
       <c r="AY113" t="inlineStr"/>
+      <c r="AZ113" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119590998</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="n">
@@ -11753,6 +12318,11 @@
         </is>
       </c>
       <c r="AY114" t="inlineStr"/>
+      <c r="AZ114" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119591011</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="n">
@@ -11850,6 +12420,11 @@
         </is>
       </c>
       <c r="AY115" t="inlineStr"/>
+      <c r="AZ115" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119591012</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="n">
@@ -11956,6 +12531,11 @@
         </is>
       </c>
       <c r="AY116" t="inlineStr"/>
+      <c r="AZ116" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119591019</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="n">
@@ -12053,6 +12633,11 @@
         </is>
       </c>
       <c r="AY117" t="inlineStr"/>
+      <c r="AZ117" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119590994</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="n">
@@ -12150,6 +12735,11 @@
         </is>
       </c>
       <c r="AY118" t="inlineStr"/>
+      <c r="AZ118" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119590995</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="n">
@@ -12247,6 +12837,11 @@
         </is>
       </c>
       <c r="AY119" t="inlineStr"/>
+      <c r="AZ119" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119591022</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="n">
@@ -12344,6 +12939,11 @@
         </is>
       </c>
       <c r="AY120" t="inlineStr"/>
+      <c r="AZ120" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119591023</t>
+        </is>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="n">
@@ -12441,8 +13041,135 @@
         </is>
       </c>
       <c r="AY121" t="inlineStr"/>
+      <c r="AZ121" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119591024</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ67" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ68" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ69" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ70" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ71" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ72" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ73" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ74" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ75" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ76" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ77" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ78" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ79" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ80" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ81" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ82" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ83" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ84" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ85" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ86" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ87" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ88" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ89" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ90" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ91" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ92" r:id="rId91"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ93" r:id="rId92"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ94" r:id="rId93"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ95" r:id="rId94"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ96" r:id="rId95"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ97" r:id="rId96"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ98" r:id="rId97"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ99" r:id="rId98"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ100" r:id="rId99"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ101" r:id="rId100"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ102" r:id="rId101"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ103" r:id="rId102"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ104" r:id="rId103"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ105" r:id="rId104"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ106" r:id="rId105"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ107" r:id="rId106"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ108" r:id="rId107"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ109" r:id="rId108"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ110" r:id="rId109"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ111" r:id="rId110"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ112" r:id="rId111"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ113" r:id="rId112"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ114" r:id="rId113"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ115" r:id="rId114"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ116" r:id="rId115"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ117" r:id="rId116"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ118" r:id="rId117"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ119" r:id="rId118"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ120" r:id="rId119"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ121" r:id="rId120"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>